--- a/worklog/김송희_주간업무일지_20260810-0814.xlsx
+++ b/worklog/김송희_주간업무일지_20260810-0814.xlsx
@@ -25,8 +25,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="hh:mm"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="hh:mm"/>
   </numFmts>
   <fonts count="37">
     <font>
@@ -308,7 +308,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -432,25 +432,46 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -994,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L79"/>
+  <dimension ref="A1:L76"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="26" min="1" max="1"/>
@@ -1927,7 +1948,6 @@
         </is>
       </c>
     </row>
-    <row r="65"/>
     <row r="66">
       <c r="A66" s="21" t="inlineStr">
         <is>
@@ -2105,9 +2125,6 @@
         </is>
       </c>
     </row>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -2187,7 +2204,7 @@
           <t>기준 주(월요일)</t>
         </is>
       </c>
-      <c r="B3" s="45" t="n">
+      <c r="B3" s="52" t="n">
         <v>46244</v>
       </c>
       <c r="C3" s="32" t="inlineStr">
@@ -2195,7 +2212,7 @@
           <t>작성일</t>
         </is>
       </c>
-      <c r="D3" s="45" t="n">
+      <c r="D3" s="52" t="n">
         <v>46248</v>
       </c>
       <c r="F3" s="32" t="inlineStr">
@@ -2313,7 +2330,7 @@
       </c>
     </row>
     <row r="7" ht="19.5" customHeight="1" s="26">
-      <c r="A7" s="46">
+      <c r="A7" s="53">
         <f>IF($B$3="","",$B$3+0)</f>
         <v/>
       </c>
@@ -2322,10 +2339,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="C7" s="47" t="n">
+      <c r="C7" s="54" t="n">
         <v>0.375</v>
       </c>
-      <c r="D7" s="47" t="n">
+      <c r="D7" s="54" t="n">
         <v>0.3958333333333333</v>
       </c>
       <c r="E7" s="5">
@@ -2391,7 +2408,7 @@
       </c>
     </row>
     <row r="8" ht="19.5" customHeight="1" s="26">
-      <c r="A8" s="46">
+      <c r="A8" s="53">
         <f>IF($B$3="","",$B$3+0)</f>
         <v/>
       </c>
@@ -2400,10 +2417,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="C8" s="47" t="n">
+      <c r="C8" s="54" t="n">
         <v>0.3958333333333333</v>
       </c>
-      <c r="D8" s="47" t="n">
+      <c r="D8" s="54" t="n">
         <v>0.4166666666666667</v>
       </c>
       <c r="E8" s="5">
@@ -2464,7 +2481,7 @@
       </c>
     </row>
     <row r="9" ht="19.5" customHeight="1" s="26">
-      <c r="A9" s="46">
+      <c r="A9" s="53">
         <f>IF($B$3="","",$B$3+0)</f>
         <v/>
       </c>
@@ -2473,10 +2490,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="C9" s="47" t="n">
+      <c r="C9" s="54" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="D9" s="47" t="n">
+      <c r="D9" s="54" t="n">
         <v>0.4583333333333333</v>
       </c>
       <c r="E9" s="5">
@@ -2541,7 +2558,7 @@
       </c>
     </row>
     <row r="10" ht="19.5" customHeight="1" s="26">
-      <c r="A10" s="46">
+      <c r="A10" s="53">
         <f>IF($B$3="","",$B$3+0)</f>
         <v/>
       </c>
@@ -2550,10 +2567,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="C10" s="47" t="n">
+      <c r="C10" s="54" t="n">
         <v>0.4583333333333333</v>
       </c>
-      <c r="D10" s="47" t="n">
+      <c r="D10" s="54" t="n">
         <v>0.4791666666666667</v>
       </c>
       <c r="E10" s="5">
@@ -2623,7 +2640,7 @@
       </c>
     </row>
     <row r="11" ht="19.5" customHeight="1" s="26">
-      <c r="A11" s="46">
+      <c r="A11" s="53">
         <f>IF($B$3="","",$B$3+0)</f>
         <v/>
       </c>
@@ -2632,10 +2649,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="C11" s="47" t="n">
+      <c r="C11" s="54" t="n">
         <v>0.4791666666666667</v>
       </c>
-      <c r="D11" s="47" t="n">
+      <c r="D11" s="54" t="n">
         <v>0.5</v>
       </c>
       <c r="E11" s="5">
@@ -2705,7 +2722,7 @@
       </c>
     </row>
     <row r="12" ht="19.5" customHeight="1" s="26">
-      <c r="A12" s="46">
+      <c r="A12" s="53">
         <f>IF($B$3="","",$B$3+0)</f>
         <v/>
       </c>
@@ -2714,10 +2731,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="C12" s="47" t="n">
+      <c r="C12" s="54" t="n">
         <v>0.5</v>
       </c>
-      <c r="D12" s="47" t="n">
+      <c r="D12" s="54" t="n">
         <v>0.5416666666666666</v>
       </c>
       <c r="E12" s="5">
@@ -2762,7 +2779,7 @@
       <c r="R12" s="9" t="n"/>
     </row>
     <row r="13" ht="19.5" customHeight="1" s="26">
-      <c r="A13" s="46">
+      <c r="A13" s="53">
         <f>IF($B$3="","",$B$3+0)</f>
         <v/>
       </c>
@@ -2771,10 +2788,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="C13" s="47" t="n">
+      <c r="C13" s="54" t="n">
         <v>0.5416666666666666</v>
       </c>
-      <c r="D13" s="47" t="n">
+      <c r="D13" s="54" t="n">
         <v>0.5625</v>
       </c>
       <c r="E13" s="5">
@@ -2844,7 +2861,7 @@
       </c>
     </row>
     <row r="14" ht="19.5" customHeight="1" s="26">
-      <c r="A14" s="46">
+      <c r="A14" s="53">
         <f>IF($B$3="","",$B$3+0)</f>
         <v/>
       </c>
@@ -2853,10 +2870,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="C14" s="47" t="n">
+      <c r="C14" s="54" t="n">
         <v>0.5625</v>
       </c>
-      <c r="D14" s="47" t="n">
+      <c r="D14" s="54" t="n">
         <v>0.5833333333333334</v>
       </c>
       <c r="E14" s="5">
@@ -2926,7 +2943,7 @@
       </c>
     </row>
     <row r="15" ht="19.5" customHeight="1" s="26">
-      <c r="A15" s="46">
+      <c r="A15" s="53">
         <f>IF($B$3="","",$B$3+0)</f>
         <v/>
       </c>
@@ -2935,10 +2952,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="C15" s="47" t="n">
+      <c r="C15" s="54" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="D15" s="47" t="n">
+      <c r="D15" s="54" t="n">
         <v>0.625</v>
       </c>
       <c r="E15" s="5">
@@ -3008,7 +3025,7 @@
       </c>
     </row>
     <row r="16" ht="19.5" customHeight="1" s="26">
-      <c r="A16" s="46">
+      <c r="A16" s="53">
         <f>IF($B$3="","",$B$3+0)</f>
         <v/>
       </c>
@@ -3017,10 +3034,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="C16" s="47" t="n">
+      <c r="C16" s="54" t="n">
         <v>0.625</v>
       </c>
-      <c r="D16" s="47" t="n">
+      <c r="D16" s="54" t="n">
         <v>0.6458333333333334</v>
       </c>
       <c r="E16" s="5">
@@ -3089,7 +3106,7 @@
       </c>
     </row>
     <row r="17" ht="19.5" customHeight="1" s="26">
-      <c r="A17" s="46">
+      <c r="A17" s="53">
         <f>IF($B$3="","",$B$3+0)</f>
         <v/>
       </c>
@@ -3098,10 +3115,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="C17" s="47" t="n">
+      <c r="C17" s="54" t="n">
         <v>0.6458333333333334</v>
       </c>
-      <c r="D17" s="47" t="n">
+      <c r="D17" s="54" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="E17" s="5">
@@ -3175,7 +3192,7 @@
       </c>
     </row>
     <row r="18" ht="19.5" customHeight="1" s="26">
-      <c r="A18" s="46">
+      <c r="A18" s="53">
         <f>IF($B$3="","",$B$3+0)</f>
         <v/>
       </c>
@@ -3184,10 +3201,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="C18" s="47" t="n">
+      <c r="C18" s="54" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="D18" s="47" t="n">
+      <c r="D18" s="54" t="n">
         <v>0.7083333333333334</v>
       </c>
       <c r="E18" s="5">
@@ -3252,7 +3269,7 @@
       </c>
     </row>
     <row r="19" ht="19.5" customHeight="1" s="26">
-      <c r="A19" s="46">
+      <c r="A19" s="53">
         <f>IF($B$3="","",$B$3+0)</f>
         <v/>
       </c>
@@ -3261,10 +3278,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="C19" s="47" t="n">
+      <c r="C19" s="54" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="D19" s="47" t="n">
+      <c r="D19" s="54" t="n">
         <v>0.75</v>
       </c>
       <c r="E19" s="5">
@@ -3338,7 +3355,7 @@
       </c>
     </row>
     <row r="20" ht="19.5" customHeight="1" s="26">
-      <c r="A20" s="46">
+      <c r="A20" s="53">
         <f>IF($B$3="","",$B$3+0)</f>
         <v/>
       </c>
@@ -3347,8 +3364,8 @@
           <t>월</t>
         </is>
       </c>
-      <c r="C20" s="47" t="n"/>
-      <c r="D20" s="47" t="n"/>
+      <c r="C20" s="54" t="n"/>
+      <c r="D20" s="54" t="n"/>
       <c r="E20" s="5">
         <f>IF(OR(C20="",D20=""),"",(D20-C20)*1440)</f>
         <v/>
@@ -3358,7 +3375,11 @@
       <c r="H20" s="9" t="n"/>
       <c r="I20" s="8" t="n"/>
       <c r="J20" s="8" t="n"/>
-      <c r="K20" s="43" t="n"/>
+      <c r="K20" s="43" t="inlineStr">
+        <is>
+          <t>https://pourstorecrm.web.app/pour-os</t>
+        </is>
+      </c>
       <c r="L20" s="8" t="n"/>
       <c r="M20" s="8" t="n"/>
       <c r="N20" s="8" t="n"/>
@@ -3368,7 +3389,7 @@
       <c r="R20" s="9" t="n"/>
     </row>
     <row r="21" ht="19.5" customHeight="1" s="26">
-      <c r="A21" s="46">
+      <c r="A21" s="53">
         <f>IF($B$3="","",$B$3+0)</f>
         <v/>
       </c>
@@ -3377,8 +3398,8 @@
           <t>월</t>
         </is>
       </c>
-      <c r="C21" s="47" t="n"/>
-      <c r="D21" s="47" t="n"/>
+      <c r="C21" s="54" t="n"/>
+      <c r="D21" s="54" t="n"/>
       <c r="E21" s="5">
         <f>IF(OR(C21="",D21=""),"",(D21-C21)*1440)</f>
         <v/>
@@ -3397,7 +3418,7 @@
       <c r="R21" s="9" t="n"/>
     </row>
     <row r="22" ht="19.5" customHeight="1" s="26">
-      <c r="A22" s="46">
+      <c r="A22" s="53">
         <f>IF($B$3="","",$B$3+0)</f>
         <v/>
       </c>
@@ -3406,8 +3427,8 @@
           <t>월</t>
         </is>
       </c>
-      <c r="C22" s="47" t="n"/>
-      <c r="D22" s="47" t="n"/>
+      <c r="C22" s="54" t="n"/>
+      <c r="D22" s="54" t="n"/>
       <c r="E22" s="5">
         <f>IF(OR(C22="",D22=""),"",(D22-C22)*1440)</f>
         <v/>
@@ -3426,7 +3447,7 @@
       <c r="R22" s="9" t="n"/>
     </row>
     <row r="23" ht="19.5" customHeight="1" s="26">
-      <c r="A23" s="46">
+      <c r="A23" s="53">
         <f>IF($B$3="","",$B$3+0)</f>
         <v/>
       </c>
@@ -3435,8 +3456,8 @@
           <t>월</t>
         </is>
       </c>
-      <c r="C23" s="47" t="n"/>
-      <c r="D23" s="47" t="n"/>
+      <c r="C23" s="54" t="n"/>
+      <c r="D23" s="54" t="n"/>
       <c r="E23" s="5">
         <f>IF(OR(C23="",D23=""),"",(D23-C23)*1440)</f>
         <v/>
@@ -3455,7 +3476,7 @@
       <c r="R23" s="9" t="n"/>
     </row>
     <row r="24" ht="19.5" customHeight="1" s="26">
-      <c r="A24" s="46">
+      <c r="A24" s="53">
         <f>IF($B$3="","",$B$3+0)</f>
         <v/>
       </c>
@@ -3464,8 +3485,8 @@
           <t>월</t>
         </is>
       </c>
-      <c r="C24" s="47" t="n"/>
-      <c r="D24" s="47" t="n"/>
+      <c r="C24" s="54" t="n"/>
+      <c r="D24" s="54" t="n"/>
       <c r="E24" s="5">
         <f>IF(OR(C24="",D24=""),"",(D24-C24)*1440)</f>
         <v/>
@@ -3484,7 +3505,7 @@
       <c r="R24" s="9" t="n"/>
     </row>
     <row r="25" ht="19.5" customHeight="1" s="26">
-      <c r="A25" s="46">
+      <c r="A25" s="53">
         <f>IF($B$3="","",$B$3+0)</f>
         <v/>
       </c>
@@ -3493,8 +3514,8 @@
           <t>월(추가)</t>
         </is>
       </c>
-      <c r="C25" s="47" t="n"/>
-      <c r="D25" s="47" t="n"/>
+      <c r="C25" s="54" t="n"/>
+      <c r="D25" s="54" t="n"/>
       <c r="E25" s="5">
         <f>IF(OR(C25="",D25=""),"",(D25-C25)*1440)</f>
         <v/>
@@ -3513,7 +3534,7 @@
       <c r="R25" s="9" t="n"/>
     </row>
     <row r="26" ht="19.5" customHeight="1" s="26">
-      <c r="A26" s="46">
+      <c r="A26" s="53">
         <f>IF($B$3="","",$B$3+0)</f>
         <v/>
       </c>
@@ -3522,8 +3543,8 @@
           <t>월(추가)</t>
         </is>
       </c>
-      <c r="C26" s="47" t="n"/>
-      <c r="D26" s="47" t="n"/>
+      <c r="C26" s="54" t="n"/>
+      <c r="D26" s="54" t="n"/>
       <c r="E26" s="5">
         <f>IF(OR(C26="",D26=""),"",(D26-C26)*1440)</f>
         <v/>
@@ -3542,7 +3563,7 @@
       <c r="R26" s="9" t="n"/>
     </row>
     <row r="27" ht="19.5" customHeight="1" s="26">
-      <c r="A27" s="46">
+      <c r="A27" s="53">
         <f>IF($B$3="","",$B$3+1)</f>
         <v/>
       </c>
@@ -3551,10 +3572,10 @@
           <t>화</t>
         </is>
       </c>
-      <c r="C27" s="47" t="n">
+      <c r="C27" s="54" t="n">
         <v>0.375</v>
       </c>
-      <c r="D27" s="47" t="n">
+      <c r="D27" s="54" t="n">
         <v>0.3958333333333333</v>
       </c>
       <c r="E27" s="5">
@@ -3620,7 +3641,7 @@
       </c>
     </row>
     <row r="28" ht="19.5" customHeight="1" s="26">
-      <c r="A28" s="46">
+      <c r="A28" s="53">
         <f>IF($B$3="","",$B$3+1)</f>
         <v/>
       </c>
@@ -3629,10 +3650,10 @@
           <t>화</t>
         </is>
       </c>
-      <c r="C28" s="47" t="n">
+      <c r="C28" s="54" t="n">
         <v>0.3958333333333333</v>
       </c>
-      <c r="D28" s="47" t="n">
+      <c r="D28" s="54" t="n">
         <v>0.4583333333333333</v>
       </c>
       <c r="E28" s="5">
@@ -3702,7 +3723,7 @@
       </c>
     </row>
     <row r="29" ht="19.5" customHeight="1" s="26">
-      <c r="A29" s="46">
+      <c r="A29" s="53">
         <f>IF($B$3="","",$B$3+1)</f>
         <v/>
       </c>
@@ -3711,10 +3732,10 @@
           <t>화</t>
         </is>
       </c>
-      <c r="C29" s="47" t="n">
+      <c r="C29" s="54" t="n">
         <v>0.4583333333333333</v>
       </c>
-      <c r="D29" s="47" t="n">
+      <c r="D29" s="54" t="n">
         <v>0.5</v>
       </c>
       <c r="E29" s="5">
@@ -3723,27 +3744,27 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>마케팅·광고운영</t>
+          <t>콘텐츠제작</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>MKT-04 인플루언서·체험단 섭외/관리</t>
+          <t>CNT-02 촬영 기획·진행</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>채림님 인플루언서 협업마케팅 진행방향 안내 및 진행안 컨펌</t>
+          <t>제품시공 촬영 — 테스트촬영 및 대여 탐색, 채림님께 인수인계하여 진행 요청 (아파트·공장·일반주택 대상)</t>
         </is>
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>POUR스토어</t>
+          <t>시공 제품 / 아파트·공장·일반주택</t>
         </is>
       </c>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>레뷰, 리뷰플레이스</t>
+          <t>CRM센터-POUR OS(업무보드)</t>
         </is>
       </c>
       <c r="K29" s="43" t="inlineStr">
@@ -3756,19 +3777,15 @@
           <t>양채림</t>
         </is>
       </c>
-      <c r="M29" s="8" t="inlineStr">
-        <is>
-          <t>인플루언서</t>
-        </is>
-      </c>
+      <c r="M29" s="8" t="n"/>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t>협업 진행안 컨펌</t>
+          <t>테스트 촬영본, 촬영 진행 요청서</t>
         </is>
       </c>
       <c r="O29" s="8" t="inlineStr">
         <is>
-          <t>주 1회</t>
+          <t>1회성</t>
         </is>
       </c>
       <c r="P29" s="8" t="inlineStr">
@@ -3783,12 +3800,12 @@
       </c>
       <c r="R29" s="9" t="inlineStr">
         <is>
-          <t>인플루언서 협업 진행 기준(가이드) 문서화 후 위임</t>
+          <t>건물유형별 시공 촬영 가이드·촬영 자산 라이브러리 공용화</t>
         </is>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="26">
-      <c r="A30" s="46">
+      <c r="A30" s="53">
         <f>IF($B$3="","",$B$3+1)</f>
         <v/>
       </c>
@@ -3797,10 +3814,10 @@
           <t>화</t>
         </is>
       </c>
-      <c r="C30" s="47" t="n">
+      <c r="C30" s="54" t="n">
         <v>0.5</v>
       </c>
-      <c r="D30" s="47" t="n">
+      <c r="D30" s="54" t="n">
         <v>0.5416666666666666</v>
       </c>
       <c r="E30" s="5">
@@ -3845,7 +3862,7 @@
       <c r="R30" s="9" t="n"/>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="26">
-      <c r="A31" s="46">
+      <c r="A31" s="53">
         <f>IF($B$3="","",$B$3+1)</f>
         <v/>
       </c>
@@ -3854,10 +3871,10 @@
           <t>화</t>
         </is>
       </c>
-      <c r="C31" s="47" t="n">
+      <c r="C31" s="54" t="n">
         <v>0.5416666666666666</v>
       </c>
-      <c r="D31" s="47" t="n">
+      <c r="D31" s="54" t="n">
         <v>0.5833333333333334</v>
       </c>
       <c r="E31" s="5">
@@ -3866,48 +3883,52 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>사내시스템·자동화</t>
+          <t>마케팅·광고운영</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>SYS-01 사내 시스템·앱 기획/개선 요청</t>
+          <t>MKT-04 인플루언서·체험단 섭외/관리</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>소싱앱 UX/UI 개선 — 정하님 추가 고도화 건 2차 피드백</t>
+          <t>채림님 인플루언서 협업마케팅 진행방향 안내 및 진행안 컨펌</t>
         </is>
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>소싱앱</t>
+          <t>POUR스토어</t>
         </is>
       </c>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>소싱앱</t>
+          <t>레뷰, 리뷰플레이스</t>
         </is>
       </c>
       <c r="K31" s="44" t="inlineStr">
         <is>
-          <t>소싱 관리 · 모여라딜 (moyeoradeal-sourcing.pages.dev)</t>
+          <t>https://pourstorecrm.web.app/pour-os</t>
         </is>
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>정하</t>
-        </is>
-      </c>
-      <c r="M31" s="8" t="n"/>
+          <t>양채림</t>
+        </is>
+      </c>
+      <c r="M31" s="8" t="inlineStr">
+        <is>
+          <t>인플루언서</t>
+        </is>
+      </c>
       <c r="N31" s="8" t="inlineStr">
         <is>
-          <t>UX/UI 2차 피드백</t>
+          <t>협업 진행안 컨펌</t>
         </is>
       </c>
       <c r="O31" s="8" t="inlineStr">
         <is>
-          <t>주 2~3회</t>
+          <t>주 1회</t>
         </is>
       </c>
       <c r="P31" s="8" t="inlineStr">
@@ -3917,17 +3938,17 @@
       </c>
       <c r="Q31" s="8" t="inlineStr">
         <is>
-          <t>모름</t>
+          <t>아마도 중복</t>
         </is>
       </c>
       <c r="R31" s="9" t="inlineStr">
         <is>
-          <t>개선 요청·피드백 이력을 앱 내 이슈보드로 관리</t>
+          <t>인플루언서 협업 진행 기준(가이드) 문서화 후 위임</t>
         </is>
       </c>
     </row>
     <row r="32" ht="19.5" customHeight="1" s="26">
-      <c r="A32" s="46">
+      <c r="A32" s="53">
         <f>IF($B$3="","",$B$3+1)</f>
         <v/>
       </c>
@@ -3936,10 +3957,10 @@
           <t>화</t>
         </is>
       </c>
-      <c r="C32" s="47" t="n">
+      <c r="C32" s="54" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="D32" s="47" t="n">
+      <c r="D32" s="54" t="n">
         <v>0.625</v>
       </c>
       <c r="E32" s="5">
@@ -3948,35 +3969,48 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>상품기획·소싱</t>
+          <t>사내시스템·자동화</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>PLN-01 신상품 아이템 발굴/시장조사</t>
+          <t>SYS-01 사내 시스템·앱 기획/개선 요청</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>본품 외 부자재·안전용품 등 판매 세팅 검토 — 우선순위 재조정으로 보류</t>
+          <t>소싱앱 UX/UI 개선 — 정하님 추가 고도화 건 2차 피드백</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>부자재·안전용품</t>
-        </is>
-      </c>
-      <c r="J32" s="8" t="n"/>
-      <c r="L32" s="8" t="n"/>
+          <t>소싱앱</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>소싱앱</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>소싱 관리 · 모여라딜 (moyeoradeal-sourcing.pages.dev)</t>
+        </is>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>정하</t>
+        </is>
+      </c>
       <c r="M32" s="8" t="n"/>
       <c r="N32" s="8" t="inlineStr">
         <is>
-          <t>판매 세팅 검토안(보류)</t>
+          <t>UX/UI 2차 피드백</t>
         </is>
       </c>
       <c r="O32" s="8" t="inlineStr">
         <is>
-          <t>분기/비정기</t>
+          <t>주 2~3회</t>
         </is>
       </c>
       <c r="P32" s="8" t="inlineStr">
@@ -3986,17 +4020,17 @@
       </c>
       <c r="Q32" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
+          <t>모름</t>
         </is>
       </c>
       <c r="R32" s="9" t="inlineStr">
         <is>
-          <t>부자재 카테고리 소싱 기준 정립 후 일괄 세팅</t>
+          <t>개선 요청·피드백 이력을 앱 내 이슈보드로 관리</t>
         </is>
       </c>
     </row>
     <row r="33" ht="19.5" customHeight="1" s="26">
-      <c r="A33" s="46">
+      <c r="A33" s="53">
         <f>IF($B$3="","",$B$3+1)</f>
         <v/>
       </c>
@@ -4005,11 +4039,11 @@
           <t>화</t>
         </is>
       </c>
-      <c r="C33" s="47" t="n">
+      <c r="C33" s="54" t="n">
         <v>0.625</v>
       </c>
-      <c r="D33" s="47" t="n">
-        <v>0.6875</v>
+      <c r="D33" s="54" t="n">
+        <v>0.6458333333333334</v>
       </c>
       <c r="E33" s="5">
         <f>IF(OR(C33="",D33=""),"",(D33-C33)*1440)</f>
@@ -4017,44 +4051,36 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>데이터·정산</t>
+          <t>상품기획·소싱</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>DAT-04 리포트·대시보드 작성</t>
+          <t>PLN-01 신상품 아이템 발굴/시장조사</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>POUR스토어 단가·공헌이익·손익계산 대시보드 제작 — 진행중(전주 이월)</t>
+          <t>본품 외 부자재·안전용품 등 판매 세팅 검토 — 우선순위 재조정으로 보류</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>POUR스토어</t>
-        </is>
-      </c>
-      <c r="J33" s="8" t="inlineStr">
-        <is>
-          <t>단가 대시보드, 엑셀</t>
-        </is>
-      </c>
-      <c r="K33" s="44" t="inlineStr">
-        <is>
-          <t>POUR스토어 가격·마진 통합 대시보드 (pour-construction-form.pages.dev)</t>
-        </is>
-      </c>
+          <t>부자재·안전용품</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="n"/>
+      <c r="K33" s="44" t="n"/>
       <c r="L33" s="8" t="n"/>
       <c r="M33" s="8" t="n"/>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t>단가·공헌이익·손익 대시보드</t>
+          <t>판매 세팅 검토안(보류)</t>
         </is>
       </c>
       <c r="O33" s="8" t="inlineStr">
         <is>
-          <t>주 2~3회</t>
+          <t>분기/비정기</t>
         </is>
       </c>
       <c r="P33" s="8" t="inlineStr">
@@ -4069,12 +4095,12 @@
       </c>
       <c r="R33" s="9" t="inlineStr">
         <is>
-          <t>채널 수수료·원가 데이터 자동 연동으로 수기 입력 제거</t>
+          <t>부자재 카테고리 소싱 기준 정립 후 일괄 세팅</t>
         </is>
       </c>
     </row>
     <row r="34" ht="19.5" customHeight="1" s="26">
-      <c r="A34" s="46">
+      <c r="A34" s="53">
         <f>IF($B$3="","",$B$3+1)</f>
         <v/>
       </c>
@@ -4083,11 +4109,11 @@
           <t>화</t>
         </is>
       </c>
-      <c r="C34" s="47" t="n">
+      <c r="C34" s="54" t="n">
+        <v>0.6458333333333334</v>
+      </c>
+      <c r="D34" s="54" t="n">
         <v>0.6875</v>
-      </c>
-      <c r="D34" s="47" t="n">
-        <v>0.75</v>
       </c>
       <c r="E34" s="5">
         <f>IF(OR(C34="",D34=""),"",(D34-C34)*1440)</f>
@@ -4095,63 +4121,64 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>제조·생산관리</t>
+          <t>데이터·정산</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>MFG-08 MSDS·라벨 등 제품 표시사항 제작</t>
+          <t>DAT-04 리포트·대시보드 작성</t>
         </is>
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>신제품 코트재 MSDS 컬러별 31개 제작 — 진행중</t>
+          <t>POUR스토어 단가·공헌이익·손익계산 대시보드 제작 — 진행중(전주 이월)</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>코트재 신제품 31색</t>
+          <t>POUR스토어</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t>챗지피티</t>
+          <t>단가 대시보드, 엑셀</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>POUR스토어 가격·마진 통합 대시보드 (pour-construction-form.pages.dev)</t>
         </is>
       </c>
       <c r="L34" s="8" t="n"/>
-      <c r="M34" s="8" t="inlineStr">
-        <is>
-          <t>세이고, 쿠팡물류센터</t>
-        </is>
-      </c>
+      <c r="M34" s="8" t="n"/>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>MSDS 31종</t>
+          <t>단가·공헌이익·손익 대시보드</t>
         </is>
       </c>
       <c r="O34" s="8" t="inlineStr">
         <is>
-          <t>1회성</t>
+          <t>주 2~3회</t>
         </is>
       </c>
       <c r="P34" s="8" t="inlineStr">
         <is>
-          <t>반정형</t>
+          <t>비정형(판단 필요)</t>
         </is>
       </c>
       <c r="Q34" s="8" t="inlineStr">
         <is>
-          <t>아니오 - 우리팀 고유</t>
+          <t>아마도 중복</t>
         </is>
       </c>
       <c r="R34" s="9" t="inlineStr">
         <is>
-          <t>품목·색상 데이터 연동으로 MSDS 서식 자동 생성</t>
+          <t>채널 수수료·원가 데이터 자동 연동으로 수기 입력 제거</t>
         </is>
       </c>
     </row>
     <row r="35" ht="19.5" customHeight="1" s="26">
-      <c r="A35" s="46">
+      <c r="A35" s="53">
         <f>IF($B$3="","",$B$3+1)</f>
         <v/>
       </c>
@@ -4160,27 +4187,75 @@
           <t>화</t>
         </is>
       </c>
-      <c r="C35" s="47" t="n"/>
-      <c r="D35" s="47" t="n"/>
+      <c r="C35" s="54" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="D35" s="54" t="n">
+        <v>0.75</v>
+      </c>
       <c r="E35" s="5">
         <f>IF(OR(C35="",D35=""),"",(D35-C35)*1440)</f>
         <v/>
       </c>
-      <c r="F35" s="8" t="n"/>
-      <c r="G35" s="8" t="n"/>
-      <c r="H35" s="9" t="n"/>
-      <c r="I35" s="8" t="n"/>
-      <c r="J35" s="8" t="n"/>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>제조·생산관리</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>MFG-08 MSDS·라벨 등 제품 표시사항 제작</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>신제품 코트재 MSDS 컬러별 31개 제작 — 진행중</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>코트재 신제품 31색</t>
+        </is>
+      </c>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>챗지피티</t>
+        </is>
+      </c>
       <c r="L35" s="8" t="n"/>
-      <c r="M35" s="8" t="n"/>
-      <c r="N35" s="8" t="n"/>
-      <c r="O35" s="8" t="n"/>
-      <c r="P35" s="8" t="n"/>
-      <c r="Q35" s="8" t="n"/>
-      <c r="R35" s="9" t="n"/>
+      <c r="M35" s="8" t="inlineStr">
+        <is>
+          <t>세이고, 쿠팡물류센터</t>
+        </is>
+      </c>
+      <c r="N35" s="8" t="inlineStr">
+        <is>
+          <t>MSDS 31종</t>
+        </is>
+      </c>
+      <c r="O35" s="8" t="inlineStr">
+        <is>
+          <t>1회성</t>
+        </is>
+      </c>
+      <c r="P35" s="8" t="inlineStr">
+        <is>
+          <t>반정형</t>
+        </is>
+      </c>
+      <c r="Q35" s="8" t="inlineStr">
+        <is>
+          <t>아니오 - 우리팀 고유</t>
+        </is>
+      </c>
+      <c r="R35" s="9" t="inlineStr">
+        <is>
+          <t>품목·색상 데이터 연동으로 MSDS 서식 자동 생성</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="19.5" customHeight="1" s="26">
-      <c r="A36" s="46">
+      <c r="A36" s="53">
         <f>IF($B$3="","",$B$3+1)</f>
         <v/>
       </c>
@@ -4189,8 +4264,8 @@
           <t>화</t>
         </is>
       </c>
-      <c r="C36" s="47" t="n"/>
-      <c r="D36" s="47" t="n"/>
+      <c r="C36" s="54" t="n"/>
+      <c r="D36" s="54" t="n"/>
       <c r="E36" s="5">
         <f>IF(OR(C36="",D36=""),"",(D36-C36)*1440)</f>
         <v/>
@@ -4209,7 +4284,7 @@
       <c r="R36" s="9" t="n"/>
     </row>
     <row r="37" ht="19.5" customHeight="1" s="26">
-      <c r="A37" s="46">
+      <c r="A37" s="53">
         <f>IF($B$3="","",$B$3+1)</f>
         <v/>
       </c>
@@ -4218,8 +4293,8 @@
           <t>화</t>
         </is>
       </c>
-      <c r="C37" s="47" t="n"/>
-      <c r="D37" s="47" t="n"/>
+      <c r="C37" s="54" t="n"/>
+      <c r="D37" s="54" t="n"/>
       <c r="E37" s="5">
         <f>IF(OR(C37="",D37=""),"",(D37-C37)*1440)</f>
         <v/>
@@ -4238,7 +4313,7 @@
       <c r="R37" s="9" t="n"/>
     </row>
     <row r="38" ht="19.5" customHeight="1" s="26">
-      <c r="A38" s="46">
+      <c r="A38" s="53">
         <f>IF($B$3="","",$B$3+1)</f>
         <v/>
       </c>
@@ -4247,8 +4322,8 @@
           <t>화</t>
         </is>
       </c>
-      <c r="C38" s="47" t="n"/>
-      <c r="D38" s="47" t="n"/>
+      <c r="C38" s="54" t="n"/>
+      <c r="D38" s="54" t="n"/>
       <c r="E38" s="5">
         <f>IF(OR(C38="",D38=""),"",(D38-C38)*1440)</f>
         <v/>
@@ -4267,7 +4342,7 @@
       <c r="R38" s="9" t="n"/>
     </row>
     <row r="39" ht="19.5" customHeight="1" s="26">
-      <c r="A39" s="46">
+      <c r="A39" s="53">
         <f>IF($B$3="","",$B$3+1)</f>
         <v/>
       </c>
@@ -4276,8 +4351,8 @@
           <t>화</t>
         </is>
       </c>
-      <c r="C39" s="47" t="n"/>
-      <c r="D39" s="47" t="n"/>
+      <c r="C39" s="54" t="n"/>
+      <c r="D39" s="54" t="n"/>
       <c r="E39" s="5">
         <f>IF(OR(C39="",D39=""),"",(D39-C39)*1440)</f>
         <v/>
@@ -4296,7 +4371,7 @@
       <c r="R39" s="9" t="n"/>
     </row>
     <row r="40" ht="19.5" customHeight="1" s="26">
-      <c r="A40" s="46">
+      <c r="A40" s="53">
         <f>IF($B$3="","",$B$3+1)</f>
         <v/>
       </c>
@@ -4305,8 +4380,8 @@
           <t>화</t>
         </is>
       </c>
-      <c r="C40" s="47" t="n"/>
-      <c r="D40" s="47" t="n"/>
+      <c r="C40" s="54" t="n"/>
+      <c r="D40" s="54" t="n"/>
       <c r="E40" s="5">
         <f>IF(OR(C40="",D40=""),"",(D40-C40)*1440)</f>
         <v/>
@@ -4325,7 +4400,7 @@
       <c r="R40" s="9" t="n"/>
     </row>
     <row r="41" ht="19.5" customHeight="1" s="26">
-      <c r="A41" s="46">
+      <c r="A41" s="53">
         <f>IF($B$3="","",$B$3+1)</f>
         <v/>
       </c>
@@ -4334,8 +4409,8 @@
           <t>화</t>
         </is>
       </c>
-      <c r="C41" s="47" t="n"/>
-      <c r="D41" s="47" t="n"/>
+      <c r="C41" s="54" t="n"/>
+      <c r="D41" s="54" t="n"/>
       <c r="E41" s="5">
         <f>IF(OR(C41="",D41=""),"",(D41-C41)*1440)</f>
         <v/>
@@ -4354,7 +4429,7 @@
       <c r="R41" s="9" t="n"/>
     </row>
     <row r="42" ht="19.5" customHeight="1" s="26">
-      <c r="A42" s="46">
+      <c r="A42" s="53">
         <f>IF($B$3="","",$B$3+1)</f>
         <v/>
       </c>
@@ -4363,8 +4438,8 @@
           <t>화</t>
         </is>
       </c>
-      <c r="C42" s="47" t="n"/>
-      <c r="D42" s="47" t="n"/>
+      <c r="C42" s="54" t="n"/>
+      <c r="D42" s="54" t="n"/>
       <c r="E42" s="5">
         <f>IF(OR(C42="",D42=""),"",(D42-C42)*1440)</f>
         <v/>
@@ -4383,7 +4458,7 @@
       <c r="R42" s="9" t="n"/>
     </row>
     <row r="43" ht="19.5" customHeight="1" s="26">
-      <c r="A43" s="46">
+      <c r="A43" s="53">
         <f>IF($B$3="","",$B$3+1)</f>
         <v/>
       </c>
@@ -4392,8 +4467,8 @@
           <t>화</t>
         </is>
       </c>
-      <c r="C43" s="47" t="n"/>
-      <c r="D43" s="47" t="n"/>
+      <c r="C43" s="54" t="n"/>
+      <c r="D43" s="54" t="n"/>
       <c r="E43" s="5">
         <f>IF(OR(C43="",D43=""),"",(D43-C43)*1440)</f>
         <v/>
@@ -4412,7 +4487,7 @@
       <c r="R43" s="9" t="n"/>
     </row>
     <row r="44" ht="19.5" customHeight="1" s="26">
-      <c r="A44" s="46">
+      <c r="A44" s="53">
         <f>IF($B$3="","",$B$3+1)</f>
         <v/>
       </c>
@@ -4421,8 +4496,8 @@
           <t>화</t>
         </is>
       </c>
-      <c r="C44" s="47" t="n"/>
-      <c r="D44" s="47" t="n"/>
+      <c r="C44" s="54" t="n"/>
+      <c r="D44" s="54" t="n"/>
       <c r="E44" s="5">
         <f>IF(OR(C44="",D44=""),"",(D44-C44)*1440)</f>
         <v/>
@@ -4441,7 +4516,7 @@
       <c r="R44" s="9" t="n"/>
     </row>
     <row r="45" ht="19.5" customHeight="1" s="26">
-      <c r="A45" s="46">
+      <c r="A45" s="53">
         <f>IF($B$3="","",$B$3+1)</f>
         <v/>
       </c>
@@ -4450,8 +4525,8 @@
           <t>화(추가)</t>
         </is>
       </c>
-      <c r="C45" s="47" t="n"/>
-      <c r="D45" s="47" t="n"/>
+      <c r="C45" s="54" t="n"/>
+      <c r="D45" s="54" t="n"/>
       <c r="E45" s="5">
         <f>IF(OR(C45="",D45=""),"",(D45-C45)*1440)</f>
         <v/>
@@ -4470,7 +4545,7 @@
       <c r="R45" s="9" t="n"/>
     </row>
     <row r="46" ht="19.5" customHeight="1" s="26">
-      <c r="A46" s="46">
+      <c r="A46" s="53">
         <f>IF($B$3="","",$B$3+1)</f>
         <v/>
       </c>
@@ -4479,8 +4554,8 @@
           <t>화(추가)</t>
         </is>
       </c>
-      <c r="C46" s="47" t="n"/>
-      <c r="D46" s="47" t="n"/>
+      <c r="C46" s="54" t="n"/>
+      <c r="D46" s="54" t="n"/>
       <c r="E46" s="5">
         <f>IF(OR(C46="",D46=""),"",(D46-C46)*1440)</f>
         <v/>
@@ -4499,7 +4574,7 @@
       <c r="R46" s="9" t="n"/>
     </row>
     <row r="47" ht="19.5" customHeight="1" s="26">
-      <c r="A47" s="46">
+      <c r="A47" s="53">
         <f>IF($B$3="","",$B$3+2)</f>
         <v/>
       </c>
@@ -4508,10 +4583,10 @@
           <t>수</t>
         </is>
       </c>
-      <c r="C47" s="47" t="n">
+      <c r="C47" s="54" t="n">
         <v>0.375</v>
       </c>
-      <c r="D47" s="47" t="n">
+      <c r="D47" s="54" t="n">
         <v>0.3958333333333333</v>
       </c>
       <c r="E47" s="5">
@@ -4577,7 +4652,7 @@
       </c>
     </row>
     <row r="48" ht="19.5" customHeight="1" s="26">
-      <c r="A48" s="46">
+      <c r="A48" s="53">
         <f>IF($B$3="","",$B$3+2)</f>
         <v/>
       </c>
@@ -4586,10 +4661,10 @@
           <t>수</t>
         </is>
       </c>
-      <c r="C48" s="47" t="n">
+      <c r="C48" s="54" t="n">
         <v>0.3958333333333333</v>
       </c>
-      <c r="D48" s="47" t="n">
+      <c r="D48" s="54" t="n">
         <v>0.4375</v>
       </c>
       <c r="E48" s="5">
@@ -4663,7 +4738,7 @@
       </c>
     </row>
     <row r="49" ht="19.5" customHeight="1" s="26">
-      <c r="A49" s="46">
+      <c r="A49" s="53">
         <f>IF($B$3="","",$B$3+2)</f>
         <v/>
       </c>
@@ -4672,10 +4747,10 @@
           <t>수</t>
         </is>
       </c>
-      <c r="C49" s="47" t="n">
+      <c r="C49" s="54" t="n">
         <v>0.4375</v>
       </c>
-      <c r="D49" s="47" t="n">
+      <c r="D49" s="54" t="n">
         <v>0.4791666666666667</v>
       </c>
       <c r="E49" s="5">
@@ -4745,7 +4820,7 @@
       </c>
     </row>
     <row r="50" ht="19.5" customHeight="1" s="26">
-      <c r="A50" s="46">
+      <c r="A50" s="53">
         <f>IF($B$3="","",$B$3+2)</f>
         <v/>
       </c>
@@ -4754,10 +4829,10 @@
           <t>수</t>
         </is>
       </c>
-      <c r="C50" s="47" t="n">
+      <c r="C50" s="54" t="n">
         <v>0.4791666666666667</v>
       </c>
-      <c r="D50" s="47" t="n">
+      <c r="D50" s="54" t="n">
         <v>0.5</v>
       </c>
       <c r="E50" s="5">
@@ -4818,7 +4893,7 @@
       </c>
     </row>
     <row r="51" ht="19.5" customHeight="1" s="26">
-      <c r="A51" s="46">
+      <c r="A51" s="53">
         <f>IF($B$3="","",$B$3+2)</f>
         <v/>
       </c>
@@ -4827,10 +4902,10 @@
           <t>수</t>
         </is>
       </c>
-      <c r="C51" s="47" t="n">
+      <c r="C51" s="54" t="n">
         <v>0.5</v>
       </c>
-      <c r="D51" s="47" t="n">
+      <c r="D51" s="54" t="n">
         <v>0.5416666666666666</v>
       </c>
       <c r="E51" s="5">
@@ -4875,7 +4950,7 @@
       <c r="R51" s="9" t="n"/>
     </row>
     <row r="52" ht="19.5" customHeight="1" s="26">
-      <c r="A52" s="46">
+      <c r="A52" s="53">
         <f>IF($B$3="","",$B$3+2)</f>
         <v/>
       </c>
@@ -4884,10 +4959,10 @@
           <t>수</t>
         </is>
       </c>
-      <c r="C52" s="47" t="n">
+      <c r="C52" s="54" t="n">
         <v>0.5416666666666666</v>
       </c>
-      <c r="D52" s="47" t="n">
+      <c r="D52" s="54" t="n">
         <v>0.5833333333333334</v>
       </c>
       <c r="E52" s="5">
@@ -4957,7 +5032,7 @@
       </c>
     </row>
     <row r="53" ht="19.5" customHeight="1" s="26">
-      <c r="A53" s="46">
+      <c r="A53" s="53">
         <f>IF($B$3="","",$B$3+2)</f>
         <v/>
       </c>
@@ -4966,10 +5041,10 @@
           <t>수</t>
         </is>
       </c>
-      <c r="C53" s="47" t="n">
+      <c r="C53" s="54" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="D53" s="47" t="n">
+      <c r="D53" s="54" t="n">
         <v>0.6041666666666666</v>
       </c>
       <c r="E53" s="5">
@@ -5039,7 +5114,7 @@
       </c>
     </row>
     <row r="54" ht="19.5" customHeight="1" s="26">
-      <c r="A54" s="46">
+      <c r="A54" s="53">
         <f>IF($B$3="","",$B$3+2)</f>
         <v/>
       </c>
@@ -5048,10 +5123,10 @@
           <t>수</t>
         </is>
       </c>
-      <c r="C54" s="47" t="n">
+      <c r="C54" s="54" t="n">
         <v>0.6041666666666666</v>
       </c>
-      <c r="D54" s="47" t="n">
+      <c r="D54" s="54" t="n">
         <v>0.6458333333333334</v>
       </c>
       <c r="E54" s="5">
@@ -5117,7 +5192,7 @@
       </c>
     </row>
     <row r="55" ht="19.5" customHeight="1" s="26">
-      <c r="A55" s="46">
+      <c r="A55" s="53">
         <f>IF($B$3="","",$B$3+2)</f>
         <v/>
       </c>
@@ -5126,10 +5201,10 @@
           <t>수</t>
         </is>
       </c>
-      <c r="C55" s="47" t="n">
+      <c r="C55" s="54" t="n">
         <v>0.6458333333333334</v>
       </c>
-      <c r="D55" s="47" t="n">
+      <c r="D55" s="54" t="n">
         <v>0.6875</v>
       </c>
       <c r="E55" s="5">
@@ -5186,7 +5261,7 @@
       </c>
     </row>
     <row r="56" ht="19.5" customHeight="1" s="26">
-      <c r="A56" s="46">
+      <c r="A56" s="53">
         <f>IF($B$3="","",$B$3+2)</f>
         <v/>
       </c>
@@ -5195,10 +5270,10 @@
           <t>수</t>
         </is>
       </c>
-      <c r="C56" s="47" t="n">
+      <c r="C56" s="54" t="n">
         <v>0.6875</v>
       </c>
-      <c r="D56" s="47" t="n">
+      <c r="D56" s="54" t="n">
         <v>0.7291666666666666</v>
       </c>
       <c r="E56" s="5">
@@ -5264,7 +5339,7 @@
       </c>
     </row>
     <row r="57" ht="19.5" customHeight="1" s="26">
-      <c r="A57" s="46">
+      <c r="A57" s="53">
         <f>IF($B$3="","",$B$3+2)</f>
         <v/>
       </c>
@@ -5273,10 +5348,10 @@
           <t>수</t>
         </is>
       </c>
-      <c r="C57" s="47" t="n">
+      <c r="C57" s="54" t="n">
         <v>0.7291666666666666</v>
       </c>
-      <c r="D57" s="47" t="n">
+      <c r="D57" s="54" t="n">
         <v>0.75</v>
       </c>
       <c r="E57" s="5">
@@ -5341,7 +5416,7 @@
       </c>
     </row>
     <row r="58" ht="19.5" customHeight="1" s="26">
-      <c r="A58" s="46">
+      <c r="A58" s="53">
         <f>IF($B$3="","",$B$3+2)</f>
         <v/>
       </c>
@@ -5350,8 +5425,8 @@
           <t>수</t>
         </is>
       </c>
-      <c r="C58" s="47" t="n"/>
-      <c r="D58" s="47" t="n"/>
+      <c r="C58" s="54" t="n"/>
+      <c r="D58" s="54" t="n"/>
       <c r="E58" s="5">
         <f>IF(OR(C58="",D58=""),"",(D58-C58)*1440)</f>
         <v/>
@@ -5370,7 +5445,7 @@
       <c r="R58" s="9" t="n"/>
     </row>
     <row r="59" ht="19.5" customHeight="1" s="26">
-      <c r="A59" s="46">
+      <c r="A59" s="53">
         <f>IF($B$3="","",$B$3+2)</f>
         <v/>
       </c>
@@ -5379,8 +5454,8 @@
           <t>수</t>
         </is>
       </c>
-      <c r="C59" s="47" t="n"/>
-      <c r="D59" s="47" t="n"/>
+      <c r="C59" s="54" t="n"/>
+      <c r="D59" s="54" t="n"/>
       <c r="E59" s="5">
         <f>IF(OR(C59="",D59=""),"",(D59-C59)*1440)</f>
         <v/>
@@ -5399,7 +5474,7 @@
       <c r="R59" s="9" t="n"/>
     </row>
     <row r="60" ht="19.5" customHeight="1" s="26">
-      <c r="A60" s="46">
+      <c r="A60" s="53">
         <f>IF($B$3="","",$B$3+2)</f>
         <v/>
       </c>
@@ -5408,8 +5483,8 @@
           <t>수</t>
         </is>
       </c>
-      <c r="C60" s="47" t="n"/>
-      <c r="D60" s="47" t="n"/>
+      <c r="C60" s="54" t="n"/>
+      <c r="D60" s="54" t="n"/>
       <c r="E60" s="5">
         <f>IF(OR(C60="",D60=""),"",(D60-C60)*1440)</f>
         <v/>
@@ -5428,7 +5503,7 @@
       <c r="R60" s="9" t="n"/>
     </row>
     <row r="61" ht="19.5" customHeight="1" s="26">
-      <c r="A61" s="46">
+      <c r="A61" s="53">
         <f>IF($B$3="","",$B$3+2)</f>
         <v/>
       </c>
@@ -5437,8 +5512,8 @@
           <t>수</t>
         </is>
       </c>
-      <c r="C61" s="47" t="n"/>
-      <c r="D61" s="47" t="n"/>
+      <c r="C61" s="54" t="n"/>
+      <c r="D61" s="54" t="n"/>
       <c r="E61" s="5">
         <f>IF(OR(C61="",D61=""),"",(D61-C61)*1440)</f>
         <v/>
@@ -5457,7 +5532,7 @@
       <c r="R61" s="9" t="n"/>
     </row>
     <row r="62" ht="19.5" customHeight="1" s="26">
-      <c r="A62" s="46">
+      <c r="A62" s="53">
         <f>IF($B$3="","",$B$3+2)</f>
         <v/>
       </c>
@@ -5466,8 +5541,8 @@
           <t>수</t>
         </is>
       </c>
-      <c r="C62" s="47" t="n"/>
-      <c r="D62" s="47" t="n"/>
+      <c r="C62" s="54" t="n"/>
+      <c r="D62" s="54" t="n"/>
       <c r="E62" s="5">
         <f>IF(OR(C62="",D62=""),"",(D62-C62)*1440)</f>
         <v/>
@@ -5486,7 +5561,7 @@
       <c r="R62" s="9" t="n"/>
     </row>
     <row r="63" ht="19.5" customHeight="1" s="26">
-      <c r="A63" s="46">
+      <c r="A63" s="53">
         <f>IF($B$3="","",$B$3+2)</f>
         <v/>
       </c>
@@ -5495,8 +5570,8 @@
           <t>수</t>
         </is>
       </c>
-      <c r="C63" s="47" t="n"/>
-      <c r="D63" s="47" t="n"/>
+      <c r="C63" s="54" t="n"/>
+      <c r="D63" s="54" t="n"/>
       <c r="E63" s="5">
         <f>IF(OR(C63="",D63=""),"",(D63-C63)*1440)</f>
         <v/>
@@ -5515,7 +5590,7 @@
       <c r="R63" s="9" t="n"/>
     </row>
     <row r="64" ht="19.5" customHeight="1" s="26">
-      <c r="A64" s="46">
+      <c r="A64" s="53">
         <f>IF($B$3="","",$B$3+2)</f>
         <v/>
       </c>
@@ -5524,8 +5599,8 @@
           <t>수</t>
         </is>
       </c>
-      <c r="C64" s="47" t="n"/>
-      <c r="D64" s="47" t="n"/>
+      <c r="C64" s="54" t="n"/>
+      <c r="D64" s="54" t="n"/>
       <c r="E64" s="5">
         <f>IF(OR(C64="",D64=""),"",(D64-C64)*1440)</f>
         <v/>
@@ -5544,7 +5619,7 @@
       <c r="R64" s="9" t="n"/>
     </row>
     <row r="65" ht="19.5" customHeight="1" s="26">
-      <c r="A65" s="46">
+      <c r="A65" s="53">
         <f>IF($B$3="","",$B$3+2)</f>
         <v/>
       </c>
@@ -5553,8 +5628,8 @@
           <t>수(추가)</t>
         </is>
       </c>
-      <c r="C65" s="47" t="n"/>
-      <c r="D65" s="47" t="n"/>
+      <c r="C65" s="54" t="n"/>
+      <c r="D65" s="54" t="n"/>
       <c r="E65" s="5">
         <f>IF(OR(C65="",D65=""),"",(D65-C65)*1440)</f>
         <v/>
@@ -5573,7 +5648,7 @@
       <c r="R65" s="9" t="n"/>
     </row>
     <row r="66" ht="19.5" customHeight="1" s="26">
-      <c r="A66" s="46">
+      <c r="A66" s="53">
         <f>IF($B$3="","",$B$3+2)</f>
         <v/>
       </c>
@@ -5582,8 +5657,8 @@
           <t>수(추가)</t>
         </is>
       </c>
-      <c r="C66" s="47" t="n"/>
-      <c r="D66" s="47" t="n"/>
+      <c r="C66" s="54" t="n"/>
+      <c r="D66" s="54" t="n"/>
       <c r="E66" s="5">
         <f>IF(OR(C66="",D66=""),"",(D66-C66)*1440)</f>
         <v/>
@@ -5602,7 +5677,7 @@
       <c r="R66" s="9" t="n"/>
     </row>
     <row r="67" ht="19.5" customHeight="1" s="26">
-      <c r="A67" s="46">
+      <c r="A67" s="53">
         <f>IF($B$3="","",$B$3+3)</f>
         <v/>
       </c>
@@ -5611,10 +5686,10 @@
           <t>목</t>
         </is>
       </c>
-      <c r="C67" s="47" t="n">
+      <c r="C67" s="54" t="n">
         <v>0.375</v>
       </c>
-      <c r="D67" s="47" t="n">
+      <c r="D67" s="54" t="n">
         <v>0.3958333333333333</v>
       </c>
       <c r="E67" s="5">
@@ -5680,7 +5755,7 @@
       </c>
     </row>
     <row r="68" ht="19.5" customHeight="1" s="26">
-      <c r="A68" s="46">
+      <c r="A68" s="53">
         <f>IF($B$3="","",$B$3+3)</f>
         <v/>
       </c>
@@ -5689,10 +5764,10 @@
           <t>목</t>
         </is>
       </c>
-      <c r="C68" s="47" t="n">
+      <c r="C68" s="54" t="n">
         <v>0.3958333333333333</v>
       </c>
-      <c r="D68" s="47" t="n">
+      <c r="D68" s="54" t="n">
         <v>0.4375</v>
       </c>
       <c r="E68" s="5">
@@ -5761,7 +5836,7 @@
       </c>
     </row>
     <row r="69" ht="19.5" customHeight="1" s="26">
-      <c r="A69" s="46">
+      <c r="A69" s="53">
         <f>IF($B$3="","",$B$3+3)</f>
         <v/>
       </c>
@@ -5770,10 +5845,10 @@
           <t>목</t>
         </is>
       </c>
-      <c r="C69" s="47" t="n">
+      <c r="C69" s="54" t="n">
         <v>0.4375</v>
       </c>
-      <c r="D69" s="47" t="n">
+      <c r="D69" s="54" t="n">
         <v>0.4791666666666667</v>
       </c>
       <c r="E69" s="5">
@@ -5834,7 +5909,7 @@
       </c>
     </row>
     <row r="70" ht="19.5" customHeight="1" s="26">
-      <c r="A70" s="46">
+      <c r="A70" s="53">
         <f>IF($B$3="","",$B$3+3)</f>
         <v/>
       </c>
@@ -5843,10 +5918,10 @@
           <t>목</t>
         </is>
       </c>
-      <c r="C70" s="47" t="n">
+      <c r="C70" s="54" t="n">
         <v>0.4791666666666667</v>
       </c>
-      <c r="D70" s="47" t="n">
+      <c r="D70" s="54" t="n">
         <v>0.5</v>
       </c>
       <c r="E70" s="5">
@@ -5916,7 +5991,7 @@
       </c>
     </row>
     <row r="71" ht="19.5" customHeight="1" s="26">
-      <c r="A71" s="46">
+      <c r="A71" s="53">
         <f>IF($B$3="","",$B$3+3)</f>
         <v/>
       </c>
@@ -5925,10 +6000,10 @@
           <t>목</t>
         </is>
       </c>
-      <c r="C71" s="47" t="n">
+      <c r="C71" s="54" t="n">
         <v>0.5</v>
       </c>
-      <c r="D71" s="47" t="n">
+      <c r="D71" s="54" t="n">
         <v>0.5416666666666666</v>
       </c>
       <c r="E71" s="5">
@@ -5973,7 +6048,7 @@
       <c r="R71" s="9" t="n"/>
     </row>
     <row r="72" ht="19.5" customHeight="1" s="26">
-      <c r="A72" s="46">
+      <c r="A72" s="53">
         <f>IF($B$3="","",$B$3+3)</f>
         <v/>
       </c>
@@ -5982,10 +6057,10 @@
           <t>목</t>
         </is>
       </c>
-      <c r="C72" s="47" t="n">
+      <c r="C72" s="54" t="n">
         <v>0.5416666666666666</v>
       </c>
-      <c r="D72" s="47" t="n">
+      <c r="D72" s="54" t="n">
         <v>0.6041666666666666</v>
       </c>
       <c r="E72" s="5">
@@ -6059,7 +6134,7 @@
       </c>
     </row>
     <row r="73" ht="19.5" customHeight="1" s="26">
-      <c r="A73" s="46">
+      <c r="A73" s="53">
         <f>IF($B$3="","",$B$3+3)</f>
         <v/>
       </c>
@@ -6068,10 +6143,10 @@
           <t>목</t>
         </is>
       </c>
-      <c r="C73" s="47" t="n">
+      <c r="C73" s="54" t="n">
         <v>0.6041666666666666</v>
       </c>
-      <c r="D73" s="47" t="n">
+      <c r="D73" s="54" t="n">
         <v>0.6458333333333334</v>
       </c>
       <c r="E73" s="5">
@@ -6132,7 +6207,7 @@
       </c>
     </row>
     <row r="74" ht="19.5" customHeight="1" s="26">
-      <c r="A74" s="46">
+      <c r="A74" s="53">
         <f>IF($B$3="","",$B$3+3)</f>
         <v/>
       </c>
@@ -6141,10 +6216,10 @@
           <t>목</t>
         </is>
       </c>
-      <c r="C74" s="47" t="n">
+      <c r="C74" s="54" t="n">
         <v>0.6458333333333334</v>
       </c>
-      <c r="D74" s="47" t="n">
+      <c r="D74" s="54" t="n">
         <v>0.7083333333333334</v>
       </c>
       <c r="E74" s="5">
@@ -6210,7 +6285,7 @@
       </c>
     </row>
     <row r="75" ht="19.5" customHeight="1" s="26">
-      <c r="A75" s="46">
+      <c r="A75" s="53">
         <f>IF($B$3="","",$B$3+3)</f>
         <v/>
       </c>
@@ -6219,10 +6294,10 @@
           <t>목</t>
         </is>
       </c>
-      <c r="C75" s="47" t="n">
+      <c r="C75" s="54" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="D75" s="47" t="n">
+      <c r="D75" s="54" t="n">
         <v>0.75</v>
       </c>
       <c r="E75" s="5">
@@ -6287,7 +6362,7 @@
       </c>
     </row>
     <row r="76" ht="19.5" customHeight="1" s="26">
-      <c r="A76" s="46">
+      <c r="A76" s="53">
         <f>IF($B$3="","",$B$3+3)</f>
         <v/>
       </c>
@@ -6296,8 +6371,8 @@
           <t>목</t>
         </is>
       </c>
-      <c r="C76" s="47" t="n"/>
-      <c r="D76" s="47" t="n"/>
+      <c r="C76" s="54" t="n"/>
+      <c r="D76" s="54" t="n"/>
       <c r="E76" s="5">
         <f>IF(OR(C76="",D76=""),"",(D76-C76)*1440)</f>
         <v/>
@@ -6316,7 +6391,7 @@
       <c r="R76" s="9" t="n"/>
     </row>
     <row r="77" ht="19.5" customHeight="1" s="26">
-      <c r="A77" s="46">
+      <c r="A77" s="53">
         <f>IF($B$3="","",$B$3+3)</f>
         <v/>
       </c>
@@ -6325,8 +6400,8 @@
           <t>목</t>
         </is>
       </c>
-      <c r="C77" s="47" t="n"/>
-      <c r="D77" s="47" t="n"/>
+      <c r="C77" s="54" t="n"/>
+      <c r="D77" s="54" t="n"/>
       <c r="E77" s="5">
         <f>IF(OR(C77="",D77=""),"",(D77-C77)*1440)</f>
         <v/>
@@ -6345,7 +6420,7 @@
       <c r="R77" s="9" t="n"/>
     </row>
     <row r="78" ht="19.5" customHeight="1" s="26">
-      <c r="A78" s="46">
+      <c r="A78" s="53">
         <f>IF($B$3="","",$B$3+3)</f>
         <v/>
       </c>
@@ -6354,8 +6429,8 @@
           <t>목</t>
         </is>
       </c>
-      <c r="C78" s="47" t="n"/>
-      <c r="D78" s="47" t="n"/>
+      <c r="C78" s="54" t="n"/>
+      <c r="D78" s="54" t="n"/>
       <c r="E78" s="5">
         <f>IF(OR(C78="",D78=""),"",(D78-C78)*1440)</f>
         <v/>
@@ -6374,7 +6449,7 @@
       <c r="R78" s="9" t="n"/>
     </row>
     <row r="79" ht="19.5" customHeight="1" s="26">
-      <c r="A79" s="46">
+      <c r="A79" s="53">
         <f>IF($B$3="","",$B$3+3)</f>
         <v/>
       </c>
@@ -6383,8 +6458,8 @@
           <t>목</t>
         </is>
       </c>
-      <c r="C79" s="47" t="n"/>
-      <c r="D79" s="47" t="n"/>
+      <c r="C79" s="54" t="n"/>
+      <c r="D79" s="54" t="n"/>
       <c r="E79" s="5">
         <f>IF(OR(C79="",D79=""),"",(D79-C79)*1440)</f>
         <v/>
@@ -6403,7 +6478,7 @@
       <c r="R79" s="9" t="n"/>
     </row>
     <row r="80" ht="19.5" customHeight="1" s="26">
-      <c r="A80" s="46">
+      <c r="A80" s="53">
         <f>IF($B$3="","",$B$3+3)</f>
         <v/>
       </c>
@@ -6412,8 +6487,8 @@
           <t>목</t>
         </is>
       </c>
-      <c r="C80" s="47" t="n"/>
-      <c r="D80" s="47" t="n"/>
+      <c r="C80" s="54" t="n"/>
+      <c r="D80" s="54" t="n"/>
       <c r="E80" s="5">
         <f>IF(OR(C80="",D80=""),"",(D80-C80)*1440)</f>
         <v/>
@@ -6432,7 +6507,7 @@
       <c r="R80" s="9" t="n"/>
     </row>
     <row r="81" ht="19.5" customHeight="1" s="26">
-      <c r="A81" s="46">
+      <c r="A81" s="53">
         <f>IF($B$3="","",$B$3+3)</f>
         <v/>
       </c>
@@ -6441,8 +6516,8 @@
           <t>목</t>
         </is>
       </c>
-      <c r="C81" s="47" t="n"/>
-      <c r="D81" s="47" t="n"/>
+      <c r="C81" s="54" t="n"/>
+      <c r="D81" s="54" t="n"/>
       <c r="E81" s="5">
         <f>IF(OR(C81="",D81=""),"",(D81-C81)*1440)</f>
         <v/>
@@ -6461,7 +6536,7 @@
       <c r="R81" s="9" t="n"/>
     </row>
     <row r="82" ht="19.5" customHeight="1" s="26">
-      <c r="A82" s="46">
+      <c r="A82" s="53">
         <f>IF($B$3="","",$B$3+3)</f>
         <v/>
       </c>
@@ -6470,8 +6545,8 @@
           <t>목</t>
         </is>
       </c>
-      <c r="C82" s="47" t="n"/>
-      <c r="D82" s="47" t="n"/>
+      <c r="C82" s="54" t="n"/>
+      <c r="D82" s="54" t="n"/>
       <c r="E82" s="5">
         <f>IF(OR(C82="",D82=""),"",(D82-C82)*1440)</f>
         <v/>
@@ -6490,7 +6565,7 @@
       <c r="R82" s="9" t="n"/>
     </row>
     <row r="83" ht="19.5" customHeight="1" s="26">
-      <c r="A83" s="46">
+      <c r="A83" s="53">
         <f>IF($B$3="","",$B$3+3)</f>
         <v/>
       </c>
@@ -6499,8 +6574,8 @@
           <t>목</t>
         </is>
       </c>
-      <c r="C83" s="47" t="n"/>
-      <c r="D83" s="47" t="n"/>
+      <c r="C83" s="54" t="n"/>
+      <c r="D83" s="54" t="n"/>
       <c r="E83" s="5">
         <f>IF(OR(C83="",D83=""),"",(D83-C83)*1440)</f>
         <v/>
@@ -6519,7 +6594,7 @@
       <c r="R83" s="9" t="n"/>
     </row>
     <row r="84" ht="19.5" customHeight="1" s="26">
-      <c r="A84" s="46">
+      <c r="A84" s="53">
         <f>IF($B$3="","",$B$3+3)</f>
         <v/>
       </c>
@@ -6528,8 +6603,8 @@
           <t>목</t>
         </is>
       </c>
-      <c r="C84" s="47" t="n"/>
-      <c r="D84" s="47" t="n"/>
+      <c r="C84" s="54" t="n"/>
+      <c r="D84" s="54" t="n"/>
       <c r="E84" s="5">
         <f>IF(OR(C84="",D84=""),"",(D84-C84)*1440)</f>
         <v/>
@@ -6548,7 +6623,7 @@
       <c r="R84" s="9" t="n"/>
     </row>
     <row r="85" ht="19.5" customHeight="1" s="26">
-      <c r="A85" s="46">
+      <c r="A85" s="53">
         <f>IF($B$3="","",$B$3+3)</f>
         <v/>
       </c>
@@ -6557,8 +6632,8 @@
           <t>목(추가)</t>
         </is>
       </c>
-      <c r="C85" s="47" t="n"/>
-      <c r="D85" s="47" t="n"/>
+      <c r="C85" s="54" t="n"/>
+      <c r="D85" s="54" t="n"/>
       <c r="E85" s="5">
         <f>IF(OR(C85="",D85=""),"",(D85-C85)*1440)</f>
         <v/>
@@ -6577,7 +6652,7 @@
       <c r="R85" s="9" t="n"/>
     </row>
     <row r="86" ht="19.5" customHeight="1" s="26">
-      <c r="A86" s="46">
+      <c r="A86" s="53">
         <f>IF($B$3="","",$B$3+3)</f>
         <v/>
       </c>
@@ -6586,8 +6661,8 @@
           <t>목(추가)</t>
         </is>
       </c>
-      <c r="C86" s="47" t="n"/>
-      <c r="D86" s="47" t="n"/>
+      <c r="C86" s="54" t="n"/>
+      <c r="D86" s="54" t="n"/>
       <c r="E86" s="5">
         <f>IF(OR(C86="",D86=""),"",(D86-C86)*1440)</f>
         <v/>
@@ -6606,7 +6681,7 @@
       <c r="R86" s="9" t="n"/>
     </row>
     <row r="87" ht="19.5" customHeight="1" s="26">
-      <c r="A87" s="46">
+      <c r="A87" s="53">
         <f>IF($B$3="","",$B$3+4)</f>
         <v/>
       </c>
@@ -6615,10 +6690,10 @@
           <t>금</t>
         </is>
       </c>
-      <c r="C87" s="47" t="n">
+      <c r="C87" s="54" t="n">
         <v>0.375</v>
       </c>
-      <c r="D87" s="47" t="n">
+      <c r="D87" s="54" t="n">
         <v>0.4583333333333333</v>
       </c>
       <c r="E87" s="5">
@@ -6671,7 +6746,7 @@
       </c>
     </row>
     <row r="88" ht="19.5" customHeight="1" s="26">
-      <c r="A88" s="46">
+      <c r="A88" s="53">
         <f>IF($B$3="","",$B$3+4)</f>
         <v/>
       </c>
@@ -6680,10 +6755,10 @@
           <t>금</t>
         </is>
       </c>
-      <c r="C88" s="47" t="n">
+      <c r="C88" s="54" t="n">
         <v>0.4583333333333333</v>
       </c>
-      <c r="D88" s="47" t="n">
+      <c r="D88" s="54" t="n">
         <v>0.5</v>
       </c>
       <c r="E88" s="5">
@@ -6744,7 +6819,7 @@
       </c>
     </row>
     <row r="89" ht="19.5" customHeight="1" s="26">
-      <c r="A89" s="46">
+      <c r="A89" s="53">
         <f>IF($B$3="","",$B$3+4)</f>
         <v/>
       </c>
@@ -6753,10 +6828,10 @@
           <t>금</t>
         </is>
       </c>
-      <c r="C89" s="47" t="n">
+      <c r="C89" s="54" t="n">
         <v>0.5</v>
       </c>
-      <c r="D89" s="47" t="n">
+      <c r="D89" s="54" t="n">
         <v>0.5416666666666666</v>
       </c>
       <c r="E89" s="5">
@@ -6801,7 +6876,7 @@
       <c r="R89" s="9" t="n"/>
     </row>
     <row r="90" ht="19.5" customHeight="1" s="26">
-      <c r="A90" s="46">
+      <c r="A90" s="53">
         <f>IF($B$3="","",$B$3+4)</f>
         <v/>
       </c>
@@ -6810,10 +6885,10 @@
           <t>금</t>
         </is>
       </c>
-      <c r="C90" s="47" t="n">
+      <c r="C90" s="54" t="n">
         <v>0.5416666666666666</v>
       </c>
-      <c r="D90" s="47" t="n">
+      <c r="D90" s="54" t="n">
         <v>0.6041666666666666</v>
       </c>
       <c r="E90" s="5">
@@ -6874,7 +6949,7 @@
       </c>
     </row>
     <row r="91" ht="19.5" customHeight="1" s="26">
-      <c r="A91" s="46">
+      <c r="A91" s="53">
         <f>IF($B$3="","",$B$3+4)</f>
         <v/>
       </c>
@@ -6883,10 +6958,10 @@
           <t>금</t>
         </is>
       </c>
-      <c r="C91" s="47" t="n">
+      <c r="C91" s="54" t="n">
         <v>0.6041666666666666</v>
       </c>
-      <c r="D91" s="47" t="n">
+      <c r="D91" s="54" t="n">
         <v>0.625</v>
       </c>
       <c r="E91" s="5">
@@ -6939,7 +7014,7 @@
       </c>
     </row>
     <row r="92" ht="19.5" customHeight="1" s="26">
-      <c r="A92" s="46">
+      <c r="A92" s="53">
         <f>IF($B$3="","",$B$3+4)</f>
         <v/>
       </c>
@@ -6948,10 +7023,10 @@
           <t>금</t>
         </is>
       </c>
-      <c r="C92" s="47" t="n">
+      <c r="C92" s="54" t="n">
         <v>0.625</v>
       </c>
-      <c r="D92" s="47" t="n">
+      <c r="D92" s="54" t="n">
         <v>0.6875</v>
       </c>
       <c r="E92" s="5">
@@ -7012,7 +7087,7 @@
       </c>
     </row>
     <row r="93" ht="19.5" customHeight="1" s="26">
-      <c r="A93" s="46">
+      <c r="A93" s="53">
         <f>IF($B$3="","",$B$3+4)</f>
         <v/>
       </c>
@@ -7021,10 +7096,10 @@
           <t>금</t>
         </is>
       </c>
-      <c r="C93" s="47" t="n">
+      <c r="C93" s="54" t="n">
         <v>0.6875</v>
       </c>
-      <c r="D93" s="47" t="n">
+      <c r="D93" s="54" t="n">
         <v>0.75</v>
       </c>
       <c r="E93" s="5">
@@ -7073,7 +7148,7 @@
       </c>
     </row>
     <row r="94" ht="19.5" customHeight="1" s="26">
-      <c r="A94" s="46">
+      <c r="A94" s="53">
         <f>IF($B$3="","",$B$3+4)</f>
         <v/>
       </c>
@@ -7082,8 +7157,8 @@
           <t>금</t>
         </is>
       </c>
-      <c r="C94" s="47" t="n"/>
-      <c r="D94" s="47" t="n"/>
+      <c r="C94" s="54" t="n"/>
+      <c r="D94" s="54" t="n"/>
       <c r="E94" s="5">
         <f>IF(OR(C94="",D94=""),"",(D94-C94)*1440)</f>
         <v/>
@@ -7102,7 +7177,7 @@
       <c r="R94" s="9" t="n"/>
     </row>
     <row r="95" ht="19.5" customHeight="1" s="26">
-      <c r="A95" s="46">
+      <c r="A95" s="53">
         <f>IF($B$3="","",$B$3+4)</f>
         <v/>
       </c>
@@ -7111,8 +7186,8 @@
           <t>금</t>
         </is>
       </c>
-      <c r="C95" s="47" t="n"/>
-      <c r="D95" s="47" t="n"/>
+      <c r="C95" s="54" t="n"/>
+      <c r="D95" s="54" t="n"/>
       <c r="E95" s="5">
         <f>IF(OR(C95="",D95=""),"",(D95-C95)*1440)</f>
         <v/>
@@ -7131,7 +7206,7 @@
       <c r="R95" s="9" t="n"/>
     </row>
     <row r="96" ht="19.5" customHeight="1" s="26">
-      <c r="A96" s="46">
+      <c r="A96" s="53">
         <f>IF($B$3="","",$B$3+4)</f>
         <v/>
       </c>
@@ -7140,8 +7215,8 @@
           <t>금</t>
         </is>
       </c>
-      <c r="C96" s="47" t="n"/>
-      <c r="D96" s="47" t="n"/>
+      <c r="C96" s="54" t="n"/>
+      <c r="D96" s="54" t="n"/>
       <c r="E96" s="5">
         <f>IF(OR(C96="",D96=""),"",(D96-C96)*1440)</f>
         <v/>
@@ -7160,7 +7235,7 @@
       <c r="R96" s="9" t="n"/>
     </row>
     <row r="97" ht="19.5" customHeight="1" s="26">
-      <c r="A97" s="46">
+      <c r="A97" s="53">
         <f>IF($B$3="","",$B$3+4)</f>
         <v/>
       </c>
@@ -7169,8 +7244,8 @@
           <t>금</t>
         </is>
       </c>
-      <c r="C97" s="47" t="n"/>
-      <c r="D97" s="47" t="n"/>
+      <c r="C97" s="54" t="n"/>
+      <c r="D97" s="54" t="n"/>
       <c r="E97" s="5">
         <f>IF(OR(C97="",D97=""),"",(D97-C97)*1440)</f>
         <v/>
@@ -7189,7 +7264,7 @@
       <c r="R97" s="9" t="n"/>
     </row>
     <row r="98" ht="19.5" customHeight="1" s="26">
-      <c r="A98" s="46">
+      <c r="A98" s="53">
         <f>IF($B$3="","",$B$3+4)</f>
         <v/>
       </c>
@@ -7198,8 +7273,8 @@
           <t>금</t>
         </is>
       </c>
-      <c r="C98" s="47" t="n"/>
-      <c r="D98" s="47" t="n"/>
+      <c r="C98" s="54" t="n"/>
+      <c r="D98" s="54" t="n"/>
       <c r="E98" s="5">
         <f>IF(OR(C98="",D98=""),"",(D98-C98)*1440)</f>
         <v/>
@@ -7218,7 +7293,7 @@
       <c r="R98" s="9" t="n"/>
     </row>
     <row r="99" ht="19.5" customHeight="1" s="26">
-      <c r="A99" s="46">
+      <c r="A99" s="53">
         <f>IF($B$3="","",$B$3+4)</f>
         <v/>
       </c>
@@ -7227,8 +7302,8 @@
           <t>금</t>
         </is>
       </c>
-      <c r="C99" s="47" t="n"/>
-      <c r="D99" s="47" t="n"/>
+      <c r="C99" s="54" t="n"/>
+      <c r="D99" s="54" t="n"/>
       <c r="E99" s="5">
         <f>IF(OR(C99="",D99=""),"",(D99-C99)*1440)</f>
         <v/>
@@ -7247,7 +7322,7 @@
       <c r="R99" s="9" t="n"/>
     </row>
     <row r="100" ht="19.5" customHeight="1" s="26">
-      <c r="A100" s="46">
+      <c r="A100" s="53">
         <f>IF($B$3="","",$B$3+4)</f>
         <v/>
       </c>
@@ -7256,8 +7331,8 @@
           <t>금</t>
         </is>
       </c>
-      <c r="C100" s="47" t="n"/>
-      <c r="D100" s="47" t="n"/>
+      <c r="C100" s="54" t="n"/>
+      <c r="D100" s="54" t="n"/>
       <c r="E100" s="5">
         <f>IF(OR(C100="",D100=""),"",(D100-C100)*1440)</f>
         <v/>
@@ -7276,7 +7351,7 @@
       <c r="R100" s="9" t="n"/>
     </row>
     <row r="101" ht="19.5" customHeight="1" s="26">
-      <c r="A101" s="46">
+      <c r="A101" s="53">
         <f>IF($B$3="","",$B$3+4)</f>
         <v/>
       </c>
@@ -7285,8 +7360,8 @@
           <t>금</t>
         </is>
       </c>
-      <c r="C101" s="47" t="n"/>
-      <c r="D101" s="47" t="n"/>
+      <c r="C101" s="54" t="n"/>
+      <c r="D101" s="54" t="n"/>
       <c r="E101" s="5">
         <f>IF(OR(C101="",D101=""),"",(D101-C101)*1440)</f>
         <v/>
@@ -7305,7 +7380,7 @@
       <c r="R101" s="9" t="n"/>
     </row>
     <row r="102" ht="19.5" customHeight="1" s="26">
-      <c r="A102" s="46">
+      <c r="A102" s="53">
         <f>IF($B$3="","",$B$3+4)</f>
         <v/>
       </c>
@@ -7314,8 +7389,8 @@
           <t>금</t>
         </is>
       </c>
-      <c r="C102" s="47" t="n"/>
-      <c r="D102" s="47" t="n"/>
+      <c r="C102" s="54" t="n"/>
+      <c r="D102" s="54" t="n"/>
       <c r="E102" s="5">
         <f>IF(OR(C102="",D102=""),"",(D102-C102)*1440)</f>
         <v/>
@@ -7334,7 +7409,7 @@
       <c r="R102" s="9" t="n"/>
     </row>
     <row r="103" ht="19.5" customHeight="1" s="26">
-      <c r="A103" s="46">
+      <c r="A103" s="53">
         <f>IF($B$3="","",$B$3+4)</f>
         <v/>
       </c>
@@ -7343,8 +7418,8 @@
           <t>금</t>
         </is>
       </c>
-      <c r="C103" s="47" t="n"/>
-      <c r="D103" s="47" t="n"/>
+      <c r="C103" s="54" t="n"/>
+      <c r="D103" s="54" t="n"/>
       <c r="E103" s="5">
         <f>IF(OR(C103="",D103=""),"",(D103-C103)*1440)</f>
         <v/>
@@ -7363,7 +7438,7 @@
       <c r="R103" s="9" t="n"/>
     </row>
     <row r="104" ht="19.5" customHeight="1" s="26">
-      <c r="A104" s="46">
+      <c r="A104" s="53">
         <f>IF($B$3="","",$B$3+4)</f>
         <v/>
       </c>
@@ -7372,8 +7447,8 @@
           <t>금</t>
         </is>
       </c>
-      <c r="C104" s="47" t="n"/>
-      <c r="D104" s="47" t="n"/>
+      <c r="C104" s="54" t="n"/>
+      <c r="D104" s="54" t="n"/>
       <c r="E104" s="5">
         <f>IF(OR(C104="",D104=""),"",(D104-C104)*1440)</f>
         <v/>
@@ -7392,7 +7467,7 @@
       <c r="R104" s="9" t="n"/>
     </row>
     <row r="105" ht="19.5" customHeight="1" s="26">
-      <c r="A105" s="46">
+      <c r="A105" s="53">
         <f>IF($B$3="","",$B$3+4)</f>
         <v/>
       </c>
@@ -7401,8 +7476,8 @@
           <t>금(추가)</t>
         </is>
       </c>
-      <c r="C105" s="47" t="n"/>
-      <c r="D105" s="47" t="n"/>
+      <c r="C105" s="54" t="n"/>
+      <c r="D105" s="54" t="n"/>
       <c r="E105" s="5">
         <f>IF(OR(C105="",D105=""),"",(D105-C105)*1440)</f>
         <v/>
@@ -7421,7 +7496,7 @@
       <c r="R105" s="9" t="n"/>
     </row>
     <row r="106" ht="19.5" customHeight="1" s="26">
-      <c r="A106" s="46">
+      <c r="A106" s="53">
         <f>IF($B$3="","",$B$3+4)</f>
         <v/>
       </c>
@@ -7430,8 +7505,8 @@
           <t>금(추가)</t>
         </is>
       </c>
-      <c r="C106" s="47" t="n"/>
-      <c r="D106" s="47" t="n"/>
+      <c r="C106" s="54" t="n"/>
+      <c r="D106" s="54" t="n"/>
       <c r="E106" s="5">
         <f>IF(OR(C106="",D106=""),"",(D106-C106)*1440)</f>
         <v/>
@@ -7727,7 +7802,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D3" s="48" t="n">
+      <c r="D3" s="55" t="n">
         <v>46244</v>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -7735,10 +7810,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="F3" s="49" t="n">
+      <c r="F3" s="56" t="n">
         <v>0.375</v>
       </c>
-      <c r="G3" s="49" t="n">
+      <c r="G3" s="56" t="n">
         <v>0.3958333333333333</v>
       </c>
       <c r="H3" s="18">
@@ -7819,7 +7894,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D4" s="50" t="n">
+      <c r="D4" s="57" t="n">
         <v>46244</v>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -7827,10 +7902,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="F4" s="51" t="n">
+      <c r="F4" s="58" t="n">
         <v>0.3958333333333333</v>
       </c>
-      <c r="G4" s="51" t="n">
+      <c r="G4" s="58" t="n">
         <v>0.4166666666666667</v>
       </c>
       <c r="H4" s="7">
@@ -7906,7 +7981,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D5" s="50" t="n">
+      <c r="D5" s="57" t="n">
         <v>46244</v>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -7914,10 +7989,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="F5" s="51" t="n">
+      <c r="F5" s="58" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="G5" s="51" t="n">
+      <c r="G5" s="58" t="n">
         <v>0.4583333333333333</v>
       </c>
       <c r="H5" s="7">
@@ -7997,7 +8072,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D6" s="50" t="n">
+      <c r="D6" s="57" t="n">
         <v>46244</v>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -8005,10 +8080,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="F6" s="51" t="n">
+      <c r="F6" s="58" t="n">
         <v>0.4583333333333333</v>
       </c>
-      <c r="G6" s="51" t="n">
+      <c r="G6" s="58" t="n">
         <v>0.4791666666666667</v>
       </c>
       <c r="H6" s="7">
@@ -8093,7 +8168,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D7" s="50" t="n">
+      <c r="D7" s="57" t="n">
         <v>46244</v>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -8101,10 +8176,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="F7" s="51" t="n">
+      <c r="F7" s="58" t="n">
         <v>0.4791666666666667</v>
       </c>
-      <c r="G7" s="51" t="n">
+      <c r="G7" s="58" t="n">
         <v>0.5</v>
       </c>
       <c r="H7" s="7">
@@ -8189,7 +8264,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D8" s="50" t="n">
+      <c r="D8" s="57" t="n">
         <v>46244</v>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -8197,10 +8272,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="F8" s="51" t="n">
+      <c r="F8" s="58" t="n">
         <v>0.5</v>
       </c>
-      <c r="G8" s="51" t="n">
+      <c r="G8" s="58" t="n">
         <v>0.5416666666666666</v>
       </c>
       <c r="H8" s="7">
@@ -8260,7 +8335,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D9" s="50" t="n">
+      <c r="D9" s="57" t="n">
         <v>46244</v>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -8268,10 +8343,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="F9" s="51" t="n">
+      <c r="F9" s="58" t="n">
         <v>0.5416666666666666</v>
       </c>
-      <c r="G9" s="51" t="n">
+      <c r="G9" s="58" t="n">
         <v>0.5625</v>
       </c>
       <c r="H9" s="7">
@@ -8356,7 +8431,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D10" s="50" t="n">
+      <c r="D10" s="57" t="n">
         <v>46244</v>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -8364,10 +8439,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="F10" s="51" t="n">
+      <c r="F10" s="58" t="n">
         <v>0.5625</v>
       </c>
-      <c r="G10" s="51" t="n">
+      <c r="G10" s="58" t="n">
         <v>0.5833333333333334</v>
       </c>
       <c r="H10" s="7">
@@ -8452,7 +8527,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D11" s="50" t="n">
+      <c r="D11" s="57" t="n">
         <v>46244</v>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -8460,10 +8535,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="F11" s="51" t="n">
+      <c r="F11" s="58" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G11" s="51" t="n">
+      <c r="G11" s="58" t="n">
         <v>0.625</v>
       </c>
       <c r="H11" s="7">
@@ -8548,7 +8623,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D12" s="50" t="n">
+      <c r="D12" s="57" t="n">
         <v>46244</v>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -8556,10 +8631,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="F12" s="51" t="n">
+      <c r="F12" s="58" t="n">
         <v>0.625</v>
       </c>
-      <c r="G12" s="51" t="n">
+      <c r="G12" s="58" t="n">
         <v>0.6458333333333334</v>
       </c>
       <c r="H12" s="7">
@@ -8643,7 +8718,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D13" s="50" t="n">
+      <c r="D13" s="57" t="n">
         <v>46244</v>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -8651,10 +8726,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="F13" s="51" t="n">
+      <c r="F13" s="58" t="n">
         <v>0.6458333333333334</v>
       </c>
-      <c r="G13" s="51" t="n">
+      <c r="G13" s="58" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="H13" s="7">
@@ -8743,7 +8818,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D14" s="50" t="n">
+      <c r="D14" s="57" t="n">
         <v>46244</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -8751,10 +8826,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="F14" s="51" t="n">
+      <c r="F14" s="58" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="G14" s="51" t="n">
+      <c r="G14" s="58" t="n">
         <v>0.7083333333333334</v>
       </c>
       <c r="H14" s="7">
@@ -8834,7 +8909,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D15" s="50" t="n">
+      <c r="D15" s="57" t="n">
         <v>46244</v>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -8842,10 +8917,10 @@
           <t>월</t>
         </is>
       </c>
-      <c r="F15" s="51" t="n">
+      <c r="F15" s="58" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="G15" s="51" t="n">
+      <c r="G15" s="58" t="n">
         <v>0.75</v>
       </c>
       <c r="H15" s="7">
@@ -8934,7 +9009,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D16" s="50" t="n">
+      <c r="D16" s="57" t="n">
         <v>46245</v>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -8942,10 +9017,10 @@
           <t>화</t>
         </is>
       </c>
-      <c r="F16" s="51" t="n">
+      <c r="F16" s="58" t="n">
         <v>0.375</v>
       </c>
-      <c r="G16" s="51" t="n">
+      <c r="G16" s="58" t="n">
         <v>0.3958333333333333</v>
       </c>
       <c r="H16" s="7">
@@ -9026,7 +9101,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D17" s="50" t="n">
+      <c r="D17" s="57" t="n">
         <v>46245</v>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -9034,10 +9109,10 @@
           <t>화</t>
         </is>
       </c>
-      <c r="F17" s="51" t="n">
+      <c r="F17" s="58" t="n">
         <v>0.3958333333333333</v>
       </c>
-      <c r="G17" s="51" t="n">
+      <c r="G17" s="58" t="n">
         <v>0.4583333333333333</v>
       </c>
       <c r="H17" s="7">
@@ -9122,7 +9197,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D18" s="50" t="n">
+      <c r="D18" s="57" t="n">
         <v>46245</v>
       </c>
       <c r="E18" s="8" t="inlineStr">
@@ -9130,10 +9205,10 @@
           <t>화</t>
         </is>
       </c>
-      <c r="F18" s="51" t="n">
+      <c r="F18" s="58" t="n">
         <v>0.4583333333333333</v>
       </c>
-      <c r="G18" s="51" t="n">
+      <c r="G18" s="58" t="n">
         <v>0.5</v>
       </c>
       <c r="H18" s="7">
@@ -9142,27 +9217,27 @@
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>마케팅·광고운영</t>
+          <t>콘텐츠제작</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>MKT-04 인플루언서·체험단 섭외/관리</t>
+          <t>CNT-02 촬영 기획·진행</t>
         </is>
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>채림님 인플루언서 협업마케팅 진행방향 안내 및 진행안 컨펌</t>
+          <t>제품시공 촬영 — 테스트촬영 및 대여 탐색, 채림님께 인수인계하여 진행 요청 (아파트·공장·일반주택 대상)</t>
         </is>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>POUR스토어</t>
+          <t>시공 제품 / 아파트·공장·일반주택</t>
         </is>
       </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
-          <t>레뷰, 리뷰플레이스</t>
+          <t>CRM센터-POUR OS(업무보드)</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -9175,19 +9250,15 @@
           <t>양채림</t>
         </is>
       </c>
-      <c r="P18" s="8" t="inlineStr">
-        <is>
-          <t>인플루언서</t>
-        </is>
-      </c>
+      <c r="P18" s="8" t="n"/>
       <c r="Q18" s="8" t="inlineStr">
         <is>
-          <t>협업 진행안 컨펌</t>
+          <t>테스트 촬영본, 촬영 진행 요청서</t>
         </is>
       </c>
       <c r="R18" s="8" t="inlineStr">
         <is>
-          <t>주 1회</t>
+          <t>1회성</t>
         </is>
       </c>
       <c r="S18" s="8" t="inlineStr">
@@ -9202,7 +9273,7 @@
       </c>
       <c r="U18" s="8" t="inlineStr">
         <is>
-          <t>인플루언서 협업 진행 기준(가이드) 문서화 후 위임</t>
+          <t>건물유형별 시공 촬영 가이드·촬영 자산 라이브러리 공용화</t>
         </is>
       </c>
     </row>
@@ -9222,7 +9293,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D19" s="50" t="n">
+      <c r="D19" s="57" t="n">
         <v>46245</v>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -9230,10 +9301,10 @@
           <t>화</t>
         </is>
       </c>
-      <c r="F19" s="51" t="n">
+      <c r="F19" s="58" t="n">
         <v>0.5</v>
       </c>
-      <c r="G19" s="51" t="n">
+      <c r="G19" s="58" t="n">
         <v>0.5416666666666666</v>
       </c>
       <c r="H19" s="7">
@@ -9293,7 +9364,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D20" s="50" t="n">
+      <c r="D20" s="57" t="n">
         <v>46245</v>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -9301,10 +9372,10 @@
           <t>화</t>
         </is>
       </c>
-      <c r="F20" s="51" t="n">
+      <c r="F20" s="58" t="n">
         <v>0.5416666666666666</v>
       </c>
-      <c r="G20" s="51" t="n">
+      <c r="G20" s="58" t="n">
         <v>0.5833333333333334</v>
       </c>
       <c r="H20" s="7">
@@ -9313,48 +9384,52 @@
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>사내시스템·자동화</t>
+          <t>마케팅·광고운영</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>SYS-01 사내 시스템·앱 기획/개선 요청</t>
+          <t>MKT-04 인플루언서·체험단 섭외/관리</t>
         </is>
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>소싱앱 UX/UI 개선 — 정하님 추가 고도화 건 2차 피드백</t>
+          <t>채림님 인플루언서 협업마케팅 진행방향 안내 및 진행안 컨펌</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>소싱앱</t>
+          <t>POUR스토어</t>
         </is>
       </c>
       <c r="M20" s="8" t="inlineStr">
         <is>
-          <t>소싱앱</t>
+          <t>레뷰, 리뷰플레이스</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>소싱 관리 · 모여라딜 (moyeoradeal-sourcing.pages.dev)</t>
+          <t>https://pourstorecrm.web.app/pour-os</t>
         </is>
       </c>
       <c r="O20" s="8" t="inlineStr">
         <is>
-          <t>정하</t>
-        </is>
-      </c>
-      <c r="P20" s="8" t="n"/>
+          <t>양채림</t>
+        </is>
+      </c>
+      <c r="P20" s="8" t="inlineStr">
+        <is>
+          <t>인플루언서</t>
+        </is>
+      </c>
       <c r="Q20" s="8" t="inlineStr">
         <is>
-          <t>UX/UI 2차 피드백</t>
+          <t>협업 진행안 컨펌</t>
         </is>
       </c>
       <c r="R20" s="8" t="inlineStr">
         <is>
-          <t>주 2~3회</t>
+          <t>주 1회</t>
         </is>
       </c>
       <c r="S20" s="8" t="inlineStr">
@@ -9364,12 +9439,12 @@
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>모름</t>
+          <t>아마도 중복</t>
         </is>
       </c>
       <c r="U20" s="8" t="inlineStr">
         <is>
-          <t>개선 요청·피드백 이력을 앱 내 이슈보드로 관리</t>
+          <t>인플루언서 협업 진행 기준(가이드) 문서화 후 위임</t>
         </is>
       </c>
     </row>
@@ -9389,7 +9464,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D21" s="50" t="n">
+      <c r="D21" s="57" t="n">
         <v>46245</v>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -9397,10 +9472,10 @@
           <t>화</t>
         </is>
       </c>
-      <c r="F21" s="51" t="n">
+      <c r="F21" s="58" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="G21" s="51" t="n">
+      <c r="G21" s="58" t="n">
         <v>0.625</v>
       </c>
       <c r="H21" s="7">
@@ -9409,35 +9484,48 @@
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>상품기획·소싱</t>
+          <t>사내시스템·자동화</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>PLN-01 신상품 아이템 발굴/시장조사</t>
+          <t>SYS-01 사내 시스템·앱 기획/개선 요청</t>
         </is>
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>본품 외 부자재·안전용품 등 판매 세팅 검토 — 우선순위 재조정으로 보류</t>
+          <t>소싱앱 UX/UI 개선 — 정하님 추가 고도화 건 2차 피드백</t>
         </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>부자재·안전용품</t>
-        </is>
-      </c>
-      <c r="M21" s="8" t="n"/>
-      <c r="O21" s="8" t="n"/>
+          <t>소싱앱</t>
+        </is>
+      </c>
+      <c r="M21" s="8" t="inlineStr">
+        <is>
+          <t>소싱앱</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>소싱 관리 · 모여라딜 (moyeoradeal-sourcing.pages.dev)</t>
+        </is>
+      </c>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>정하</t>
+        </is>
+      </c>
       <c r="P21" s="8" t="n"/>
       <c r="Q21" s="8" t="inlineStr">
         <is>
-          <t>판매 세팅 검토안(보류)</t>
+          <t>UX/UI 2차 피드백</t>
         </is>
       </c>
       <c r="R21" s="8" t="inlineStr">
         <is>
-          <t>분기/비정기</t>
+          <t>주 2~3회</t>
         </is>
       </c>
       <c r="S21" s="8" t="inlineStr">
@@ -9447,12 +9535,12 @@
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
+          <t>모름</t>
         </is>
       </c>
       <c r="U21" s="8" t="inlineStr">
         <is>
-          <t>부자재 카테고리 소싱 기준 정립 후 일괄 세팅</t>
+          <t>개선 요청·피드백 이력을 앱 내 이슈보드로 관리</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9560,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D22" s="50" t="n">
+      <c r="D22" s="57" t="n">
         <v>46245</v>
       </c>
       <c r="E22" s="8" t="inlineStr">
@@ -9480,11 +9568,11 @@
           <t>화</t>
         </is>
       </c>
-      <c r="F22" s="51" t="n">
+      <c r="F22" s="58" t="n">
         <v>0.625</v>
       </c>
-      <c r="G22" s="51" t="n">
-        <v>0.6875</v>
+      <c r="G22" s="58" t="n">
+        <v>0.6458333333333334</v>
       </c>
       <c r="H22" s="7">
         <f>IF(OR(F22="",G22=""),"",(G22-F22)*1440)</f>
@@ -9492,44 +9580,35 @@
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>데이터·정산</t>
+          <t>상품기획·소싱</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>DAT-04 리포트·대시보드 작성</t>
+          <t>PLN-01 신상품 아이템 발굴/시장조사</t>
         </is>
       </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
-          <t>POUR스토어 단가·공헌이익·손익계산 대시보드 제작 — 진행중(전주 이월)</t>
+          <t>본품 외 부자재·안전용품 등 판매 세팅 검토 — 우선순위 재조정으로 보류</t>
         </is>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>POUR스토어</t>
-        </is>
-      </c>
-      <c r="M22" s="8" t="inlineStr">
-        <is>
-          <t>단가 대시보드, 엑셀</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>POUR스토어 가격·마진 통합 대시보드 (pour-construction-form.pages.dev)</t>
-        </is>
-      </c>
+          <t>부자재·안전용품</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="n"/>
       <c r="O22" s="8" t="n"/>
       <c r="P22" s="8" t="n"/>
       <c r="Q22" s="8" t="inlineStr">
         <is>
-          <t>단가·공헌이익·손익 대시보드</t>
+          <t>판매 세팅 검토안(보류)</t>
         </is>
       </c>
       <c r="R22" s="8" t="inlineStr">
         <is>
-          <t>주 2~3회</t>
+          <t>분기/비정기</t>
         </is>
       </c>
       <c r="S22" s="8" t="inlineStr">
@@ -9544,7 +9623,7 @@
       </c>
       <c r="U22" s="8" t="inlineStr">
         <is>
-          <t>채널 수수료·원가 데이터 자동 연동으로 수기 입력 제거</t>
+          <t>부자재 카테고리 소싱 기준 정립 후 일괄 세팅</t>
         </is>
       </c>
     </row>
@@ -9564,7 +9643,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D23" s="50" t="n">
+      <c r="D23" s="57" t="n">
         <v>46245</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -9572,11 +9651,11 @@
           <t>화</t>
         </is>
       </c>
-      <c r="F23" s="51" t="n">
+      <c r="F23" s="58" t="n">
+        <v>0.6458333333333334</v>
+      </c>
+      <c r="G23" s="58" t="n">
         <v>0.6875</v>
-      </c>
-      <c r="G23" s="51" t="n">
-        <v>0.75</v>
       </c>
       <c r="H23" s="7">
         <f>IF(OR(F23="",G23=""),"",(G23-F23)*1440)</f>
@@ -9584,58 +9663,59 @@
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>제조·생산관리</t>
+          <t>데이터·정산</t>
         </is>
       </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>MFG-08 MSDS·라벨 등 제품 표시사항 제작</t>
+          <t>DAT-04 리포트·대시보드 작성</t>
         </is>
       </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>신제품 코트재 MSDS 컬러별 31개 제작 — 진행중</t>
+          <t>POUR스토어 단가·공헌이익·손익계산 대시보드 제작 — 진행중(전주 이월)</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>코트재 신제품 31색</t>
+          <t>POUR스토어</t>
         </is>
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
-          <t>챗지피티</t>
+          <t>단가 대시보드, 엑셀</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>POUR스토어 가격·마진 통합 대시보드 (pour-construction-form.pages.dev)</t>
         </is>
       </c>
       <c r="O23" s="8" t="n"/>
-      <c r="P23" s="8" t="inlineStr">
-        <is>
-          <t>세이고, 쿠팡물류센터</t>
-        </is>
-      </c>
+      <c r="P23" s="8" t="n"/>
       <c r="Q23" s="8" t="inlineStr">
         <is>
-          <t>MSDS 31종</t>
+          <t>단가·공헌이익·손익 대시보드</t>
         </is>
       </c>
       <c r="R23" s="8" t="inlineStr">
         <is>
-          <t>1회성</t>
+          <t>주 2~3회</t>
         </is>
       </c>
       <c r="S23" s="8" t="inlineStr">
         <is>
-          <t>반정형</t>
+          <t>비정형(판단 필요)</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>아니오 - 우리팀 고유</t>
+          <t>아마도 중복</t>
         </is>
       </c>
       <c r="U23" s="8" t="inlineStr">
         <is>
-          <t>품목·색상 데이터 연동으로 MSDS 서식 자동 생성</t>
+          <t>채널 수수료·원가 데이터 자동 연동으로 수기 입력 제거</t>
         </is>
       </c>
     </row>
@@ -9655,19 +9735,19 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D24" s="50" t="n">
-        <v>46246</v>
+      <c r="D24" s="57" t="n">
+        <v>46245</v>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>수</t>
-        </is>
-      </c>
-      <c r="F24" s="51" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="G24" s="51" t="n">
-        <v>0.3958333333333333</v>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="F24" s="58" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="G24" s="58" t="n">
+        <v>0.75</v>
       </c>
       <c r="H24" s="7">
         <f>IF(OR(F24="",G24=""),"",(G24-F24)*1440)</f>
@@ -9675,59 +9755,58 @@
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>기타·행정</t>
+          <t>제조·생산관리</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>ETC-01 메일·메신저 확인 및 회신</t>
+          <t>MFG-08 MSDS·라벨 등 제품 표시사항 제작</t>
         </is>
       </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>출근 후 메일·메신저·업무보드 확인 및 회신</t>
+          <t>신제품 코트재 MSDS 컬러별 31개 제작 — 진행중</t>
         </is>
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>전사</t>
+          <t>코트재 신제품 31색</t>
         </is>
       </c>
       <c r="M24" s="8" t="inlineStr">
         <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
+          <t>챗지피티</t>
         </is>
       </c>
       <c r="O24" s="8" t="n"/>
-      <c r="P24" s="8" t="n"/>
+      <c r="P24" s="8" t="inlineStr">
+        <is>
+          <t>세이고, 쿠팡물류센터</t>
+        </is>
+      </c>
       <c r="Q24" s="8" t="inlineStr">
         <is>
-          <t>회신 처리</t>
+          <t>MSDS 31종</t>
         </is>
       </c>
       <c r="R24" s="8" t="inlineStr">
         <is>
-          <t>매일</t>
+          <t>1회성</t>
         </is>
       </c>
       <c r="S24" s="8" t="inlineStr">
         <is>
-          <t>정형(매뉴얼화 가능)</t>
+          <t>반정형</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>예 - 확실히 중복</t>
+          <t>아니오 - 우리팀 고유</t>
         </is>
       </c>
       <c r="U24" s="8" t="inlineStr">
         <is>
-          <t>팀별 요청·공지를 업무보드 알림 하나로 일원화</t>
+          <t>품목·색상 데이터 연동으로 MSDS 서식 자동 생성</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9826,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D25" s="50" t="n">
+      <c r="D25" s="57" t="n">
         <v>46246</v>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -9755,11 +9834,11 @@
           <t>수</t>
         </is>
       </c>
-      <c r="F25" s="51" t="n">
+      <c r="F25" s="58" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="G25" s="58" t="n">
         <v>0.3958333333333333</v>
-      </c>
-      <c r="G25" s="51" t="n">
-        <v>0.4375</v>
       </c>
       <c r="H25" s="7">
         <f>IF(OR(F25="",G25=""),"",(G25-F25)*1440)</f>
@@ -9767,22 +9846,22 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>파트너·대리점관리</t>
+          <t>기타·행정</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>PTR-01 대리점·파트너사 방문·미팅</t>
+          <t>ETC-01 메일·메신저 확인 및 회신</t>
         </is>
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
-          <t>부산 대리점 방문 준비 — 촬영물품 및 미팅·인터뷰 질문지 최종 확인</t>
+          <t>출근 후 메일·메신저·업무보드 확인 및 회신</t>
         </is>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>대리점(가나랜드·겸남지사)</t>
+          <t>전사</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
@@ -9795,39 +9874,31 @@
           <t>https://pourstorecrm.web.app/pour-os</t>
         </is>
       </c>
-      <c r="O25" s="8" t="inlineStr">
-        <is>
-          <t>이란</t>
-        </is>
-      </c>
-      <c r="P25" s="8" t="inlineStr">
-        <is>
-          <t>가나랜드, 겸남지사</t>
-        </is>
-      </c>
+      <c r="O25" s="8" t="n"/>
+      <c r="P25" s="8" t="n"/>
       <c r="Q25" s="8" t="inlineStr">
         <is>
-          <t>방문 준비 체크리스트</t>
+          <t>회신 처리</t>
         </is>
       </c>
       <c r="R25" s="8" t="inlineStr">
         <is>
-          <t>분기/비정기</t>
+          <t>매일</t>
         </is>
       </c>
       <c r="S25" s="8" t="inlineStr">
         <is>
-          <t>반정형</t>
+          <t>정형(매뉴얼화 가능)</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>모름</t>
+          <t>예 - 확실히 중복</t>
         </is>
       </c>
       <c r="U25" s="8" t="inlineStr">
         <is>
-          <t>대리점 방문 준비 체크리스트 표준화</t>
+          <t>팀별 요청·공지를 업무보드 알림 하나로 일원화</t>
         </is>
       </c>
     </row>
@@ -9847,7 +9918,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D26" s="50" t="n">
+      <c r="D26" s="57" t="n">
         <v>46246</v>
       </c>
       <c r="E26" s="8" t="inlineStr">
@@ -9855,11 +9926,11 @@
           <t>수</t>
         </is>
       </c>
-      <c r="F26" s="51" t="n">
+      <c r="F26" s="58" t="n">
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="G26" s="58" t="n">
         <v>0.4375</v>
-      </c>
-      <c r="G26" s="51" t="n">
-        <v>0.4791666666666667</v>
       </c>
       <c r="H26" s="7">
         <f>IF(OR(F26="",G26=""),"",(G26-F26)*1440)</f>
@@ -9867,22 +9938,22 @@
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>마케팅·광고운영</t>
+          <t>파트너·대리점관리</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>MKT-05 프로모션·기획전 기획</t>
+          <t>PTR-01 대리점·파트너사 방문·미팅</t>
         </is>
       </c>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>스토어 8~10월 프로모션 기획안 검토 및 피드백(민지님)</t>
+          <t>부산 대리점 방문 준비 — 촬영물품 및 미팅·인터뷰 질문지 최종 확인</t>
         </is>
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>POUR스토어</t>
+          <t>대리점(가나랜드·겸남지사)</t>
         </is>
       </c>
       <c r="M26" s="8" t="inlineStr">
@@ -9897,18 +9968,22 @@
       </c>
       <c r="O26" s="8" t="inlineStr">
         <is>
-          <t>김민지</t>
-        </is>
-      </c>
-      <c r="P26" s="8" t="n"/>
+          <t>이란</t>
+        </is>
+      </c>
+      <c r="P26" s="8" t="inlineStr">
+        <is>
+          <t>가나랜드, 겸남지사</t>
+        </is>
+      </c>
       <c r="Q26" s="8" t="inlineStr">
         <is>
-          <t>프로모션 기획 피드백</t>
+          <t>방문 준비 체크리스트</t>
         </is>
       </c>
       <c r="R26" s="8" t="inlineStr">
         <is>
-          <t>월 1회</t>
+          <t>분기/비정기</t>
         </is>
       </c>
       <c r="S26" s="8" t="inlineStr">
@@ -9918,12 +9993,12 @@
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
+          <t>모름</t>
         </is>
       </c>
       <c r="U26" s="8" t="inlineStr">
         <is>
-          <t>본부 공용 프로모션 캘린더로 3팀 일정·중복 방지</t>
+          <t>대리점 방문 준비 체크리스트 표준화</t>
         </is>
       </c>
     </row>
@@ -9943,7 +10018,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D27" s="50" t="n">
+      <c r="D27" s="57" t="n">
         <v>46246</v>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -9951,11 +10026,11 @@
           <t>수</t>
         </is>
       </c>
-      <c r="F27" s="51" t="n">
+      <c r="F27" s="58" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="G27" s="58" t="n">
         <v>0.4791666666666667</v>
-      </c>
-      <c r="G27" s="51" t="n">
-        <v>0.5</v>
       </c>
       <c r="H27" s="7">
         <f>IF(OR(F27="",G27=""),"",(G27-F27)*1440)</f>
@@ -9968,49 +10043,58 @@
       </c>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>MKT-02 광고 성과 모니터링·최적화</t>
+          <t>MKT-05 프로모션·기획전 기획</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>신제품(철재페인트) 키워드광고 상위노출 확인</t>
+          <t>스토어 8~10월 프로모션 기획안 검토 및 피드백(민지님)</t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t>신제품 철재페인트 / 네이버</t>
+          <t>POUR스토어</t>
         </is>
       </c>
       <c r="M27" s="8" t="inlineStr">
         <is>
-          <t>네이버 검색, 검색광고 관리자</t>
-        </is>
-      </c>
-      <c r="O27" s="8" t="n"/>
+          <t>CRM센터-POUR OS(업무보드)</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>https://pourstorecrm.web.app/pour-os</t>
+        </is>
+      </c>
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
       <c r="P27" s="8" t="n"/>
       <c r="Q27" s="8" t="inlineStr">
         <is>
-          <t>노출 순위 점검 메모</t>
+          <t>프로모션 기획 피드백</t>
         </is>
       </c>
       <c r="R27" s="8" t="inlineStr">
         <is>
-          <t>주 2~3회</t>
+          <t>월 1회</t>
         </is>
       </c>
       <c r="S27" s="8" t="inlineStr">
         <is>
-          <t>정형(매뉴얼화 가능)</t>
+          <t>반정형</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>예 - 확실히 중복</t>
+          <t>아마도 중복</t>
         </is>
       </c>
       <c r="U27" s="8" t="inlineStr">
         <is>
-          <t>키워드 순위 자동 추적 리포트로 대체</t>
+          <t>본부 공용 프로모션 캘린더로 3팀 일정·중복 방지</t>
         </is>
       </c>
     </row>
@@ -10030,7 +10114,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D28" s="50" t="n">
+      <c r="D28" s="57" t="n">
         <v>46246</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
@@ -10038,11 +10122,11 @@
           <t>수</t>
         </is>
       </c>
-      <c r="F28" s="51" t="n">
+      <c r="F28" s="58" t="n">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="G28" s="58" t="n">
         <v>0.5</v>
-      </c>
-      <c r="G28" s="51" t="n">
-        <v>0.5416666666666666</v>
       </c>
       <c r="H28" s="7">
         <f>IF(OR(F28="",G28=""),"",(G28-F28)*1440)</f>
@@ -10050,27 +10134,39 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>기타·행정</t>
+          <t>마케팅·광고운영</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>ETC-05 휴게·점심</t>
+          <t>MKT-02 광고 성과 모니터링·최적화</t>
         </is>
       </c>
       <c r="K28" s="8" t="inlineStr">
         <is>
-          <t>점심 및 휴게</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="n"/>
-      <c r="M28" s="8" t="n"/>
+          <t>신제품(철재페인트) 키워드광고 상위노출 확인</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>신제품 철재페인트 / 네이버</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t>네이버 검색, 검색광고 관리자</t>
+        </is>
+      </c>
       <c r="O28" s="8" t="n"/>
       <c r="P28" s="8" t="n"/>
-      <c r="Q28" s="8" t="n"/>
+      <c r="Q28" s="8" t="inlineStr">
+        <is>
+          <t>노출 순위 점검 메모</t>
+        </is>
+      </c>
       <c r="R28" s="8" t="inlineStr">
         <is>
-          <t>매일</t>
+          <t>주 2~3회</t>
         </is>
       </c>
       <c r="S28" s="8" t="inlineStr">
@@ -10083,7 +10179,11 @@
           <t>예 - 확실히 중복</t>
         </is>
       </c>
-      <c r="U28" s="8" t="n"/>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>키워드 순위 자동 추적 리포트로 대체</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -10101,7 +10201,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D29" s="50" t="n">
+      <c r="D29" s="57" t="n">
         <v>46246</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -10109,11 +10209,11 @@
           <t>수</t>
         </is>
       </c>
-      <c r="F29" s="51" t="n">
+      <c r="F29" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G29" s="58" t="n">
         <v>0.5416666666666666</v>
-      </c>
-      <c r="G29" s="51" t="n">
-        <v>0.5833333333333334</v>
       </c>
       <c r="H29" s="7">
         <f>IF(OR(F29="",G29=""),"",(G29-F29)*1440)</f>
@@ -10121,65 +10221,40 @@
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>기획·보고·회의</t>
+          <t>기타·행정</t>
         </is>
       </c>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>MGT-06 팀원 업무·산출물 검토·피드백</t>
+          <t>ETC-05 휴게·점심</t>
         </is>
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>AX+업무리스트 보고서 검토 및 피드백(정하님)</t>
-        </is>
-      </c>
-      <c r="L29" s="8" t="inlineStr">
-        <is>
-          <t>팀 업무관리</t>
-        </is>
-      </c>
-      <c r="M29" s="8" t="inlineStr">
-        <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
-        </is>
-      </c>
-      <c r="O29" s="8" t="inlineStr">
-        <is>
-          <t>정하</t>
-        </is>
-      </c>
+          <t>점심 및 휴게</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="n"/>
+      <c r="M29" s="8" t="n"/>
+      <c r="O29" s="8" t="n"/>
       <c r="P29" s="8" t="n"/>
-      <c r="Q29" s="8" t="inlineStr">
-        <is>
-          <t>검토 피드백</t>
-        </is>
-      </c>
+      <c r="Q29" s="8" t="n"/>
       <c r="R29" s="8" t="inlineStr">
         <is>
-          <t>주 1회</t>
+          <t>매일</t>
         </is>
       </c>
       <c r="S29" s="8" t="inlineStr">
         <is>
-          <t>비정형(판단 필요)</t>
+          <t>정형(매뉴얼화 가능)</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>업무보드 데이터 자동 집계로 보고서 수기작성 제거</t>
-        </is>
-      </c>
+          <t>예 - 확실히 중복</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -10197,7 +10272,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D30" s="50" t="n">
+      <c r="D30" s="57" t="n">
         <v>46246</v>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -10205,11 +10280,11 @@
           <t>수</t>
         </is>
       </c>
-      <c r="F30" s="51" t="n">
+      <c r="F30" s="58" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="G30" s="58" t="n">
         <v>0.5833333333333334</v>
-      </c>
-      <c r="G30" s="51" t="n">
-        <v>0.6041666666666666</v>
       </c>
       <c r="H30" s="7">
         <f>IF(OR(F30="",G30=""),"",(G30-F30)*1440)</f>
@@ -10227,7 +10302,7 @@
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>AX+업무리스트 보고서 검토 및 피드백(채림님)</t>
+          <t>AX+업무리스트 보고서 검토 및 피드백(정하님)</t>
         </is>
       </c>
       <c r="L30" s="8" t="inlineStr">
@@ -10247,7 +10322,7 @@
       </c>
       <c r="O30" s="8" t="inlineStr">
         <is>
-          <t>양채림</t>
+          <t>정하</t>
         </is>
       </c>
       <c r="P30" s="8" t="n"/>
@@ -10293,7 +10368,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D31" s="50" t="n">
+      <c r="D31" s="57" t="n">
         <v>46246</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -10301,11 +10376,11 @@
           <t>수</t>
         </is>
       </c>
-      <c r="F31" s="51" t="n">
+      <c r="F31" s="58" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="G31" s="58" t="n">
         <v>0.6041666666666666</v>
-      </c>
-      <c r="G31" s="51" t="n">
-        <v>0.6458333333333334</v>
       </c>
       <c r="H31" s="7">
         <f>IF(OR(F31="",G31=""),"",(G31-F31)*1440)</f>
@@ -10318,17 +10393,17 @@
       </c>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>MGT-07 업무 인수인계·이관</t>
+          <t>MGT-06 팀원 업무·산출물 검토·피드백</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>그로홈 업무 인수인계 받음 — 담당 범위·진행건 확인</t>
+          <t>AX+업무리스트 보고서 검토 및 피드백(채림님)</t>
         </is>
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>그로홈</t>
+          <t>팀 업무관리</t>
         </is>
       </c>
       <c r="M31" s="8" t="inlineStr">
@@ -10341,16 +10416,20 @@
           <t>https://pourstorecrm.web.app/pour-os</t>
         </is>
       </c>
-      <c r="O31" s="8" t="n"/>
+      <c r="O31" s="8" t="inlineStr">
+        <is>
+          <t>양채림</t>
+        </is>
+      </c>
       <c r="P31" s="8" t="n"/>
       <c r="Q31" s="8" t="inlineStr">
         <is>
-          <t>인수인계 항목 정리</t>
+          <t>검토 피드백</t>
         </is>
       </c>
       <c r="R31" s="8" t="inlineStr">
         <is>
-          <t>1회성</t>
+          <t>주 1회</t>
         </is>
       </c>
       <c r="S31" s="8" t="inlineStr">
@@ -10360,12 +10439,12 @@
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>모름</t>
+          <t>아마도 중복</t>
         </is>
       </c>
       <c r="U31" s="8" t="inlineStr">
         <is>
-          <t>인수인계 체크리스트·담당 매핑표 상시 관리</t>
+          <t>업무보드 데이터 자동 집계로 보고서 수기작성 제거</t>
         </is>
       </c>
     </row>
@@ -10385,7 +10464,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D32" s="50" t="n">
+      <c r="D32" s="57" t="n">
         <v>46246</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -10393,11 +10472,11 @@
           <t>수</t>
         </is>
       </c>
-      <c r="F32" s="51" t="n">
+      <c r="F32" s="58" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="G32" s="58" t="n">
         <v>0.6458333333333334</v>
-      </c>
-      <c r="G32" s="51" t="n">
-        <v>0.6875</v>
       </c>
       <c r="H32" s="7">
         <f>IF(OR(F32="",G32=""),"",(G32-F32)*1440)</f>
@@ -10405,30 +10484,39 @@
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>콘텐츠제작</t>
+          <t>기획·보고·회의</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>CNT-07 카탈로그·영업자료 제작</t>
+          <t>MGT-07 업무 인수인계·이관</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>부자재 소개 카달로그 제작</t>
+          <t>그로홈 업무 인수인계 받음 — 담당 범위·진행건 확인</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>부자재</t>
-        </is>
-      </c>
-      <c r="M32" s="8" t="n"/>
+          <t>그로홈</t>
+        </is>
+      </c>
+      <c r="M32" s="8" t="inlineStr">
+        <is>
+          <t>CRM센터-POUR OS(업무보드)</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>https://pourstorecrm.web.app/pour-os</t>
+        </is>
+      </c>
       <c r="O32" s="8" t="n"/>
       <c r="P32" s="8" t="n"/>
       <c r="Q32" s="8" t="inlineStr">
         <is>
-          <t>부자재 소개 카달로그</t>
+          <t>인수인계 항목 정리</t>
         </is>
       </c>
       <c r="R32" s="8" t="inlineStr">
@@ -10438,17 +10526,17 @@
       </c>
       <c r="S32" s="8" t="inlineStr">
         <is>
-          <t>반정형</t>
+          <t>비정형(판단 필요)</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
+          <t>모름</t>
         </is>
       </c>
       <c r="U32" s="8" t="inlineStr">
         <is>
-          <t>상품 마스터 데이터로 카달로그 자동 생성</t>
+          <t>인수인계 체크리스트·담당 매핑표 상시 관리</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10556,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D33" s="50" t="n">
+      <c r="D33" s="57" t="n">
         <v>46246</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -10476,11 +10564,11 @@
           <t>수</t>
         </is>
       </c>
-      <c r="F33" s="51" t="n">
+      <c r="F33" s="58" t="n">
+        <v>0.6458333333333334</v>
+      </c>
+      <c r="G33" s="58" t="n">
         <v>0.6875</v>
-      </c>
-      <c r="G33" s="51" t="n">
-        <v>0.7291666666666666</v>
       </c>
       <c r="H33" s="7">
         <f>IF(OR(F33="",G33=""),"",(G33-F33)*1440)</f>
@@ -10488,49 +10576,40 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>데이터·정산</t>
+          <t>콘텐츠제작</t>
         </is>
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>DAT-04 리포트·대시보드 작성</t>
+          <t>CNT-07 카탈로그·영업자료 제작</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>POUR스토어 단가·공헌이익·손익계산 대시보드 제작 — 진행중</t>
+          <t>부자재 소개 카달로그 제작</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>POUR스토어</t>
-        </is>
-      </c>
-      <c r="M33" s="8" t="inlineStr">
-        <is>
-          <t>단가 대시보드, 엑셀</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>POUR스토어 가격·마진 통합 대시보드 (pour-construction-form.pages.dev)</t>
-        </is>
-      </c>
+          <t>부자재</t>
+        </is>
+      </c>
+      <c r="M33" s="8" t="n"/>
       <c r="O33" s="8" t="n"/>
       <c r="P33" s="8" t="n"/>
       <c r="Q33" s="8" t="inlineStr">
         <is>
-          <t>단가·공헌이익·손익 대시보드</t>
+          <t>부자재 소개 카달로그</t>
         </is>
       </c>
       <c r="R33" s="8" t="inlineStr">
         <is>
-          <t>주 2~3회</t>
+          <t>1회성</t>
         </is>
       </c>
       <c r="S33" s="8" t="inlineStr">
         <is>
-          <t>비정형(판단 필요)</t>
+          <t>반정형</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
@@ -10540,7 +10619,7 @@
       </c>
       <c r="U33" s="8" t="inlineStr">
         <is>
-          <t>채널 수수료·원가 데이터 자동 연동으로 수기 입력 제거</t>
+          <t>상품 마스터 데이터로 카달로그 자동 생성</t>
         </is>
       </c>
     </row>
@@ -10560,7 +10639,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D34" s="50" t="n">
+      <c r="D34" s="57" t="n">
         <v>46246</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
@@ -10568,11 +10647,11 @@
           <t>수</t>
         </is>
       </c>
-      <c r="F34" s="51" t="n">
+      <c r="F34" s="58" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="G34" s="58" t="n">
         <v>0.7291666666666666</v>
-      </c>
-      <c r="G34" s="51" t="n">
-        <v>0.75</v>
       </c>
       <c r="H34" s="7">
         <f>IF(OR(F34="",G34=""),"",(G34-F34)*1440)</f>
@@ -10580,58 +10659,59 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>제조·생산관리</t>
+          <t>데이터·정산</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t>MFG-08 MSDS·라벨 등 제품 표시사항 제작</t>
+          <t>DAT-04 리포트·대시보드 작성</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>신제품 코트재 MSDS 컬러별 31개 제작 — 진행중</t>
+          <t>POUR스토어 단가·공헌이익·손익계산 대시보드 제작 — 진행중</t>
         </is>
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t>코트재 신제품 31색</t>
+          <t>POUR스토어</t>
         </is>
       </c>
       <c r="M34" s="8" t="inlineStr">
         <is>
-          <t>챗지피티</t>
+          <t>단가 대시보드, 엑셀</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>POUR스토어 가격·마진 통합 대시보드 (pour-construction-form.pages.dev)</t>
         </is>
       </c>
       <c r="O34" s="8" t="n"/>
-      <c r="P34" s="8" t="inlineStr">
-        <is>
-          <t>세이고, 쿠팡물류센터</t>
-        </is>
-      </c>
+      <c r="P34" s="8" t="n"/>
       <c r="Q34" s="8" t="inlineStr">
         <is>
-          <t>MSDS 31종</t>
+          <t>단가·공헌이익·손익 대시보드</t>
         </is>
       </c>
       <c r="R34" s="8" t="inlineStr">
         <is>
-          <t>1회성</t>
+          <t>주 2~3회</t>
         </is>
       </c>
       <c r="S34" s="8" t="inlineStr">
         <is>
-          <t>반정형</t>
+          <t>비정형(판단 필요)</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>아니오 - 우리팀 고유</t>
+          <t>아마도 중복</t>
         </is>
       </c>
       <c r="U34" s="8" t="inlineStr">
         <is>
-          <t>품목·색상 데이터 연동으로 MSDS 서식 자동 생성</t>
+          <t>채널 수수료·원가 데이터 자동 연동으로 수기 입력 제거</t>
         </is>
       </c>
     </row>
@@ -10651,19 +10731,19 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D35" s="50" t="n">
-        <v>46247</v>
+      <c r="D35" s="57" t="n">
+        <v>46246</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>목</t>
-        </is>
-      </c>
-      <c r="F35" s="51" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="G35" s="51" t="n">
-        <v>0.3958333333333333</v>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="F35" s="58" t="n">
+        <v>0.7291666666666666</v>
+      </c>
+      <c r="G35" s="58" t="n">
+        <v>0.75</v>
       </c>
       <c r="H35" s="7">
         <f>IF(OR(F35="",G35=""),"",(G35-F35)*1440)</f>
@@ -10671,59 +10751,58 @@
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>기타·행정</t>
+          <t>제조·생산관리</t>
         </is>
       </c>
       <c r="J35" s="8" t="inlineStr">
         <is>
-          <t>ETC-01 메일·메신저 확인 및 회신</t>
+          <t>MFG-08 MSDS·라벨 등 제품 표시사항 제작</t>
         </is>
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>출근 후 메일·메신저·업무보드 확인 및 회신</t>
+          <t>신제품 코트재 MSDS 컬러별 31개 제작 — 진행중</t>
         </is>
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>전사</t>
+          <t>코트재 신제품 31색</t>
         </is>
       </c>
       <c r="M35" s="8" t="inlineStr">
         <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
+          <t>챗지피티</t>
         </is>
       </c>
       <c r="O35" s="8" t="n"/>
-      <c r="P35" s="8" t="n"/>
+      <c r="P35" s="8" t="inlineStr">
+        <is>
+          <t>세이고, 쿠팡물류센터</t>
+        </is>
+      </c>
       <c r="Q35" s="8" t="inlineStr">
         <is>
-          <t>회신 처리</t>
+          <t>MSDS 31종</t>
         </is>
       </c>
       <c r="R35" s="8" t="inlineStr">
         <is>
-          <t>매일</t>
+          <t>1회성</t>
         </is>
       </c>
       <c r="S35" s="8" t="inlineStr">
         <is>
-          <t>정형(매뉴얼화 가능)</t>
+          <t>반정형</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>예 - 확실히 중복</t>
+          <t>아니오 - 우리팀 고유</t>
         </is>
       </c>
       <c r="U35" s="8" t="inlineStr">
         <is>
-          <t>팀별 요청·공지를 업무보드 알림 하나로 일원화</t>
+          <t>품목·색상 데이터 연동으로 MSDS 서식 자동 생성</t>
         </is>
       </c>
     </row>
@@ -10743,7 +10822,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D36" s="50" t="n">
+      <c r="D36" s="57" t="n">
         <v>46247</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
@@ -10751,11 +10830,11 @@
           <t>목</t>
         </is>
       </c>
-      <c r="F36" s="51" t="n">
+      <c r="F36" s="58" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="G36" s="58" t="n">
         <v>0.3958333333333333</v>
-      </c>
-      <c r="G36" s="51" t="n">
-        <v>0.4375</v>
       </c>
       <c r="H36" s="7">
         <f>IF(OR(F36="",G36=""),"",(G36-F36)*1440)</f>
@@ -10763,47 +10842,44 @@
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>마케팅·광고운영</t>
+          <t>기타·행정</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>MKT-08 제휴마케팅(링크프라이스 등) 운영·성과확인</t>
+          <t>ETC-01 메일·메신저 확인 및 회신</t>
         </is>
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>링크프라이스 네이버쇼핑·파워링크 주간보고 수령 → 본부장님 보고 → 보성님 인계</t>
+          <t>출근 후 메일·메신저·업무보드 확인 및 회신</t>
         </is>
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
-          <t>POUR스토어 / 네이버쇼핑·파워링크</t>
+          <t>전사</t>
         </is>
       </c>
       <c r="M36" s="8" t="inlineStr">
         <is>
-          <t>링크프라이스 관리자</t>
-        </is>
-      </c>
-      <c r="O36" s="8" t="inlineStr">
-        <is>
-          <t>본부장, 보성님</t>
-        </is>
-      </c>
-      <c r="P36" s="8" t="inlineStr">
-        <is>
-          <t>링크프라이스</t>
-        </is>
-      </c>
+          <t>CRM센터-POUR OS(업무보드)</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>https://pourstorecrm.web.app/pour-os</t>
+        </is>
+      </c>
+      <c r="O36" s="8" t="n"/>
+      <c r="P36" s="8" t="n"/>
       <c r="Q36" s="8" t="inlineStr">
         <is>
-          <t>제휴·검색광고 주간보고</t>
+          <t>회신 처리</t>
         </is>
       </c>
       <c r="R36" s="8" t="inlineStr">
         <is>
-          <t>주 1회</t>
+          <t>매일</t>
         </is>
       </c>
       <c r="S36" s="8" t="inlineStr">
@@ -10818,7 +10894,7 @@
       </c>
       <c r="U36" s="8" t="inlineStr">
         <is>
-          <t>주간보고 자동 생성 후 공유(수령→전달 단계 제거)</t>
+          <t>팀별 요청·공지를 업무보드 알림 하나로 일원화</t>
         </is>
       </c>
     </row>
@@ -10838,7 +10914,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D37" s="50" t="n">
+      <c r="D37" s="57" t="n">
         <v>46247</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -10846,11 +10922,11 @@
           <t>목</t>
         </is>
       </c>
-      <c r="F37" s="51" t="n">
+      <c r="F37" s="58" t="n">
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="G37" s="58" t="n">
         <v>0.4375</v>
-      </c>
-      <c r="G37" s="51" t="n">
-        <v>0.4791666666666667</v>
       </c>
       <c r="H37" s="7">
         <f>IF(OR(F37="",G37=""),"",(G37-F37)*1440)</f>
@@ -10858,34 +10934,42 @@
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>기타·행정</t>
+          <t>마케팅·광고운영</t>
         </is>
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>ETC-02 행정·경비·구매 처리</t>
+          <t>MKT-08 제휴마케팅(링크프라이스 등) 운영·성과확인</t>
         </is>
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>씰맥스프로 결제 처리 및 세이고 입고내역 자료 송부(김성준 공장장님께)</t>
+          <t>링크프라이스 네이버쇼핑·파워링크 주간보고 수령 → 본부장님 보고 → 보성님 인계</t>
         </is>
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
-          <t>씰맥스프로 / 세이고</t>
-        </is>
-      </c>
-      <c r="M37" s="8" t="n"/>
-      <c r="O37" s="8" t="n"/>
+          <t>POUR스토어 / 네이버쇼핑·파워링크</t>
+        </is>
+      </c>
+      <c r="M37" s="8" t="inlineStr">
+        <is>
+          <t>링크프라이스 관리자</t>
+        </is>
+      </c>
+      <c r="O37" s="8" t="inlineStr">
+        <is>
+          <t>본부장, 보성님</t>
+        </is>
+      </c>
       <c r="P37" s="8" t="inlineStr">
         <is>
-          <t>세이고, 김성준 공장장</t>
+          <t>링크프라이스</t>
         </is>
       </c>
       <c r="Q37" s="8" t="inlineStr">
         <is>
-          <t>결제 완료·입고내역 자료</t>
+          <t>제휴·검색광고 주간보고</t>
         </is>
       </c>
       <c r="R37" s="8" t="inlineStr">
@@ -10900,12 +10984,12 @@
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
+          <t>예 - 확실히 중복</t>
         </is>
       </c>
       <c r="U37" s="8" t="inlineStr">
         <is>
-          <t>결제·입고내역 자동 정산 시트 연동</t>
+          <t>주간보고 자동 생성 후 공유(수령→전달 단계 제거)</t>
         </is>
       </c>
     </row>
@@ -10925,7 +11009,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D38" s="50" t="n">
+      <c r="D38" s="57" t="n">
         <v>46247</v>
       </c>
       <c r="E38" s="8" t="inlineStr">
@@ -10933,11 +11017,11 @@
           <t>목</t>
         </is>
       </c>
-      <c r="F38" s="51" t="n">
+      <c r="F38" s="58" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="G38" s="58" t="n">
         <v>0.4791666666666667</v>
-      </c>
-      <c r="G38" s="51" t="n">
-        <v>0.5</v>
       </c>
       <c r="H38" s="7">
         <f>IF(OR(F38="",G38=""),"",(G38-F38)*1440)</f>
@@ -10945,43 +11029,34 @@
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>기획·보고·회의</t>
+          <t>기타·행정</t>
         </is>
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>MGT-06 팀원 업무·산출물 검토·피드백</t>
+          <t>ETC-02 행정·경비·구매 처리</t>
         </is>
       </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
-          <t>정하님 업무정리 리스트 검토</t>
+          <t>씰맥스프로 결제 처리 및 세이고 입고내역 자료 송부(김성준 공장장님께)</t>
         </is>
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
-          <t>팀 업무관리</t>
-        </is>
-      </c>
-      <c r="M38" s="8" t="inlineStr">
-        <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
-        </is>
-      </c>
-      <c r="O38" s="8" t="inlineStr">
-        <is>
-          <t>정하</t>
-        </is>
-      </c>
-      <c r="P38" s="8" t="n"/>
+          <t>씰맥스프로 / 세이고</t>
+        </is>
+      </c>
+      <c r="M38" s="8" t="n"/>
+      <c r="O38" s="8" t="n"/>
+      <c r="P38" s="8" t="inlineStr">
+        <is>
+          <t>세이고, 김성준 공장장</t>
+        </is>
+      </c>
       <c r="Q38" s="8" t="inlineStr">
         <is>
-          <t>검토 의견</t>
+          <t>결제 완료·입고내역 자료</t>
         </is>
       </c>
       <c r="R38" s="8" t="inlineStr">
@@ -10991,7 +11066,7 @@
       </c>
       <c r="S38" s="8" t="inlineStr">
         <is>
-          <t>비정형(판단 필요)</t>
+          <t>정형(매뉴얼화 가능)</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
@@ -11001,7 +11076,7 @@
       </c>
       <c r="U38" s="8" t="inlineStr">
         <is>
-          <t>업무보드 데이터 자동 집계로 대체</t>
+          <t>결제·입고내역 자동 정산 시트 연동</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11096,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D39" s="50" t="n">
+      <c r="D39" s="57" t="n">
         <v>46247</v>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -11029,11 +11104,11 @@
           <t>목</t>
         </is>
       </c>
-      <c r="F39" s="51" t="n">
+      <c r="F39" s="58" t="n">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="G39" s="58" t="n">
         <v>0.5</v>
-      </c>
-      <c r="G39" s="51" t="n">
-        <v>0.5416666666666666</v>
       </c>
       <c r="H39" s="7">
         <f>IF(OR(F39="",G39=""),"",(G39-F39)*1440)</f>
@@ -11041,40 +11116,65 @@
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>기타·행정</t>
+          <t>기획·보고·회의</t>
         </is>
       </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>ETC-05 휴게·점심</t>
+          <t>MGT-06 팀원 업무·산출물 검토·피드백</t>
         </is>
       </c>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>점심 및 휴게</t>
-        </is>
-      </c>
-      <c r="L39" s="8" t="n"/>
-      <c r="M39" s="8" t="n"/>
-      <c r="O39" s="8" t="n"/>
+          <t>정하님 업무정리 리스트 검토</t>
+        </is>
+      </c>
+      <c r="L39" s="8" t="inlineStr">
+        <is>
+          <t>팀 업무관리</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="inlineStr">
+        <is>
+          <t>CRM센터-POUR OS(업무보드)</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>https://pourstorecrm.web.app/pour-os</t>
+        </is>
+      </c>
+      <c r="O39" s="8" t="inlineStr">
+        <is>
+          <t>정하</t>
+        </is>
+      </c>
       <c r="P39" s="8" t="n"/>
-      <c r="Q39" s="8" t="n"/>
+      <c r="Q39" s="8" t="inlineStr">
+        <is>
+          <t>검토 의견</t>
+        </is>
+      </c>
       <c r="R39" s="8" t="inlineStr">
         <is>
-          <t>매일</t>
+          <t>주 1회</t>
         </is>
       </c>
       <c r="S39" s="8" t="inlineStr">
         <is>
-          <t>정형(매뉴얼화 가능)</t>
+          <t>비정형(판단 필요)</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>예 - 확실히 중복</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="n"/>
+          <t>아마도 중복</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>업무보드 데이터 자동 집계로 대체</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -11092,7 +11192,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D40" s="50" t="n">
+      <c r="D40" s="57" t="n">
         <v>46247</v>
       </c>
       <c r="E40" s="8" t="inlineStr">
@@ -11100,11 +11200,11 @@
           <t>목</t>
         </is>
       </c>
-      <c r="F40" s="51" t="n">
+      <c r="F40" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G40" s="58" t="n">
         <v>0.5416666666666666</v>
-      </c>
-      <c r="G40" s="51" t="n">
-        <v>0.6041666666666666</v>
       </c>
       <c r="H40" s="7">
         <f>IF(OR(F40="",G40=""),"",(G40-F40)*1440)</f>
@@ -11112,69 +11212,40 @@
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>마케팅·광고운영</t>
+          <t>기타·행정</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>MKT-04 인플루언서·체험단 섭외/관리</t>
+          <t>ETC-05 휴게·점심</t>
         </is>
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>채림님 퍼포먼스마케팅 진행 방안(①직판 ②대리점·파트너사 2트랙 바이럴) 안내 및 매체·대행사 시장조사 요청</t>
-        </is>
-      </c>
-      <c r="L40" s="8" t="inlineStr">
-        <is>
-          <t>POUR스토어 / 블로그·유튜브·카페·인스타</t>
-        </is>
-      </c>
-      <c r="M40" s="8" t="inlineStr">
-        <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
-        </is>
-      </c>
-      <c r="O40" s="8" t="inlineStr">
-        <is>
-          <t>양채림</t>
-        </is>
-      </c>
-      <c r="P40" s="8" t="inlineStr">
-        <is>
-          <t>인플루언서, 바이럴 대행사(레뷰 등)</t>
-        </is>
-      </c>
-      <c r="Q40" s="8" t="inlineStr">
-        <is>
-          <t>진행 방안 안내·시장조사 요청서</t>
-        </is>
-      </c>
+          <t>점심 및 휴게</t>
+        </is>
+      </c>
+      <c r="L40" s="8" t="n"/>
+      <c r="M40" s="8" t="n"/>
+      <c r="O40" s="8" t="n"/>
+      <c r="P40" s="8" t="n"/>
+      <c r="Q40" s="8" t="n"/>
       <c r="R40" s="8" t="inlineStr">
         <is>
-          <t>주 1회</t>
+          <t>매일</t>
         </is>
       </c>
       <c r="S40" s="8" t="inlineStr">
         <is>
-          <t>비정형(판단 필요)</t>
+          <t>정형(매뉴얼화 가능)</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>바이럴 매체·대행사 후보 DB 공용화</t>
-        </is>
-      </c>
+          <t>예 - 확실히 중복</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -11192,7 +11263,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D41" s="50" t="n">
+      <c r="D41" s="57" t="n">
         <v>46247</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -11200,11 +11271,11 @@
           <t>목</t>
         </is>
       </c>
-      <c r="F41" s="51" t="n">
+      <c r="F41" s="58" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="G41" s="58" t="n">
         <v>0.6041666666666666</v>
-      </c>
-      <c r="G41" s="51" t="n">
-        <v>0.6458333333333334</v>
       </c>
       <c r="H41" s="7">
         <f>IF(OR(F41="",G41=""),"",(G41-F41)*1440)</f>
@@ -11212,54 +11283,67 @@
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>채널·스토어운영</t>
+          <t>마케팅·광고운영</t>
         </is>
       </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
-          <t>CHN-03 자사몰 운영·관리</t>
+          <t>MKT-04 인플루언서·체험단 섭외/관리</t>
         </is>
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>자사몰 회원 등급별 구매가능 상품 확인 페이지 제작 및 랜딩 링크 삽입 요청</t>
+          <t>채림님 퍼포먼스마케팅 진행 방안(①직판 ②대리점·파트너사 2트랙 바이럴) 안내 및 매체·대행사 시장조사 요청</t>
         </is>
       </c>
       <c r="L41" s="8" t="inlineStr">
         <is>
-          <t>POUR스토어 자사몰</t>
+          <t>POUR스토어 / 블로그·유튜브·카페·인스타</t>
         </is>
       </c>
       <c r="M41" s="8" t="inlineStr">
         <is>
-          <t>자사몰 관리자</t>
-        </is>
-      </c>
-      <c r="O41" s="8" t="n"/>
-      <c r="P41" s="8" t="n"/>
+          <t>CRM센터-POUR OS(업무보드)</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>https://pourstorecrm.web.app/pour-os</t>
+        </is>
+      </c>
+      <c r="O41" s="8" t="inlineStr">
+        <is>
+          <t>양채림</t>
+        </is>
+      </c>
+      <c r="P41" s="8" t="inlineStr">
+        <is>
+          <t>인플루언서, 바이럴 대행사(레뷰 등)</t>
+        </is>
+      </c>
       <c r="Q41" s="8" t="inlineStr">
         <is>
-          <t>등급별 구매가능 페이지 요청서</t>
+          <t>진행 방안 안내·시장조사 요청서</t>
         </is>
       </c>
       <c r="R41" s="8" t="inlineStr">
         <is>
-          <t>1회성</t>
+          <t>주 1회</t>
         </is>
       </c>
       <c r="S41" s="8" t="inlineStr">
         <is>
-          <t>반정형</t>
+          <t>비정형(판단 필요)</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>모름</t>
+          <t>아마도 중복</t>
         </is>
       </c>
       <c r="U41" s="8" t="inlineStr">
         <is>
-          <t>회원등급·판매권한 데이터 연동으로 페이지 자동 생성</t>
+          <t>바이럴 매체·대행사 후보 DB 공용화</t>
         </is>
       </c>
     </row>
@@ -11279,7 +11363,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D42" s="50" t="n">
+      <c r="D42" s="57" t="n">
         <v>46247</v>
       </c>
       <c r="E42" s="8" t="inlineStr">
@@ -11287,11 +11371,11 @@
           <t>목</t>
         </is>
       </c>
-      <c r="F42" s="51" t="n">
+      <c r="F42" s="58" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="G42" s="58" t="n">
         <v>0.6458333333333334</v>
-      </c>
-      <c r="G42" s="51" t="n">
-        <v>0.7083333333333334</v>
       </c>
       <c r="H42" s="7">
         <f>IF(OR(F42="",G42=""),"",(G42-F42)*1440)</f>
@@ -11299,59 +11383,54 @@
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>데이터·정산</t>
+          <t>채널·스토어운영</t>
         </is>
       </c>
       <c r="J42" s="8" t="inlineStr">
         <is>
-          <t>DAT-04 리포트·대시보드 작성</t>
+          <t>CHN-03 자사몰 운영·관리</t>
         </is>
       </c>
       <c r="K42" s="8" t="inlineStr">
         <is>
-          <t>POUR스토어 단가·공헌이익·손익계산 대시보드 제작 — 진행중</t>
+          <t>자사몰 회원 등급별 구매가능 상품 확인 페이지 제작 및 랜딩 링크 삽입 요청</t>
         </is>
       </c>
       <c r="L42" s="8" t="inlineStr">
         <is>
-          <t>POUR스토어</t>
+          <t>POUR스토어 자사몰</t>
         </is>
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>단가 대시보드, 엑셀</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>POUR스토어 가격·마진 통합 대시보드 (pour-construction-form.pages.dev)</t>
+          <t>자사몰 관리자</t>
         </is>
       </c>
       <c r="O42" s="8" t="n"/>
       <c r="P42" s="8" t="n"/>
       <c r="Q42" s="8" t="inlineStr">
         <is>
-          <t>단가·공헌이익·손익 대시보드</t>
+          <t>등급별 구매가능 페이지 요청서</t>
         </is>
       </c>
       <c r="R42" s="8" t="inlineStr">
         <is>
-          <t>주 2~3회</t>
+          <t>1회성</t>
         </is>
       </c>
       <c r="S42" s="8" t="inlineStr">
         <is>
-          <t>비정형(판단 필요)</t>
+          <t>반정형</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
+          <t>모름</t>
         </is>
       </c>
       <c r="U42" s="8" t="inlineStr">
         <is>
-          <t>채널 수수료·원가 데이터 자동 연동으로 수기 입력 제거</t>
+          <t>회원등급·판매권한 데이터 연동으로 페이지 자동 생성</t>
         </is>
       </c>
     </row>
@@ -11371,7 +11450,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D43" s="50" t="n">
+      <c r="D43" s="57" t="n">
         <v>46247</v>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -11379,11 +11458,11 @@
           <t>목</t>
         </is>
       </c>
-      <c r="F43" s="51" t="n">
+      <c r="F43" s="58" t="n">
+        <v>0.6458333333333334</v>
+      </c>
+      <c r="G43" s="58" t="n">
         <v>0.7083333333333334</v>
-      </c>
-      <c r="G43" s="51" t="n">
-        <v>0.75</v>
       </c>
       <c r="H43" s="7">
         <f>IF(OR(F43="",G43=""),"",(G43-F43)*1440)</f>
@@ -11391,58 +11470,59 @@
       </c>
       <c r="I43" s="8" t="inlineStr">
         <is>
-          <t>제조·생산관리</t>
+          <t>데이터·정산</t>
         </is>
       </c>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t>MFG-08 MSDS·라벨 등 제품 표시사항 제작</t>
+          <t>DAT-04 리포트·대시보드 작성</t>
         </is>
       </c>
       <c r="K43" s="8" t="inlineStr">
         <is>
-          <t>신제품 코트재 MSDS 컬러별 31개 제작 — 진행중</t>
+          <t>POUR스토어 단가·공헌이익·손익계산 대시보드 제작 — 진행중</t>
         </is>
       </c>
       <c r="L43" s="8" t="inlineStr">
         <is>
-          <t>코트재 신제품 31색</t>
+          <t>POUR스토어</t>
         </is>
       </c>
       <c r="M43" s="8" t="inlineStr">
         <is>
-          <t>챗지피티</t>
+          <t>단가 대시보드, 엑셀</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>POUR스토어 가격·마진 통합 대시보드 (pour-construction-form.pages.dev)</t>
         </is>
       </c>
       <c r="O43" s="8" t="n"/>
-      <c r="P43" s="8" t="inlineStr">
-        <is>
-          <t>세이고, 쿠팡물류센터</t>
-        </is>
-      </c>
+      <c r="P43" s="8" t="n"/>
       <c r="Q43" s="8" t="inlineStr">
         <is>
-          <t>MSDS 31종</t>
+          <t>단가·공헌이익·손익 대시보드</t>
         </is>
       </c>
       <c r="R43" s="8" t="inlineStr">
         <is>
-          <t>1회성</t>
+          <t>주 2~3회</t>
         </is>
       </c>
       <c r="S43" s="8" t="inlineStr">
         <is>
-          <t>반정형</t>
+          <t>비정형(판단 필요)</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>아니오 - 우리팀 고유</t>
+          <t>아마도 중복</t>
         </is>
       </c>
       <c r="U43" s="8" t="inlineStr">
         <is>
-          <t>품목·색상 데이터 연동으로 MSDS 서식 자동 생성</t>
+          <t>채널 수수료·원가 데이터 자동 연동으로 수기 입력 제거</t>
         </is>
       </c>
     </row>
@@ -11462,19 +11542,19 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D44" s="50" t="n">
-        <v>46248</v>
+      <c r="D44" s="57" t="n">
+        <v>46247</v>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>금</t>
-        </is>
-      </c>
-      <c r="F44" s="51" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="G44" s="51" t="n">
-        <v>0.4583333333333333</v>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="F44" s="58" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="G44" s="58" t="n">
+        <v>0.75</v>
       </c>
       <c r="H44" s="7">
         <f>IF(OR(F44="",G44=""),"",(G44-F44)*1440)</f>
@@ -11482,46 +11562,58 @@
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>기타·행정</t>
+          <t>제조·생산관리</t>
         </is>
       </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>ETC-04 이동·외근</t>
+          <t>MFG-08 MSDS·라벨 등 제품 표시사항 제작</t>
         </is>
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>부산 대리점 방문 이동(사무실 → 부산)</t>
+          <t>신제품 코트재 MSDS 컬러별 31개 제작 — 진행중</t>
         </is>
       </c>
       <c r="L44" s="8" t="inlineStr">
         <is>
-          <t>대리점(가나랜드·겸남지사)</t>
-        </is>
-      </c>
-      <c r="M44" s="8" t="n"/>
+          <t>코트재 신제품 31색</t>
+        </is>
+      </c>
+      <c r="M44" s="8" t="inlineStr">
+        <is>
+          <t>챗지피티</t>
+        </is>
+      </c>
       <c r="O44" s="8" t="n"/>
-      <c r="P44" s="8" t="n"/>
-      <c r="Q44" s="8" t="n"/>
+      <c r="P44" s="8" t="inlineStr">
+        <is>
+          <t>세이고, 쿠팡물류센터</t>
+        </is>
+      </c>
+      <c r="Q44" s="8" t="inlineStr">
+        <is>
+          <t>MSDS 31종</t>
+        </is>
+      </c>
       <c r="R44" s="8" t="inlineStr">
         <is>
-          <t>분기/비정기</t>
+          <t>1회성</t>
         </is>
       </c>
       <c r="S44" s="8" t="inlineStr">
         <is>
-          <t>정형(매뉴얼화 가능)</t>
+          <t>반정형</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
+          <t>아니오 - 우리팀 고유</t>
         </is>
       </c>
       <c r="U44" s="8" t="inlineStr">
         <is>
-          <t>인근 대리점 방문 일정 묶어 이동시간 절감</t>
+          <t>품목·색상 데이터 연동으로 MSDS 서식 자동 생성</t>
         </is>
       </c>
     </row>
@@ -11541,7 +11633,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D45" s="50" t="n">
+      <c r="D45" s="57" t="n">
         <v>46248</v>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -11549,11 +11641,11 @@
           <t>금</t>
         </is>
       </c>
-      <c r="F45" s="51" t="n">
+      <c r="F45" s="58" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="G45" s="58" t="n">
         <v>0.4583333333333333</v>
-      </c>
-      <c r="G45" s="51" t="n">
-        <v>0.5</v>
       </c>
       <c r="H45" s="7">
         <f>IF(OR(F45="",G45=""),"",(G45-F45)*1440)</f>
@@ -11561,36 +11653,28 @@
       </c>
       <c r="I45" s="8" t="inlineStr">
         <is>
-          <t>파트너·대리점관리</t>
+          <t>기타·행정</t>
         </is>
       </c>
       <c r="J45" s="8" t="inlineStr">
         <is>
-          <t>PTR-01 대리점·파트너사 방문·미팅</t>
+          <t>ETC-04 이동·외근</t>
         </is>
       </c>
       <c r="K45" s="8" t="inlineStr">
         <is>
-          <t>가나랜드 대리점 방문 미팅 — 판매 현황·요청사항 청취</t>
+          <t>부산 대리점 방문 이동(사무실 → 부산)</t>
         </is>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
-          <t>가나랜드</t>
+          <t>대리점(가나랜드·겸남지사)</t>
         </is>
       </c>
       <c r="M45" s="8" t="n"/>
       <c r="O45" s="8" t="n"/>
-      <c r="P45" s="8" t="inlineStr">
-        <is>
-          <t>가나랜드</t>
-        </is>
-      </c>
-      <c r="Q45" s="8" t="inlineStr">
-        <is>
-          <t>방문 미팅 기록</t>
-        </is>
-      </c>
+      <c r="P45" s="8" t="n"/>
+      <c r="Q45" s="8" t="n"/>
       <c r="R45" s="8" t="inlineStr">
         <is>
           <t>분기/비정기</t>
@@ -11598,17 +11682,17 @@
       </c>
       <c r="S45" s="8" t="inlineStr">
         <is>
-          <t>반정형</t>
+          <t>정형(매뉴얼화 가능)</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>모름</t>
+          <t>아마도 중복</t>
         </is>
       </c>
       <c r="U45" s="8" t="inlineStr">
         <is>
-          <t>대리점 방문 결과를 공용 대리점 카드에 기록·공유</t>
+          <t>인근 대리점 방문 일정 묶어 이동시간 절감</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11712,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D46" s="50" t="n">
+      <c r="D46" s="57" t="n">
         <v>46248</v>
       </c>
       <c r="E46" s="8" t="inlineStr">
@@ -11636,11 +11720,11 @@
           <t>금</t>
         </is>
       </c>
-      <c r="F46" s="51" t="n">
+      <c r="F46" s="58" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="G46" s="58" t="n">
         <v>0.5</v>
-      </c>
-      <c r="G46" s="51" t="n">
-        <v>0.5416666666666666</v>
       </c>
       <c r="H46" s="7">
         <f>IF(OR(F46="",G46=""),"",(G46-F46)*1440)</f>
@@ -11648,40 +11732,56 @@
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>기타·행정</t>
+          <t>파트너·대리점관리</t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>ETC-05 휴게·점심</t>
+          <t>PTR-01 대리점·파트너사 방문·미팅</t>
         </is>
       </c>
       <c r="K46" s="8" t="inlineStr">
         <is>
-          <t>점심 및 휴게</t>
-        </is>
-      </c>
-      <c r="L46" s="8" t="n"/>
+          <t>가나랜드 대리점 방문 미팅 — 판매 현황·요청사항 청취</t>
+        </is>
+      </c>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t>가나랜드</t>
+        </is>
+      </c>
       <c r="M46" s="8" t="n"/>
       <c r="O46" s="8" t="n"/>
-      <c r="P46" s="8" t="n"/>
-      <c r="Q46" s="8" t="n"/>
+      <c r="P46" s="8" t="inlineStr">
+        <is>
+          <t>가나랜드</t>
+        </is>
+      </c>
+      <c r="Q46" s="8" t="inlineStr">
+        <is>
+          <t>방문 미팅 기록</t>
+        </is>
+      </c>
       <c r="R46" s="8" t="inlineStr">
         <is>
-          <t>매일</t>
+          <t>분기/비정기</t>
         </is>
       </c>
       <c r="S46" s="8" t="inlineStr">
         <is>
-          <t>정형(매뉴얼화 가능)</t>
+          <t>반정형</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>예 - 확실히 중복</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="n"/>
+          <t>모름</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>대리점 방문 결과를 공용 대리점 카드에 기록·공유</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -11699,7 +11799,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D47" s="50" t="n">
+      <c r="D47" s="57" t="n">
         <v>46248</v>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -11707,11 +11807,11 @@
           <t>금</t>
         </is>
       </c>
-      <c r="F47" s="51" t="n">
+      <c r="F47" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G47" s="58" t="n">
         <v>0.5416666666666666</v>
-      </c>
-      <c r="G47" s="51" t="n">
-        <v>0.6041666666666666</v>
       </c>
       <c r="H47" s="7">
         <f>IF(OR(F47="",G47=""),"",(G47-F47)*1440)</f>
@@ -11719,56 +11819,40 @@
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>파트너·대리점관리</t>
+          <t>기타·행정</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>PTR-02 대리점·파트너 인터뷰·VOC 수집</t>
+          <t>ETC-05 휴게·점심</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>가나랜드 인터뷰 진행 및 현장 촬영(질문지 기반 VOC 수집)</t>
-        </is>
-      </c>
-      <c r="L47" s="8" t="inlineStr">
-        <is>
-          <t>가나랜드</t>
-        </is>
-      </c>
+          <t>점심 및 휴게</t>
+        </is>
+      </c>
+      <c r="L47" s="8" t="n"/>
       <c r="M47" s="8" t="n"/>
       <c r="O47" s="8" t="n"/>
-      <c r="P47" s="8" t="inlineStr">
-        <is>
-          <t>가나랜드</t>
-        </is>
-      </c>
-      <c r="Q47" s="8" t="inlineStr">
-        <is>
-          <t>인터뷰 기록·현장 촬영물</t>
-        </is>
-      </c>
+      <c r="P47" s="8" t="n"/>
+      <c r="Q47" s="8" t="n"/>
       <c r="R47" s="8" t="inlineStr">
         <is>
-          <t>분기/비정기</t>
+          <t>매일</t>
         </is>
       </c>
       <c r="S47" s="8" t="inlineStr">
         <is>
-          <t>반정형</t>
+          <t>정형(매뉴얼화 가능)</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>모름</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>인터뷰 VOC를 상품·마케팅 기획 입력값으로 자동 연결</t>
-        </is>
-      </c>
+          <t>예 - 확실히 중복</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
@@ -11786,7 +11870,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D48" s="50" t="n">
+      <c r="D48" s="57" t="n">
         <v>46248</v>
       </c>
       <c r="E48" s="8" t="inlineStr">
@@ -11794,11 +11878,11 @@
           <t>금</t>
         </is>
       </c>
-      <c r="F48" s="51" t="n">
+      <c r="F48" s="58" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="G48" s="58" t="n">
         <v>0.6041666666666666</v>
-      </c>
-      <c r="G48" s="51" t="n">
-        <v>0.625</v>
       </c>
       <c r="H48" s="7">
         <f>IF(OR(F48="",G48=""),"",(G48-F48)*1440)</f>
@@ -11806,28 +11890,36 @@
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>기타·행정</t>
+          <t>파트너·대리점관리</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
-          <t>ETC-04 이동·외근</t>
+          <t>PTR-02 대리점·파트너 인터뷰·VOC 수집</t>
         </is>
       </c>
       <c r="K48" s="8" t="inlineStr">
         <is>
-          <t>가나랜드 → 겸남지사 이동</t>
+          <t>가나랜드 인터뷰 진행 및 현장 촬영(질문지 기반 VOC 수집)</t>
         </is>
       </c>
       <c r="L48" s="8" t="inlineStr">
         <is>
-          <t>대리점(겸남지사)</t>
+          <t>가나랜드</t>
         </is>
       </c>
       <c r="M48" s="8" t="n"/>
       <c r="O48" s="8" t="n"/>
-      <c r="P48" s="8" t="n"/>
-      <c r="Q48" s="8" t="n"/>
+      <c r="P48" s="8" t="inlineStr">
+        <is>
+          <t>가나랜드</t>
+        </is>
+      </c>
+      <c r="Q48" s="8" t="inlineStr">
+        <is>
+          <t>인터뷰 기록·현장 촬영물</t>
+        </is>
+      </c>
       <c r="R48" s="8" t="inlineStr">
         <is>
           <t>분기/비정기</t>
@@ -11835,17 +11927,17 @@
       </c>
       <c r="S48" s="8" t="inlineStr">
         <is>
-          <t>정형(매뉴얼화 가능)</t>
+          <t>반정형</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
+          <t>모름</t>
         </is>
       </c>
       <c r="U48" s="8" t="inlineStr">
         <is>
-          <t>인근 대리점 방문 일정 묶어 이동시간 절감</t>
+          <t>인터뷰 VOC를 상품·마케팅 기획 입력값으로 자동 연결</t>
         </is>
       </c>
     </row>
@@ -11865,7 +11957,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D49" s="50" t="n">
+      <c r="D49" s="57" t="n">
         <v>46248</v>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -11873,11 +11965,11 @@
           <t>금</t>
         </is>
       </c>
-      <c r="F49" s="51" t="n">
+      <c r="F49" s="58" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="G49" s="58" t="n">
         <v>0.625</v>
-      </c>
-      <c r="G49" s="51" t="n">
-        <v>0.6875</v>
       </c>
       <c r="H49" s="7">
         <f>IF(OR(F49="",G49=""),"",(G49-F49)*1440)</f>
@@ -11885,36 +11977,28 @@
       </c>
       <c r="I49" s="8" t="inlineStr">
         <is>
-          <t>파트너·대리점관리</t>
+          <t>기타·행정</t>
         </is>
       </c>
       <c r="J49" s="8" t="inlineStr">
         <is>
-          <t>PTR-01 대리점·파트너사 방문·미팅</t>
+          <t>ETC-04 이동·외근</t>
         </is>
       </c>
       <c r="K49" s="8" t="inlineStr">
         <is>
-          <t>겸남지사 방문 미팅 및 인터뷰 진행</t>
+          <t>가나랜드 → 겸남지사 이동</t>
         </is>
       </c>
       <c r="L49" s="8" t="inlineStr">
         <is>
-          <t>겸남지사</t>
+          <t>대리점(겸남지사)</t>
         </is>
       </c>
       <c r="M49" s="8" t="n"/>
       <c r="O49" s="8" t="n"/>
-      <c r="P49" s="8" t="inlineStr">
-        <is>
-          <t>겸남지사</t>
-        </is>
-      </c>
-      <c r="Q49" s="8" t="inlineStr">
-        <is>
-          <t>방문 미팅·인터뷰 기록</t>
-        </is>
-      </c>
+      <c r="P49" s="8" t="n"/>
+      <c r="Q49" s="8" t="n"/>
       <c r="R49" s="8" t="inlineStr">
         <is>
           <t>분기/비정기</t>
@@ -11922,17 +12006,17 @@
       </c>
       <c r="S49" s="8" t="inlineStr">
         <is>
-          <t>반정형</t>
+          <t>정형(매뉴얼화 가능)</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>모름</t>
+          <t>아마도 중복</t>
         </is>
       </c>
       <c r="U49" s="8" t="inlineStr">
         <is>
-          <t>대리점 방문 결과를 공용 대리점 카드에 기록·공유</t>
+          <t>인근 대리점 방문 일정 묶어 이동시간 절감</t>
         </is>
       </c>
     </row>
@@ -11952,7 +12036,7 @@
           <t>브랜드커머스, 모여라딜 리드</t>
         </is>
       </c>
-      <c r="D50" s="50" t="n">
+      <c r="D50" s="57" t="n">
         <v>46248</v>
       </c>
       <c r="E50" s="8" t="inlineStr">
@@ -11960,11 +12044,11 @@
           <t>금</t>
         </is>
       </c>
-      <c r="F50" s="51" t="n">
+      <c r="F50" s="58" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G50" s="58" t="n">
         <v>0.6875</v>
-      </c>
-      <c r="G50" s="51" t="n">
-        <v>0.75</v>
       </c>
       <c r="H50" s="7">
         <f>IF(OR(F50="",G50=""),"",(G50-F50)*1440)</f>
@@ -11972,24 +12056,36 @@
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>기타·행정</t>
+          <t>파트너·대리점관리</t>
         </is>
       </c>
       <c r="J50" s="8" t="inlineStr">
         <is>
-          <t>ETC-04 이동·외근</t>
+          <t>PTR-01 대리점·파트너사 방문·미팅</t>
         </is>
       </c>
       <c r="K50" s="8" t="inlineStr">
         <is>
-          <t>부산 → 사무실 복귀 이동</t>
-        </is>
-      </c>
-      <c r="L50" s="8" t="n"/>
+          <t>겸남지사 방문 미팅 및 인터뷰 진행</t>
+        </is>
+      </c>
+      <c r="L50" s="8" t="inlineStr">
+        <is>
+          <t>겸남지사</t>
+        </is>
+      </c>
       <c r="M50" s="8" t="n"/>
       <c r="O50" s="8" t="n"/>
-      <c r="P50" s="8" t="n"/>
-      <c r="Q50" s="8" t="n"/>
+      <c r="P50" s="8" t="inlineStr">
+        <is>
+          <t>겸남지사</t>
+        </is>
+      </c>
+      <c r="Q50" s="8" t="inlineStr">
+        <is>
+          <t>방문 미팅·인터뷰 기록</t>
+        </is>
+      </c>
       <c r="R50" s="8" t="inlineStr">
         <is>
           <t>분기/비정기</t>
@@ -11997,44 +12093,94 @@
       </c>
       <c r="S50" s="8" t="inlineStr">
         <is>
-          <t>정형(매뉴얼화 가능)</t>
+          <t>반정형</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
+          <t>모름</t>
         </is>
       </c>
       <c r="U50" s="8" t="inlineStr">
         <is>
-          <t>인근 대리점 방문 일정 묶어 이동시간 절감</t>
+          <t>대리점 방문 결과를 공용 대리점 카드에 기록·공유</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="n"/>
-      <c r="B51" s="8" t="n"/>
-      <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="n"/>
-      <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="n"/>
-      <c r="G51" s="8" t="n"/>
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>브랜드커머스</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>김송희</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>브랜드커머스, 모여라딜 리드</t>
+        </is>
+      </c>
+      <c r="D51" s="57" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="F51" s="58" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="G51" s="58" t="n">
+        <v>0.75</v>
+      </c>
       <c r="H51" s="7">
         <f>IF(OR(F51="",G51=""),"",(G51-F51)*1440)</f>
         <v/>
       </c>
-      <c r="I51" s="8" t="n"/>
-      <c r="J51" s="8" t="n"/>
-      <c r="K51" s="8" t="n"/>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>기타·행정</t>
+        </is>
+      </c>
+      <c r="J51" s="8" t="inlineStr">
+        <is>
+          <t>ETC-04 이동·외근</t>
+        </is>
+      </c>
+      <c r="K51" s="8" t="inlineStr">
+        <is>
+          <t>부산 → 사무실 복귀 이동</t>
+        </is>
+      </c>
       <c r="L51" s="8" t="n"/>
       <c r="M51" s="8" t="n"/>
       <c r="O51" s="8" t="n"/>
       <c r="P51" s="8" t="n"/>
       <c r="Q51" s="8" t="n"/>
-      <c r="R51" s="8" t="n"/>
-      <c r="S51" s="8" t="n"/>
-      <c r="T51" s="8" t="n"/>
-      <c r="U51" s="8" t="n"/>
+      <c r="R51" s="8" t="inlineStr">
+        <is>
+          <t>분기/비정기</t>
+        </is>
+      </c>
+      <c r="S51" s="8" t="inlineStr">
+        <is>
+          <t>정형(매뉴얼화 가능)</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>아마도 중복</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>인근 대리점 방문 일정 묶어 이동시간 절감</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="n"/>

--- a/worklog/김송희_주간업무일지_20260810-0814.xlsx
+++ b/worklog/김송희_주간업무일지_20260810-0814.xlsx
@@ -2912,7 +2912,7 @@
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>정하</t>
+          <t>용정하</t>
         </is>
       </c>
       <c r="M14" s="8" t="n"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>정하</t>
+          <t>용정하</t>
         </is>
       </c>
       <c r="M15" s="8" t="n"/>
@@ -3680,11 +3680,7 @@
           <t>모여라딜</t>
         </is>
       </c>
-      <c r="J28" s="8" t="inlineStr">
-        <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
-        </is>
-      </c>
+      <c r="J28" s="8" t="n"/>
       <c r="K28" s="43" t="inlineStr">
         <is>
           <t>https://pourstorecrm.web.app/pour-os</t>
@@ -3692,7 +3688,7 @@
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>정하</t>
+          <t>용정하</t>
         </is>
       </c>
       <c r="M28" s="8" t="n"/>
@@ -3893,7 +3889,7 @@
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>채림님 인플루언서 협업마케팅 진행방향 안내 및 진행안 컨펌</t>
+          <t>채림님 인플루언서 협업마케팅 진행방향 안내 및 멘트 컨펌</t>
         </is>
       </c>
       <c r="I31" s="8" t="inlineStr">
@@ -3999,7 +3995,7 @@
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>정하</t>
+          <t>용정하</t>
         </is>
       </c>
       <c r="M32" s="8" t="n"/>
@@ -4061,7 +4057,7 @@
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>본품 외 부자재·안전용품 등 판매 세팅 검토 — 우선순위 재조정으로 보류</t>
+          <t>부자재(롤링독) 판매 세팅 검토 — 우선순위 재조정으로 보류</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
@@ -4070,7 +4066,11 @@
         </is>
       </c>
       <c r="J33" s="8" t="n"/>
-      <c r="K33" s="44" t="n"/>
+      <c r="K33" s="44" t="inlineStr">
+        <is>
+          <t>https://pour-construction-form.pages.dev/pourstore-pricing-dashboard</t>
+        </is>
+      </c>
       <c r="L33" s="8" t="n"/>
       <c r="M33" s="8" t="n"/>
       <c r="N33" s="8" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>대리점(가나랜드·겸남지사)</t>
+          <t>대리점(가나랜드·경남지사)</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="M48" s="8" t="inlineStr">
         <is>
-          <t>가나랜드, 겸남지사</t>
+          <t>가나랜드, 경남지사</t>
         </is>
       </c>
       <c r="N48" s="8" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
-          <t>정하</t>
+          <t>용정하</t>
         </is>
       </c>
       <c r="M52" s="8" t="n"/>
@@ -5876,10 +5876,14 @@
         </is>
       </c>
       <c r="J69" s="8" t="n"/>
-      <c r="L69" s="8" t="n"/>
+      <c r="L69" s="8" t="inlineStr">
+        <is>
+          <t>김성준 공장장</t>
+        </is>
+      </c>
       <c r="M69" s="8" t="inlineStr">
         <is>
-          <t>세이고, 김성준 공장장</t>
+          <t>세이고</t>
         </is>
       </c>
       <c r="N69" s="8" t="inlineStr">
@@ -5960,7 +5964,7 @@
       </c>
       <c r="L70" s="8" t="inlineStr">
         <is>
-          <t>정하</t>
+          <t>용정하</t>
         </is>
       </c>
       <c r="M70" s="8" t="n"/>
@@ -6089,7 +6093,7 @@
       </c>
       <c r="J72" s="8" t="inlineStr">
         <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
+          <t>레뷰, 리뷰플레이스</t>
         </is>
       </c>
       <c r="K72" s="43" t="inlineStr">
@@ -6694,7 +6698,7 @@
         <v>0.375</v>
       </c>
       <c r="D87" s="54" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="E87" s="5">
         <f>IF(OR(C87="",D87=""),"",(D87-C87)*1440)</f>
@@ -6712,12 +6716,12 @@
       </c>
       <c r="H87" s="9" t="inlineStr">
         <is>
-          <t>부산 대리점 방문 이동(사무실 → 부산)</t>
+          <t>부산 대리점 방문 이동(사무실 → 경남지사)</t>
         </is>
       </c>
       <c r="I87" s="8" t="inlineStr">
         <is>
-          <t>대리점(가나랜드·겸남지사)</t>
+          <t>대리점(경남지사)</t>
         </is>
       </c>
       <c r="J87" s="8" t="n"/>
@@ -6756,10 +6760,10 @@
         </is>
       </c>
       <c r="C88" s="54" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="D88" s="54" t="n">
-        <v>0.5</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="E88" s="5">
         <f>IF(OR(C88="",D88=""),"",(D88-C88)*1440)</f>
@@ -6777,19 +6781,19 @@
       </c>
       <c r="H88" s="9" t="inlineStr">
         <is>
-          <t>가나랜드 대리점 방문 미팅 — 판매 현황·요청사항 청취</t>
+          <t>경남지사 방문 미팅 — 판매 현황·요청사항 청취</t>
         </is>
       </c>
       <c r="I88" s="8" t="inlineStr">
         <is>
-          <t>가나랜드</t>
+          <t>경남지사</t>
         </is>
       </c>
       <c r="J88" s="8" t="n"/>
       <c r="L88" s="8" t="n"/>
       <c r="M88" s="8" t="inlineStr">
         <is>
-          <t>가나랜드</t>
+          <t>경남지사</t>
         </is>
       </c>
       <c r="N88" s="8" t="inlineStr">
@@ -6829,10 +6833,10 @@
         </is>
       </c>
       <c r="C89" s="54" t="n">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="D89" s="54" t="n">
         <v>0.5</v>
-      </c>
-      <c r="D89" s="54" t="n">
-        <v>0.5416666666666666</v>
       </c>
       <c r="E89" s="5">
         <f>IF(OR(C89="",D89=""),"",(D89-C89)*1440)</f>
@@ -6840,40 +6844,56 @@
       </c>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>기타·행정</t>
+          <t>파트너·대리점관리</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>ETC-05 휴게·점심</t>
+          <t>PTR-02 대리점·파트너 인터뷰·VOC 수집</t>
         </is>
       </c>
       <c r="H89" s="9" t="inlineStr">
         <is>
-          <t>점심 및 휴게</t>
-        </is>
-      </c>
-      <c r="I89" s="8" t="n"/>
+          <t>경남지사 인터뷰 진행(질문지 기반 VOC 수집)</t>
+        </is>
+      </c>
+      <c r="I89" s="8" t="inlineStr">
+        <is>
+          <t>경남지사</t>
+        </is>
+      </c>
       <c r="J89" s="8" t="n"/>
       <c r="L89" s="8" t="n"/>
-      <c r="M89" s="8" t="n"/>
-      <c r="N89" s="8" t="n"/>
+      <c r="M89" s="8" t="inlineStr">
+        <is>
+          <t>경남지사</t>
+        </is>
+      </c>
+      <c r="N89" s="8" t="inlineStr">
+        <is>
+          <t>인터뷰 기록</t>
+        </is>
+      </c>
       <c r="O89" s="8" t="inlineStr">
         <is>
-          <t>매일</t>
+          <t>분기/비정기</t>
         </is>
       </c>
       <c r="P89" s="8" t="inlineStr">
         <is>
-          <t>정형(매뉴얼화 가능)</t>
+          <t>반정형</t>
         </is>
       </c>
       <c r="Q89" s="8" t="inlineStr">
         <is>
-          <t>예 - 확실히 중복</t>
-        </is>
-      </c>
-      <c r="R89" s="9" t="n"/>
+          <t>모름</t>
+        </is>
+      </c>
+      <c r="R89" s="9" t="inlineStr">
+        <is>
+          <t>인터뷰 VOC를 상품·마케팅 기획 입력값으로 자동 연결</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="19.5" customHeight="1" s="26">
       <c r="A90" s="53">
@@ -6886,10 +6906,10 @@
         </is>
       </c>
       <c r="C90" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D90" s="54" t="n">
         <v>0.5416666666666666</v>
-      </c>
-      <c r="D90" s="54" t="n">
-        <v>0.6041666666666666</v>
       </c>
       <c r="E90" s="5">
         <f>IF(OR(C90="",D90=""),"",(D90-C90)*1440)</f>
@@ -6897,56 +6917,40 @@
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>파트너·대리점관리</t>
+          <t>기타·행정</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>PTR-02 대리점·파트너 인터뷰·VOC 수집</t>
+          <t>ETC-05 휴게·점심</t>
         </is>
       </c>
       <c r="H90" s="9" t="inlineStr">
         <is>
-          <t>가나랜드 인터뷰 진행 및 현장 촬영(질문지 기반 VOC 수집)</t>
-        </is>
-      </c>
-      <c r="I90" s="8" t="inlineStr">
-        <is>
-          <t>가나랜드</t>
-        </is>
-      </c>
+          <t>점심 및 휴게</t>
+        </is>
+      </c>
+      <c r="I90" s="8" t="n"/>
       <c r="J90" s="8" t="n"/>
       <c r="L90" s="8" t="n"/>
-      <c r="M90" s="8" t="inlineStr">
-        <is>
-          <t>가나랜드</t>
-        </is>
-      </c>
-      <c r="N90" s="8" t="inlineStr">
-        <is>
-          <t>인터뷰 기록·현장 촬영물</t>
-        </is>
-      </c>
+      <c r="M90" s="8" t="n"/>
+      <c r="N90" s="8" t="n"/>
       <c r="O90" s="8" t="inlineStr">
         <is>
-          <t>분기/비정기</t>
+          <t>매일</t>
         </is>
       </c>
       <c r="P90" s="8" t="inlineStr">
         <is>
-          <t>반정형</t>
+          <t>정형(매뉴얼화 가능)</t>
         </is>
       </c>
       <c r="Q90" s="8" t="inlineStr">
         <is>
-          <t>모름</t>
-        </is>
-      </c>
-      <c r="R90" s="9" t="inlineStr">
-        <is>
-          <t>인터뷰 VOC를 상품·마케팅 기획 입력값으로 자동 연결</t>
-        </is>
-      </c>
+          <t>예 - 확실히 중복</t>
+        </is>
+      </c>
+      <c r="R90" s="9" t="n"/>
     </row>
     <row r="91" ht="19.5" customHeight="1" s="26">
       <c r="A91" s="53">
@@ -6959,10 +6963,10 @@
         </is>
       </c>
       <c r="C91" s="54" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="D91" s="54" t="n">
-        <v>0.625</v>
+        <v>0.5625</v>
       </c>
       <c r="E91" s="5">
         <f>IF(OR(C91="",D91=""),"",(D91-C91)*1440)</f>
@@ -6980,12 +6984,12 @@
       </c>
       <c r="H91" s="9" t="inlineStr">
         <is>
-          <t>가나랜드 → 겸남지사 이동</t>
+          <t>경남지사 → 가나랜드 이동</t>
         </is>
       </c>
       <c r="I91" s="8" t="inlineStr">
         <is>
-          <t>대리점(겸남지사)</t>
+          <t>대리점(가나랜드)</t>
         </is>
       </c>
       <c r="J91" s="8" t="n"/>
@@ -7024,10 +7028,10 @@
         </is>
       </c>
       <c r="C92" s="54" t="n">
-        <v>0.625</v>
+        <v>0.5625</v>
       </c>
       <c r="D92" s="54" t="n">
-        <v>0.6875</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="E92" s="5">
         <f>IF(OR(C92="",D92=""),"",(D92-C92)*1440)</f>
@@ -7045,24 +7049,24 @@
       </c>
       <c r="H92" s="9" t="inlineStr">
         <is>
-          <t>겸남지사 방문 미팅 및 인터뷰 진행</t>
+          <t>가나랜드 방문 미팅 — 판매 현황·요청사항 청취</t>
         </is>
       </c>
       <c r="I92" s="8" t="inlineStr">
         <is>
-          <t>겸남지사</t>
+          <t>가나랜드</t>
         </is>
       </c>
       <c r="J92" s="8" t="n"/>
       <c r="L92" s="8" t="n"/>
       <c r="M92" s="8" t="inlineStr">
         <is>
-          <t>겸남지사</t>
+          <t>가나랜드</t>
         </is>
       </c>
       <c r="N92" s="8" t="inlineStr">
         <is>
-          <t>방문 미팅·인터뷰 기록</t>
+          <t>방문 미팅 기록</t>
         </is>
       </c>
       <c r="O92" s="8" t="inlineStr">
@@ -7097,10 +7101,10 @@
         </is>
       </c>
       <c r="C93" s="54" t="n">
-        <v>0.6875</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="D93" s="54" t="n">
-        <v>0.75</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E93" s="5">
         <f>IF(OR(C93="",D93=""),"",(D93-C93)*1440)</f>
@@ -7108,24 +7112,36 @@
       </c>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>기타·행정</t>
+          <t>파트너·대리점관리</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>ETC-04 이동·외근</t>
+          <t>PTR-02 대리점·파트너 인터뷰·VOC 수집</t>
         </is>
       </c>
       <c r="H93" s="9" t="inlineStr">
         <is>
-          <t>부산 → 사무실 복귀 이동</t>
-        </is>
-      </c>
-      <c r="I93" s="8" t="n"/>
+          <t>가나랜드 인터뷰 진행 및 현장 촬영(질문지 기반 VOC 수집)</t>
+        </is>
+      </c>
+      <c r="I93" s="8" t="inlineStr">
+        <is>
+          <t>가나랜드</t>
+        </is>
+      </c>
       <c r="J93" s="8" t="n"/>
       <c r="L93" s="8" t="n"/>
-      <c r="M93" s="8" t="n"/>
-      <c r="N93" s="8" t="n"/>
+      <c r="M93" s="8" t="inlineStr">
+        <is>
+          <t>가나랜드</t>
+        </is>
+      </c>
+      <c r="N93" s="8" t="inlineStr">
+        <is>
+          <t>인터뷰 기록·현장 촬영물</t>
+        </is>
+      </c>
       <c r="O93" s="8" t="inlineStr">
         <is>
           <t>분기/비정기</t>
@@ -7133,17 +7149,17 @@
       </c>
       <c r="P93" s="8" t="inlineStr">
         <is>
-          <t>정형(매뉴얼화 가능)</t>
+          <t>반정형</t>
         </is>
       </c>
       <c r="Q93" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
+          <t>모름</t>
         </is>
       </c>
       <c r="R93" s="9" t="inlineStr">
         <is>
-          <t>인근 대리점 방문 일정 묶어 이동시간 절감</t>
+          <t>인터뷰 VOC를 상품·마케팅 기획 입력값으로 자동 연결</t>
         </is>
       </c>
     </row>
@@ -7157,24 +7173,56 @@
           <t>금</t>
         </is>
       </c>
-      <c r="C94" s="54" t="n"/>
-      <c r="D94" s="54" t="n"/>
+      <c r="C94" s="54" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="D94" s="54" t="n">
+        <v>0.75</v>
+      </c>
       <c r="E94" s="5">
         <f>IF(OR(C94="",D94=""),"",(D94-C94)*1440)</f>
         <v/>
       </c>
-      <c r="F94" s="8" t="n"/>
-      <c r="G94" s="8" t="n"/>
-      <c r="H94" s="9" t="n"/>
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>기타·행정</t>
+        </is>
+      </c>
+      <c r="G94" s="8" t="inlineStr">
+        <is>
+          <t>ETC-04 이동·외근</t>
+        </is>
+      </c>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>부산 → 사무실 복귀 이동</t>
+        </is>
+      </c>
       <c r="I94" s="8" t="n"/>
       <c r="J94" s="8" t="n"/>
       <c r="L94" s="8" t="n"/>
       <c r="M94" s="8" t="n"/>
       <c r="N94" s="8" t="n"/>
-      <c r="O94" s="8" t="n"/>
-      <c r="P94" s="8" t="n"/>
-      <c r="Q94" s="8" t="n"/>
-      <c r="R94" s="9" t="n"/>
+      <c r="O94" s="8" t="inlineStr">
+        <is>
+          <t>분기/비정기</t>
+        </is>
+      </c>
+      <c r="P94" s="8" t="inlineStr">
+        <is>
+          <t>정형(매뉴얼화 가능)</t>
+        </is>
+      </c>
+      <c r="Q94" s="8" t="inlineStr">
+        <is>
+          <t>아마도 중복</t>
+        </is>
+      </c>
+      <c r="R94" s="9" t="inlineStr">
+        <is>
+          <t>인근 대리점 방문 일정 묶어 이동시간 절감</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="19.5" customHeight="1" s="26">
       <c r="A95" s="53">
@@ -8481,7 +8529,7 @@
       </c>
       <c r="O10" s="8" t="inlineStr">
         <is>
-          <t>정하</t>
+          <t>용정하</t>
         </is>
       </c>
       <c r="P10" s="8" t="n"/>
@@ -8577,7 +8625,7 @@
       </c>
       <c r="O11" s="8" t="inlineStr">
         <is>
-          <t>정하</t>
+          <t>용정하</t>
         </is>
       </c>
       <c r="P11" s="8" t="n"/>
@@ -9139,11 +9187,7 @@
           <t>모여라딜</t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr">
-        <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
-        </is>
-      </c>
+      <c r="M17" s="8" t="n"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>https://pourstorecrm.web.app/pour-os</t>
@@ -9151,7 +9195,7 @@
       </c>
       <c r="O17" s="8" t="inlineStr">
         <is>
-          <t>정하</t>
+          <t>용정하</t>
         </is>
       </c>
       <c r="P17" s="8" t="n"/>
@@ -9394,7 +9438,7 @@
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>채림님 인플루언서 협업마케팅 진행방향 안내 및 진행안 컨펌</t>
+          <t>채림님 인플루언서 협업마케팅 진행방향 안내 및 멘트 컨펌</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
@@ -9514,7 +9558,7 @@
       </c>
       <c r="O21" s="8" t="inlineStr">
         <is>
-          <t>정하</t>
+          <t>용정하</t>
         </is>
       </c>
       <c r="P21" s="8" t="n"/>
@@ -9590,7 +9634,7 @@
       </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
-          <t>본품 외 부자재·안전용품 등 판매 세팅 검토 — 우선순위 재조정으로 보류</t>
+          <t>부자재(롤링독) 판매 세팅 검토 — 우선순위 재조정으로 보류</t>
         </is>
       </c>
       <c r="L22" s="8" t="inlineStr">
@@ -9599,6 +9643,11 @@
         </is>
       </c>
       <c r="M22" s="8" t="n"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>https://pour-construction-form.pages.dev/pourstore-pricing-dashboard</t>
+        </is>
+      </c>
       <c r="O22" s="8" t="n"/>
       <c r="P22" s="8" t="n"/>
       <c r="Q22" s="8" t="inlineStr">
@@ -9953,7 +10002,7 @@
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>대리점(가나랜드·겸남지사)</t>
+          <t>대리점(가나랜드·경남지사)</t>
         </is>
       </c>
       <c r="M26" s="8" t="inlineStr">
@@ -9973,7 +10022,7 @@
       </c>
       <c r="P26" s="8" t="inlineStr">
         <is>
-          <t>가나랜드, 겸남지사</t>
+          <t>가나랜드, 경남지사</t>
         </is>
       </c>
       <c r="Q26" s="8" t="inlineStr">
@@ -10322,7 +10371,7 @@
       </c>
       <c r="O30" s="8" t="inlineStr">
         <is>
-          <t>정하</t>
+          <t>용정하</t>
         </is>
       </c>
       <c r="P30" s="8" t="n"/>
@@ -11048,10 +11097,14 @@
         </is>
       </c>
       <c r="M38" s="8" t="n"/>
-      <c r="O38" s="8" t="n"/>
+      <c r="O38" s="8" t="inlineStr">
+        <is>
+          <t>김성준 공장장</t>
+        </is>
+      </c>
       <c r="P38" s="8" t="inlineStr">
         <is>
-          <t>세이고, 김성준 공장장</t>
+          <t>세이고</t>
         </is>
       </c>
       <c r="Q38" s="8" t="inlineStr">
@@ -11146,7 +11199,7 @@
       </c>
       <c r="O39" s="8" t="inlineStr">
         <is>
-          <t>정하</t>
+          <t>용정하</t>
         </is>
       </c>
       <c r="P39" s="8" t="n"/>
@@ -11303,7 +11356,7 @@
       </c>
       <c r="M41" s="8" t="inlineStr">
         <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
+          <t>레뷰, 리뷰플레이스</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -11645,7 +11698,7 @@
         <v>0.375</v>
       </c>
       <c r="G45" s="58" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="H45" s="7">
         <f>IF(OR(F45="",G45=""),"",(G45-F45)*1440)</f>
@@ -11663,12 +11716,12 @@
       </c>
       <c r="K45" s="8" t="inlineStr">
         <is>
-          <t>부산 대리점 방문 이동(사무실 → 부산)</t>
+          <t>부산 대리점 방문 이동(사무실 → 경남지사)</t>
         </is>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
-          <t>대리점(가나랜드·겸남지사)</t>
+          <t>대리점(경남지사)</t>
         </is>
       </c>
       <c r="M45" s="8" t="n"/>
@@ -11721,10 +11774,10 @@
         </is>
       </c>
       <c r="F46" s="58" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="G46" s="58" t="n">
-        <v>0.5</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="H46" s="7">
         <f>IF(OR(F46="",G46=""),"",(G46-F46)*1440)</f>
@@ -11742,19 +11795,19 @@
       </c>
       <c r="K46" s="8" t="inlineStr">
         <is>
-          <t>가나랜드 대리점 방문 미팅 — 판매 현황·요청사항 청취</t>
+          <t>경남지사 방문 미팅 — 판매 현황·요청사항 청취</t>
         </is>
       </c>
       <c r="L46" s="8" t="inlineStr">
         <is>
-          <t>가나랜드</t>
+          <t>경남지사</t>
         </is>
       </c>
       <c r="M46" s="8" t="n"/>
       <c r="O46" s="8" t="n"/>
       <c r="P46" s="8" t="inlineStr">
         <is>
-          <t>가나랜드</t>
+          <t>경남지사</t>
         </is>
       </c>
       <c r="Q46" s="8" t="inlineStr">
@@ -11808,10 +11861,10 @@
         </is>
       </c>
       <c r="F47" s="58" t="n">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="G47" s="58" t="n">
         <v>0.5</v>
-      </c>
-      <c r="G47" s="58" t="n">
-        <v>0.5416666666666666</v>
       </c>
       <c r="H47" s="7">
         <f>IF(OR(F47="",G47=""),"",(G47-F47)*1440)</f>
@@ -11819,40 +11872,56 @@
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>기타·행정</t>
+          <t>파트너·대리점관리</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>ETC-05 휴게·점심</t>
+          <t>PTR-02 대리점·파트너 인터뷰·VOC 수집</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>점심 및 휴게</t>
-        </is>
-      </c>
-      <c r="L47" s="8" t="n"/>
+          <t>경남지사 인터뷰 진행(질문지 기반 VOC 수집)</t>
+        </is>
+      </c>
+      <c r="L47" s="8" t="inlineStr">
+        <is>
+          <t>경남지사</t>
+        </is>
+      </c>
       <c r="M47" s="8" t="n"/>
       <c r="O47" s="8" t="n"/>
-      <c r="P47" s="8" t="n"/>
-      <c r="Q47" s="8" t="n"/>
+      <c r="P47" s="8" t="inlineStr">
+        <is>
+          <t>경남지사</t>
+        </is>
+      </c>
+      <c r="Q47" s="8" t="inlineStr">
+        <is>
+          <t>인터뷰 기록</t>
+        </is>
+      </c>
       <c r="R47" s="8" t="inlineStr">
         <is>
-          <t>매일</t>
+          <t>분기/비정기</t>
         </is>
       </c>
       <c r="S47" s="8" t="inlineStr">
         <is>
-          <t>정형(매뉴얼화 가능)</t>
+          <t>반정형</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>예 - 확실히 중복</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="n"/>
+          <t>모름</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>인터뷰 VOC를 상품·마케팅 기획 입력값으로 자동 연결</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
@@ -11879,10 +11948,10 @@
         </is>
       </c>
       <c r="F48" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G48" s="58" t="n">
         <v>0.5416666666666666</v>
-      </c>
-      <c r="G48" s="58" t="n">
-        <v>0.6041666666666666</v>
       </c>
       <c r="H48" s="7">
         <f>IF(OR(F48="",G48=""),"",(G48-F48)*1440)</f>
@@ -11890,56 +11959,40 @@
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>파트너·대리점관리</t>
+          <t>기타·행정</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
-          <t>PTR-02 대리점·파트너 인터뷰·VOC 수집</t>
+          <t>ETC-05 휴게·점심</t>
         </is>
       </c>
       <c r="K48" s="8" t="inlineStr">
         <is>
-          <t>가나랜드 인터뷰 진행 및 현장 촬영(질문지 기반 VOC 수집)</t>
-        </is>
-      </c>
-      <c r="L48" s="8" t="inlineStr">
-        <is>
-          <t>가나랜드</t>
-        </is>
-      </c>
+          <t>점심 및 휴게</t>
+        </is>
+      </c>
+      <c r="L48" s="8" t="n"/>
       <c r="M48" s="8" t="n"/>
       <c r="O48" s="8" t="n"/>
-      <c r="P48" s="8" t="inlineStr">
-        <is>
-          <t>가나랜드</t>
-        </is>
-      </c>
-      <c r="Q48" s="8" t="inlineStr">
-        <is>
-          <t>인터뷰 기록·현장 촬영물</t>
-        </is>
-      </c>
+      <c r="P48" s="8" t="n"/>
+      <c r="Q48" s="8" t="n"/>
       <c r="R48" s="8" t="inlineStr">
         <is>
-          <t>분기/비정기</t>
+          <t>매일</t>
         </is>
       </c>
       <c r="S48" s="8" t="inlineStr">
         <is>
-          <t>반정형</t>
+          <t>정형(매뉴얼화 가능)</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>모름</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>인터뷰 VOC를 상품·마케팅 기획 입력값으로 자동 연결</t>
-        </is>
-      </c>
+          <t>예 - 확실히 중복</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -11966,10 +12019,10 @@
         </is>
       </c>
       <c r="F49" s="58" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="G49" s="58" t="n">
-        <v>0.625</v>
+        <v>0.5625</v>
       </c>
       <c r="H49" s="7">
         <f>IF(OR(F49="",G49=""),"",(G49-F49)*1440)</f>
@@ -11987,12 +12040,12 @@
       </c>
       <c r="K49" s="8" t="inlineStr">
         <is>
-          <t>가나랜드 → 겸남지사 이동</t>
+          <t>경남지사 → 가나랜드 이동</t>
         </is>
       </c>
       <c r="L49" s="8" t="inlineStr">
         <is>
-          <t>대리점(겸남지사)</t>
+          <t>대리점(가나랜드)</t>
         </is>
       </c>
       <c r="M49" s="8" t="n"/>
@@ -12045,10 +12098,10 @@
         </is>
       </c>
       <c r="F50" s="58" t="n">
-        <v>0.625</v>
+        <v>0.5625</v>
       </c>
       <c r="G50" s="58" t="n">
-        <v>0.6875</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="H50" s="7">
         <f>IF(OR(F50="",G50=""),"",(G50-F50)*1440)</f>
@@ -12066,24 +12119,24 @@
       </c>
       <c r="K50" s="8" t="inlineStr">
         <is>
-          <t>겸남지사 방문 미팅 및 인터뷰 진행</t>
+          <t>가나랜드 방문 미팅 — 판매 현황·요청사항 청취</t>
         </is>
       </c>
       <c r="L50" s="8" t="inlineStr">
         <is>
-          <t>겸남지사</t>
+          <t>가나랜드</t>
         </is>
       </c>
       <c r="M50" s="8" t="n"/>
       <c r="O50" s="8" t="n"/>
       <c r="P50" s="8" t="inlineStr">
         <is>
-          <t>겸남지사</t>
+          <t>가나랜드</t>
         </is>
       </c>
       <c r="Q50" s="8" t="inlineStr">
         <is>
-          <t>방문 미팅·인터뷰 기록</t>
+          <t>방문 미팅 기록</t>
         </is>
       </c>
       <c r="R50" s="8" t="inlineStr">
@@ -12132,10 +12185,10 @@
         </is>
       </c>
       <c r="F51" s="58" t="n">
-        <v>0.6875</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="G51" s="58" t="n">
-        <v>0.75</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H51" s="7">
         <f>IF(OR(F51="",G51=""),"",(G51-F51)*1440)</f>
@@ -12143,24 +12196,36 @@
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>기타·행정</t>
+          <t>파트너·대리점관리</t>
         </is>
       </c>
       <c r="J51" s="8" t="inlineStr">
         <is>
-          <t>ETC-04 이동·외근</t>
+          <t>PTR-02 대리점·파트너 인터뷰·VOC 수집</t>
         </is>
       </c>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>부산 → 사무실 복귀 이동</t>
-        </is>
-      </c>
-      <c r="L51" s="8" t="n"/>
+          <t>가나랜드 인터뷰 진행 및 현장 촬영(질문지 기반 VOC 수집)</t>
+        </is>
+      </c>
+      <c r="L51" s="8" t="inlineStr">
+        <is>
+          <t>가나랜드</t>
+        </is>
+      </c>
       <c r="M51" s="8" t="n"/>
       <c r="O51" s="8" t="n"/>
-      <c r="P51" s="8" t="n"/>
-      <c r="Q51" s="8" t="n"/>
+      <c r="P51" s="8" t="inlineStr">
+        <is>
+          <t>가나랜드</t>
+        </is>
+      </c>
+      <c r="Q51" s="8" t="inlineStr">
+        <is>
+          <t>인터뷰 기록·현장 촬영물</t>
+        </is>
+      </c>
       <c r="R51" s="8" t="inlineStr">
         <is>
           <t>분기/비정기</t>
@@ -12168,44 +12233,94 @@
       </c>
       <c r="S51" s="8" t="inlineStr">
         <is>
-          <t>정형(매뉴얼화 가능)</t>
+          <t>반정형</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
+          <t>모름</t>
         </is>
       </c>
       <c r="U51" s="8" t="inlineStr">
         <is>
-          <t>인근 대리점 방문 일정 묶어 이동시간 절감</t>
+          <t>인터뷰 VOC를 상품·마케팅 기획 입력값으로 자동 연결</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="n"/>
-      <c r="B52" s="8" t="n"/>
-      <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
-      <c r="E52" s="8" t="n"/>
-      <c r="F52" s="8" t="n"/>
-      <c r="G52" s="8" t="n"/>
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>브랜드커머스</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>김송희</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>브랜드커머스, 모여라딜 리드</t>
+        </is>
+      </c>
+      <c r="D52" s="57" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="F52" s="58" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G52" s="58" t="n">
+        <v>0.75</v>
+      </c>
       <c r="H52" s="7">
         <f>IF(OR(F52="",G52=""),"",(G52-F52)*1440)</f>
         <v/>
       </c>
-      <c r="I52" s="8" t="n"/>
-      <c r="J52" s="8" t="n"/>
-      <c r="K52" s="8" t="n"/>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>기타·행정</t>
+        </is>
+      </c>
+      <c r="J52" s="8" t="inlineStr">
+        <is>
+          <t>ETC-04 이동·외근</t>
+        </is>
+      </c>
+      <c r="K52" s="8" t="inlineStr">
+        <is>
+          <t>부산 → 사무실 복귀 이동</t>
+        </is>
+      </c>
       <c r="L52" s="8" t="n"/>
       <c r="M52" s="8" t="n"/>
       <c r="O52" s="8" t="n"/>
       <c r="P52" s="8" t="n"/>
       <c r="Q52" s="8" t="n"/>
-      <c r="R52" s="8" t="n"/>
-      <c r="S52" s="8" t="n"/>
-      <c r="T52" s="8" t="n"/>
-      <c r="U52" s="8" t="n"/>
+      <c r="R52" s="8" t="inlineStr">
+        <is>
+          <t>분기/비정기</t>
+        </is>
+      </c>
+      <c r="S52" s="8" t="inlineStr">
+        <is>
+          <t>정형(매뉴얼화 가능)</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>아마도 중복</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>인근 대리점 방문 일정 묶어 이동시간 절감</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n"/>

--- a/worklog/김송희_주간업무일지_20260810-0814.xlsx
+++ b/worklog/김송희_주간업무일지_20260810-0814.xlsx
@@ -2474,11 +2474,7 @@
           <t>예 - 확실히 중복</t>
         </is>
       </c>
-      <c r="R8" s="9" t="inlineStr">
-        <is>
-          <t>채널별 주문을 통합 주문판으로 자동 취합</t>
-        </is>
-      </c>
+      <c r="R8" s="9" t="n"/>
     </row>
     <row r="9" ht="19.5" customHeight="1" s="26">
       <c r="A9" s="53">
@@ -2597,16 +2593,8 @@
           <t>POUR스토어</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
-        </is>
-      </c>
-      <c r="K10" s="43" t="inlineStr">
-        <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
-        </is>
-      </c>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="43" t="n"/>
       <c r="L10" s="8" t="inlineStr">
         <is>
           <t>김민지</t>
@@ -2679,16 +2667,8 @@
           <t>대리점(가나랜드·경남지사)</t>
         </is>
       </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
-        </is>
-      </c>
-      <c r="K11" s="43" t="inlineStr">
-        <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
-        </is>
-      </c>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="43" t="n"/>
       <c r="L11" s="8" t="inlineStr">
         <is>
           <t>이란</t>
@@ -2715,11 +2695,7 @@
           <t>모름</t>
         </is>
       </c>
-      <c r="R11" s="9" t="inlineStr">
-        <is>
-          <t>대리점 인터뷰 질문지 표준 템플릿화</t>
-        </is>
-      </c>
+      <c r="R11" s="9" t="n"/>
     </row>
     <row r="12" ht="19.5" customHeight="1" s="26">
       <c r="A12" s="53">
@@ -3018,11 +2994,7 @@
           <t>모름</t>
         </is>
       </c>
-      <c r="R15" s="9" t="inlineStr">
-        <is>
-          <t>개선 요청·피드백 이력을 앱 내 이슈보드로 관리해 재설명 시간 제거</t>
-        </is>
-      </c>
+      <c r="R15" s="9" t="n"/>
     </row>
     <row r="16" ht="19.5" customHeight="1" s="26">
       <c r="A16" s="53">
@@ -3099,11 +3071,7 @@
           <t>예 - 확실히 중복</t>
         </is>
       </c>
-      <c r="R16" s="9" t="inlineStr">
-        <is>
-          <t>상품 마스터 DB 기준 채널 자동 등록</t>
-        </is>
-      </c>
+      <c r="R16" s="9" t="n"/>
     </row>
     <row r="17" ht="19.5" customHeight="1" s="26">
       <c r="A17" s="53">
@@ -3145,16 +3113,8 @@
           <t>신제품 4종</t>
         </is>
       </c>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
-        </is>
-      </c>
-      <c r="K17" s="43" t="inlineStr">
-        <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
-        </is>
-      </c>
+      <c r="J17" s="8" t="n"/>
+      <c r="K17" s="43" t="n"/>
       <c r="L17" s="8" t="inlineStr">
         <is>
           <t>양채림</t>
@@ -3205,7 +3165,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="D18" s="54" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6875</v>
       </c>
       <c r="E18" s="5">
         <f>IF(OR(C18="",D18=""),"",(D18-C18)*1440)</f>
@@ -3279,10 +3239,10 @@
         </is>
       </c>
       <c r="C19" s="54" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="D19" s="54" t="n">
         <v>0.7083333333333334</v>
-      </c>
-      <c r="D19" s="54" t="n">
-        <v>0.75</v>
       </c>
       <c r="E19" s="5">
         <f>IF(OR(C19="",D19=""),"",(D19-C19)*1440)</f>
@@ -3290,67 +3250,58 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>마케팅·광고운영</t>
+          <t>콘텐츠제작</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>MKT-04 인플루언서·체험단 섭외/관리</t>
+          <t>CNT-06 디자인 시안 피드백</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>퍼포먼스마케팅 인플루언서/셀러 협업 현황 확인 및 컨택 방안 피드백(채림님께)</t>
+          <t>대리점 경남지사 명함디자인 컨펌 승인</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>POUR스토어</t>
-        </is>
-      </c>
-      <c r="J19" s="8" t="inlineStr">
-        <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
-        </is>
-      </c>
+          <t>대리점(경남지사)</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="n"/>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>양채림</t>
+          <t>이란</t>
         </is>
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t>인플루언서·셀러</t>
+          <t>경남지사</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>협업 컨택 방안 피드백</t>
+          <t>명함 디자인 컨펌</t>
         </is>
       </c>
       <c r="O19" s="8" t="inlineStr">
         <is>
-          <t>주 1회</t>
+          <t>1회성</t>
         </is>
       </c>
       <c r="P19" s="8" t="inlineStr">
         <is>
-          <t>비정형(판단 필요)</t>
+          <t>반정형</t>
         </is>
       </c>
       <c r="Q19" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
+          <t>모름</t>
         </is>
       </c>
       <c r="R19" s="9" t="inlineStr">
         <is>
-          <t>인플루언서/셀러 컨택 이력 DB 공용화(중복 컨택 방지)</t>
+          <t>대리점 인쇄물 디자인 템플릿 표준화</t>
         </is>
       </c>
     </row>
@@ -3364,29 +3315,73 @@
           <t>월</t>
         </is>
       </c>
-      <c r="C20" s="54" t="n"/>
-      <c r="D20" s="54" t="n"/>
+      <c r="C20" s="54" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="D20" s="54" t="n">
+        <v>0.75</v>
+      </c>
       <c r="E20" s="5">
         <f>IF(OR(C20="",D20=""),"",(D20-C20)*1440)</f>
         <v/>
       </c>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="9" t="n"/>
-      <c r="I20" s="8" t="n"/>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>마케팅·광고운영</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>MKT-04 인플루언서·체험단 섭외/관리</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>퍼포먼스마케팅 인플루언서/셀러 협업 현황 확인 및 컨택 방안 피드백(채림님께)</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>POUR스토어</t>
+        </is>
+      </c>
       <c r="J20" s="8" t="n"/>
-      <c r="K20" s="43" t="inlineStr">
-        <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
-        </is>
-      </c>
-      <c r="L20" s="8" t="n"/>
-      <c r="M20" s="8" t="n"/>
-      <c r="N20" s="8" t="n"/>
-      <c r="O20" s="8" t="n"/>
-      <c r="P20" s="8" t="n"/>
-      <c r="Q20" s="8" t="n"/>
-      <c r="R20" s="9" t="n"/>
+      <c r="K20" s="43" t="n"/>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t>양채림</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t>인플루언서·셀러</t>
+        </is>
+      </c>
+      <c r="N20" s="8" t="inlineStr">
+        <is>
+          <t>협업 컨택 방안 피드백</t>
+        </is>
+      </c>
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>주 1회</t>
+        </is>
+      </c>
+      <c r="P20" s="8" t="inlineStr">
+        <is>
+          <t>비정형(판단 필요)</t>
+        </is>
+      </c>
+      <c r="Q20" s="8" t="inlineStr">
+        <is>
+          <t>아마도 중복</t>
+        </is>
+      </c>
+      <c r="R20" s="9" t="inlineStr">
+        <is>
+          <t>인플루언서/셀러 컨택 이력 DB 공용화(중복 컨택 방지)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="19.5" customHeight="1" s="26">
       <c r="A21" s="53">
@@ -3654,7 +3649,7 @@
         <v>0.3958333333333333</v>
       </c>
       <c r="D28" s="54" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="E28" s="5">
         <f>IF(OR(C28="",D28=""),"",(D28-C28)*1440)</f>
@@ -3729,10 +3724,10 @@
         </is>
       </c>
       <c r="C29" s="54" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="D29" s="54" t="n">
-        <v>0.5</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="E29" s="5">
         <f>IF(OR(C29="",D29=""),"",(D29-C29)*1440)</f>
@@ -3811,10 +3806,10 @@
         </is>
       </c>
       <c r="C30" s="54" t="n">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="D30" s="54" t="n">
         <v>0.5</v>
-      </c>
-      <c r="D30" s="54" t="n">
-        <v>0.5416666666666666</v>
       </c>
       <c r="E30" s="5">
         <f>IF(OR(C30="",D30=""),"",(D30-C30)*1440)</f>
@@ -3822,40 +3817,56 @@
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>기타·행정</t>
+          <t>콘텐츠제작</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>ETC-05 휴게·점심</t>
+          <t>CNT-04 카피·문구 작성</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>점심 및 휴게</t>
-        </is>
-      </c>
-      <c r="I30" s="8" t="n"/>
+          <t>관리주체 안내 멘트 컨펌 승인</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>POUR스토어</t>
+        </is>
+      </c>
       <c r="J30" s="8" t="n"/>
-      <c r="L30" s="8" t="n"/>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>이란</t>
+        </is>
+      </c>
       <c r="M30" s="8" t="n"/>
-      <c r="N30" s="8" t="n"/>
+      <c r="N30" s="8" t="inlineStr">
+        <is>
+          <t>안내 멘트 컨펌</t>
+        </is>
+      </c>
       <c r="O30" s="8" t="inlineStr">
         <is>
-          <t>매일</t>
+          <t>1회성</t>
         </is>
       </c>
       <c r="P30" s="8" t="inlineStr">
         <is>
-          <t>정형(매뉴얼화 가능)</t>
+          <t>반정형</t>
         </is>
       </c>
       <c r="Q30" s="8" t="inlineStr">
         <is>
-          <t>예 - 확실히 중복</t>
-        </is>
-      </c>
-      <c r="R30" s="9" t="n"/>
+          <t>모름</t>
+        </is>
+      </c>
+      <c r="R30" s="9" t="inlineStr">
+        <is>
+          <t>고객 안내 멘트 표준 문구집 관리</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="26">
       <c r="A31" s="53">
@@ -3868,10 +3879,10 @@
         </is>
       </c>
       <c r="C31" s="54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D31" s="54" t="n">
         <v>0.5416666666666666</v>
-      </c>
-      <c r="D31" s="54" t="n">
-        <v>0.5833333333333334</v>
       </c>
       <c r="E31" s="5">
         <f>IF(OR(C31="",D31=""),"",(D31-C31)*1440)</f>
@@ -3879,69 +3890,41 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>마케팅·광고운영</t>
+          <t>기타·행정</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>MKT-04 인플루언서·체험단 섭외/관리</t>
+          <t>ETC-05 휴게·점심</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>채림님 인플루언서 협업마케팅 진행방향 안내 및 멘트 컨펌</t>
-        </is>
-      </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>POUR스토어</t>
-        </is>
-      </c>
-      <c r="J31" s="8" t="inlineStr">
-        <is>
-          <t>레뷰, 리뷰플레이스</t>
-        </is>
-      </c>
-      <c r="K31" s="44" t="inlineStr">
-        <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
-        </is>
-      </c>
-      <c r="L31" s="8" t="inlineStr">
-        <is>
-          <t>양채림</t>
-        </is>
-      </c>
-      <c r="M31" s="8" t="inlineStr">
-        <is>
-          <t>인플루언서</t>
-        </is>
-      </c>
-      <c r="N31" s="8" t="inlineStr">
-        <is>
-          <t>협업 진행안 컨펌</t>
-        </is>
-      </c>
+          <t>점심 및 휴게</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="n"/>
+      <c r="J31" s="8" t="n"/>
+      <c r="K31" s="44" t="n"/>
+      <c r="L31" s="8" t="n"/>
+      <c r="M31" s="8" t="n"/>
+      <c r="N31" s="8" t="n"/>
       <c r="O31" s="8" t="inlineStr">
         <is>
-          <t>주 1회</t>
+          <t>매일</t>
         </is>
       </c>
       <c r="P31" s="8" t="inlineStr">
         <is>
-          <t>비정형(판단 필요)</t>
+          <t>정형(매뉴얼화 가능)</t>
         </is>
       </c>
       <c r="Q31" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
-        </is>
-      </c>
-      <c r="R31" s="9" t="inlineStr">
-        <is>
-          <t>인플루언서 협업 진행 기준(가이드) 문서화 후 위임</t>
-        </is>
-      </c>
+          <t>예 - 확실히 중복</t>
+        </is>
+      </c>
+      <c r="R31" s="9" t="n"/>
     </row>
     <row r="32" ht="19.5" customHeight="1" s="26">
       <c r="A32" s="53">
@@ -3954,10 +3937,10 @@
         </is>
       </c>
       <c r="C32" s="54" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="D32" s="54" t="n">
         <v>0.5833333333333334</v>
-      </c>
-      <c r="D32" s="54" t="n">
-        <v>0.625</v>
       </c>
       <c r="E32" s="5">
         <f>IF(OR(C32="",D32=""),"",(D32-C32)*1440)</f>
@@ -3965,48 +3948,52 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>사내시스템·자동화</t>
+          <t>마케팅·광고운영</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>SYS-01 사내 시스템·앱 기획/개선 요청</t>
+          <t>MKT-04 인플루언서·체험단 섭외/관리</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>소싱앱 UX/UI 개선 — 정하님 추가 고도화 건 2차 피드백</t>
+          <t>채림님 인플루언서 협업마케팅 진행방향 안내 및 멘트 컨펌</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>소싱앱</t>
+          <t>POUR스토어</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>소싱앱</t>
+          <t>레뷰, 리뷰플레이스</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>소싱 관리 · 모여라딜 (moyeoradeal-sourcing.pages.dev)</t>
+          <t>https://pourstorecrm.web.app/pour-os</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>용정하</t>
-        </is>
-      </c>
-      <c r="M32" s="8" t="n"/>
+          <t>양채림</t>
+        </is>
+      </c>
+      <c r="M32" s="8" t="inlineStr">
+        <is>
+          <t>인플루언서</t>
+        </is>
+      </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
-          <t>UX/UI 2차 피드백</t>
+          <t>협업 진행안 컨펌</t>
         </is>
       </c>
       <c r="O32" s="8" t="inlineStr">
         <is>
-          <t>주 2~3회</t>
+          <t>주 1회</t>
         </is>
       </c>
       <c r="P32" s="8" t="inlineStr">
@@ -4016,12 +4003,12 @@
       </c>
       <c r="Q32" s="8" t="inlineStr">
         <is>
-          <t>모름</t>
+          <t>아마도 중복</t>
         </is>
       </c>
       <c r="R32" s="9" t="inlineStr">
         <is>
-          <t>개선 요청·피드백 이력을 앱 내 이슈보드로 관리</t>
+          <t>인플루언서 협업 진행 기준(가이드) 문서화 후 위임</t>
         </is>
       </c>
     </row>
@@ -4036,10 +4023,10 @@
         </is>
       </c>
       <c r="C33" s="54" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="D33" s="54" t="n">
         <v>0.625</v>
-      </c>
-      <c r="D33" s="54" t="n">
-        <v>0.6458333333333334</v>
       </c>
       <c r="E33" s="5">
         <f>IF(OR(C33="",D33=""),"",(D33-C33)*1440)</f>
@@ -4047,40 +4034,48 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>상품기획·소싱</t>
+          <t>사내시스템·자동화</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>PLN-01 신상품 아이템 발굴/시장조사</t>
+          <t>SYS-01 사내 시스템·앱 기획/개선 요청</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>부자재(롤링독) 판매 세팅 검토 — 우선순위 재조정으로 보류</t>
+          <t>소싱앱 UX/UI 개선 — 정하님 추가 고도화 건 2차 피드백</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>부자재·안전용품</t>
-        </is>
-      </c>
-      <c r="J33" s="8" t="n"/>
+          <t>소싱앱</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>소싱앱</t>
+        </is>
+      </c>
       <c r="K33" s="44" t="inlineStr">
         <is>
-          <t>https://pour-construction-form.pages.dev/pourstore-pricing-dashboard</t>
-        </is>
-      </c>
-      <c r="L33" s="8" t="n"/>
+          <t>소싱 관리 · 모여라딜 (moyeoradeal-sourcing.pages.dev)</t>
+        </is>
+      </c>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>용정하</t>
+        </is>
+      </c>
       <c r="M33" s="8" t="n"/>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t>판매 세팅 검토안(보류)</t>
+          <t>UX/UI 2차 피드백</t>
         </is>
       </c>
       <c r="O33" s="8" t="inlineStr">
         <is>
-          <t>분기/비정기</t>
+          <t>주 2~3회</t>
         </is>
       </c>
       <c r="P33" s="8" t="inlineStr">
@@ -4090,12 +4085,12 @@
       </c>
       <c r="Q33" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
+          <t>모름</t>
         </is>
       </c>
       <c r="R33" s="9" t="inlineStr">
         <is>
-          <t>부자재 카테고리 소싱 기준 정립 후 일괄 세팅</t>
+          <t>개선 요청·피드백 이력을 앱 내 이슈보드로 관리</t>
         </is>
       </c>
     </row>
@@ -4110,10 +4105,10 @@
         </is>
       </c>
       <c r="C34" s="54" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="D34" s="54" t="n">
         <v>0.6458333333333334</v>
-      </c>
-      <c r="D34" s="54" t="n">
-        <v>0.6875</v>
       </c>
       <c r="E34" s="5">
         <f>IF(OR(C34="",D34=""),"",(D34-C34)*1440)</f>
@@ -4121,44 +4116,39 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>데이터·정산</t>
+          <t>마케팅·광고운영</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>DAT-04 리포트·대시보드 작성</t>
+          <t>MKT-04 인플루언서·체험단 섭외/관리</t>
         </is>
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>POUR스토어 단가·공헌이익·손익계산 대시보드 제작 — 진행중(전주 이월)</t>
+          <t>POUR스토어 자사몰에 체험단모집 진행 컨펌 승인 및 서포터즈 관리진행 요청</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>POUR스토어</t>
-        </is>
-      </c>
-      <c r="J34" s="8" t="inlineStr">
-        <is>
-          <t>단가 대시보드, 엑셀</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>POUR스토어 가격·마진 통합 대시보드 (pour-construction-form.pages.dev)</t>
-        </is>
-      </c>
-      <c r="L34" s="8" t="n"/>
+          <t>POUR스토어 자사몰</t>
+        </is>
+      </c>
+      <c r="J34" s="8" t="n"/>
+      <c r="L34" s="8" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
       <c r="M34" s="8" t="n"/>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>단가·공헌이익·손익 대시보드</t>
+          <t>체험단 모집 컨펌·서포터즈 관리 요청</t>
         </is>
       </c>
       <c r="O34" s="8" t="inlineStr">
         <is>
-          <t>주 2~3회</t>
+          <t>1회성</t>
         </is>
       </c>
       <c r="P34" s="8" t="inlineStr">
@@ -4173,7 +4163,7 @@
       </c>
       <c r="R34" s="9" t="inlineStr">
         <is>
-          <t>채널 수수료·원가 데이터 자동 연동으로 수기 입력 제거</t>
+          <t>체험단·서포터즈 운영 프로세스 문서화</t>
         </is>
       </c>
     </row>
@@ -4188,10 +4178,10 @@
         </is>
       </c>
       <c r="C35" s="54" t="n">
-        <v>0.6875</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="D35" s="54" t="n">
-        <v>0.75</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E35" s="5">
         <f>IF(OR(C35="",D35=""),"",(D35-C35)*1440)</f>
@@ -4199,58 +4189,55 @@
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>제조·생산관리</t>
+          <t>상품기획·소싱</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>MFG-08 MSDS·라벨 등 제품 표시사항 제작</t>
+          <t>PLN-01 신상품 아이템 발굴/시장조사</t>
         </is>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>신제품 코트재 MSDS 컬러별 31개 제작 — 진행중</t>
+          <t>부자재(롤링독) 판매 세팅 검토 — 우선순위 재조정으로 보류</t>
         </is>
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>코트재 신제품 31색</t>
-        </is>
-      </c>
-      <c r="J35" s="8" t="inlineStr">
-        <is>
-          <t>챗지피티</t>
+          <t>부자재·안전용품</t>
+        </is>
+      </c>
+      <c r="J35" s="8" t="n"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>https://pour-construction-form.pages.dev/pourstore-pricing-dashboard</t>
         </is>
       </c>
       <c r="L35" s="8" t="n"/>
-      <c r="M35" s="8" t="inlineStr">
-        <is>
-          <t>세이고, 쿠팡물류센터</t>
-        </is>
-      </c>
+      <c r="M35" s="8" t="n"/>
       <c r="N35" s="8" t="inlineStr">
         <is>
-          <t>MSDS 31종</t>
+          <t>판매 세팅 검토안(보류)</t>
         </is>
       </c>
       <c r="O35" s="8" t="inlineStr">
         <is>
-          <t>1회성</t>
+          <t>분기/비정기</t>
         </is>
       </c>
       <c r="P35" s="8" t="inlineStr">
         <is>
-          <t>반정형</t>
+          <t>비정형(판단 필요)</t>
         </is>
       </c>
       <c r="Q35" s="8" t="inlineStr">
         <is>
-          <t>아니오 - 우리팀 고유</t>
+          <t>아마도 중복</t>
         </is>
       </c>
       <c r="R35" s="9" t="inlineStr">
         <is>
-          <t>품목·색상 데이터 연동으로 MSDS 서식 자동 생성</t>
+          <t>부자재 카테고리 소싱 기준 정립 후 일괄 세팅</t>
         </is>
       </c>
     </row>
@@ -4264,24 +4251,73 @@
           <t>화</t>
         </is>
       </c>
-      <c r="C36" s="54" t="n"/>
-      <c r="D36" s="54" t="n"/>
+      <c r="C36" s="54" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="D36" s="54" t="n">
+        <v>0.7083333333333334</v>
+      </c>
       <c r="E36" s="5">
         <f>IF(OR(C36="",D36=""),"",(D36-C36)*1440)</f>
         <v/>
       </c>
-      <c r="F36" s="8" t="n"/>
-      <c r="G36" s="8" t="n"/>
-      <c r="H36" s="9" t="n"/>
-      <c r="I36" s="8" t="n"/>
-      <c r="J36" s="8" t="n"/>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>데이터·정산</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>DAT-04 리포트·대시보드 작성</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>POUR스토어 단가·공헌이익·손익계산 대시보드 제작 — 진행중(전주 이월)</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>POUR스토어</t>
+        </is>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>단가 대시보드, 엑셀</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>POUR스토어 가격·마진 통합 대시보드 (pour-construction-form.pages.dev)</t>
+        </is>
+      </c>
       <c r="L36" s="8" t="n"/>
       <c r="M36" s="8" t="n"/>
-      <c r="N36" s="8" t="n"/>
-      <c r="O36" s="8" t="n"/>
-      <c r="P36" s="8" t="n"/>
-      <c r="Q36" s="8" t="n"/>
-      <c r="R36" s="9" t="n"/>
+      <c r="N36" s="8" t="inlineStr">
+        <is>
+          <t>단가·공헌이익·손익 대시보드</t>
+        </is>
+      </c>
+      <c r="O36" s="8" t="inlineStr">
+        <is>
+          <t>주 2~3회</t>
+        </is>
+      </c>
+      <c r="P36" s="8" t="inlineStr">
+        <is>
+          <t>비정형(판단 필요)</t>
+        </is>
+      </c>
+      <c r="Q36" s="8" t="inlineStr">
+        <is>
+          <t>아마도 중복</t>
+        </is>
+      </c>
+      <c r="R36" s="9" t="inlineStr">
+        <is>
+          <t>채널 수수료·원가 데이터 자동 연동으로 수기 입력 제거</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="19.5" customHeight="1" s="26">
       <c r="A37" s="53">
@@ -4293,24 +4329,72 @@
           <t>화</t>
         </is>
       </c>
-      <c r="C37" s="54" t="n"/>
-      <c r="D37" s="54" t="n"/>
+      <c r="C37" s="54" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="D37" s="54" t="n">
+        <v>0.75</v>
+      </c>
       <c r="E37" s="5">
         <f>IF(OR(C37="",D37=""),"",(D37-C37)*1440)</f>
         <v/>
       </c>
-      <c r="F37" s="8" t="n"/>
-      <c r="G37" s="8" t="n"/>
-      <c r="H37" s="9" t="n"/>
-      <c r="I37" s="8" t="n"/>
-      <c r="J37" s="8" t="n"/>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>제조·생산관리</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>MFG-08 MSDS·라벨 등 제품 표시사항 제작</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>신제품 코트재 MSDS 컬러별 31개 제작 — 진행중</t>
+        </is>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>코트재 신제품 31색</t>
+        </is>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>챗지피티</t>
+        </is>
+      </c>
       <c r="L37" s="8" t="n"/>
-      <c r="M37" s="8" t="n"/>
-      <c r="N37" s="8" t="n"/>
-      <c r="O37" s="8" t="n"/>
-      <c r="P37" s="8" t="n"/>
-      <c r="Q37" s="8" t="n"/>
-      <c r="R37" s="9" t="n"/>
+      <c r="M37" s="8" t="inlineStr">
+        <is>
+          <t>세이고, 쿠팡물류센터</t>
+        </is>
+      </c>
+      <c r="N37" s="8" t="inlineStr">
+        <is>
+          <t>MSDS 31종</t>
+        </is>
+      </c>
+      <c r="O37" s="8" t="inlineStr">
+        <is>
+          <t>1회성</t>
+        </is>
+      </c>
+      <c r="P37" s="8" t="inlineStr">
+        <is>
+          <t>반정형</t>
+        </is>
+      </c>
+      <c r="Q37" s="8" t="inlineStr">
+        <is>
+          <t>아니오 - 우리팀 고유</t>
+        </is>
+      </c>
+      <c r="R37" s="9" t="inlineStr">
+        <is>
+          <t>품목·색상 데이터 연동으로 MSDS 서식 자동 생성</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="19.5" customHeight="1" s="26">
       <c r="A38" s="53">
@@ -4665,7 +4749,7 @@
         <v>0.3958333333333333</v>
       </c>
       <c r="D48" s="54" t="n">
-        <v>0.4375</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="E48" s="5">
         <f>IF(OR(C48="",D48=""),"",(D48-C48)*1440)</f>
@@ -4748,10 +4832,10 @@
         </is>
       </c>
       <c r="C49" s="54" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="D49" s="54" t="n">
         <v>0.4375</v>
-      </c>
-      <c r="D49" s="54" t="n">
-        <v>0.4791666666666667</v>
       </c>
       <c r="E49" s="5">
         <f>IF(OR(C49="",D49=""),"",(D49-C49)*1440)</f>
@@ -4830,10 +4914,10 @@
         </is>
       </c>
       <c r="C50" s="54" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="D50" s="54" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="E50" s="5">
         <f>IF(OR(C50="",D50=""),"",(D50-C50)*1440)</f>
@@ -4841,39 +4925,43 @@
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>마케팅·광고운영</t>
+          <t>채널·스토어운영</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>MKT-02 광고 성과 모니터링·최적화</t>
+          <t>CHN-01 상품 등록·수정(옵션/가격)</t>
         </is>
       </c>
       <c r="H50" s="9" t="inlineStr">
         <is>
-          <t>신제품(철재페인트) 키워드광고 상위노출 확인</t>
+          <t>자사몰 판매가 변경 건 8/19까지 수정 요청</t>
         </is>
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>신제품 철재페인트 / 네이버</t>
+          <t>POUR스토어 자사몰</t>
         </is>
       </c>
       <c r="J50" s="8" t="inlineStr">
         <is>
-          <t>네이버 검색, 검색광고 관리자</t>
-        </is>
-      </c>
-      <c r="L50" s="8" t="n"/>
+          <t>자사몰 관리자</t>
+        </is>
+      </c>
+      <c r="L50" s="8" t="inlineStr">
+        <is>
+          <t>이란, 김민지</t>
+        </is>
+      </c>
       <c r="M50" s="8" t="n"/>
       <c r="N50" s="8" t="inlineStr">
         <is>
-          <t>노출 순위 점검 메모</t>
+          <t>판매가 변경 요청(8/19까지)</t>
         </is>
       </c>
       <c r="O50" s="8" t="inlineStr">
         <is>
-          <t>주 2~3회</t>
+          <t>분기/비정기</t>
         </is>
       </c>
       <c r="P50" s="8" t="inlineStr">
@@ -4888,7 +4976,7 @@
       </c>
       <c r="R50" s="9" t="inlineStr">
         <is>
-          <t>키워드 순위 자동 추적 리포트로 대체</t>
+          <t>단가 대시보드와 채널 판매가 연동으로 수기 변경 제거</t>
         </is>
       </c>
     </row>
@@ -4903,10 +4991,10 @@
         </is>
       </c>
       <c r="C51" s="54" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="D51" s="54" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="E51" s="5">
         <f>IF(OR(C51="",D51=""),"",(D51-C51)*1440)</f>
@@ -4914,27 +5002,43 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>기타·행정</t>
+          <t>마케팅·광고운영</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>ETC-05 휴게·점심</t>
+          <t>MKT-01 광고 계정 세팅·집행(메타/구글 등)</t>
         </is>
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
-          <t>점심 및 휴게</t>
-        </is>
-      </c>
-      <c r="I51" s="8" t="n"/>
-      <c r="J51" s="8" t="n"/>
-      <c r="L51" s="8" t="n"/>
+          <t>네이버쇼핑 광고를 위해 카페24 네이버 쇼핑 서비스 신청 요청</t>
+        </is>
+      </c>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>POUR스토어 자사몰 / 네이버쇼핑</t>
+        </is>
+      </c>
+      <c r="J51" s="8" t="inlineStr">
+        <is>
+          <t>카페24 관리자</t>
+        </is>
+      </c>
+      <c r="L51" s="8" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
       <c r="M51" s="8" t="n"/>
-      <c r="N51" s="8" t="n"/>
+      <c r="N51" s="8" t="inlineStr">
+        <is>
+          <t>네이버쇼핑 서비스 신청</t>
+        </is>
+      </c>
       <c r="O51" s="8" t="inlineStr">
         <is>
-          <t>매일</t>
+          <t>1회성</t>
         </is>
       </c>
       <c r="P51" s="8" t="inlineStr">
@@ -4944,10 +5048,14 @@
       </c>
       <c r="Q51" s="8" t="inlineStr">
         <is>
-          <t>예 - 확실히 중복</t>
-        </is>
-      </c>
-      <c r="R51" s="9" t="n"/>
+          <t>아마도 중복</t>
+        </is>
+      </c>
+      <c r="R51" s="9" t="inlineStr">
+        <is>
+          <t>채널 광고 계정·서비스 신청 체크리스트화</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="19.5" customHeight="1" s="26">
       <c r="A52" s="53">
@@ -4960,10 +5068,10 @@
         </is>
       </c>
       <c r="C52" s="54" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="D52" s="54" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="E52" s="5">
         <f>IF(OR(C52="",D52=""),"",(D52-C52)*1440)</f>
@@ -4971,63 +5079,55 @@
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>기획·보고·회의</t>
+          <t>마케팅·광고운영</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>MGT-06 팀원 업무·산출물 검토·피드백</t>
+          <t>MKT-02 광고 성과 모니터링·최적화</t>
         </is>
       </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
-          <t>AX+업무리스트 보고서 검토 및 피드백(정하님)</t>
+          <t>신제품(철재페인트) 키워드광고 상위노출 확인</t>
         </is>
       </c>
       <c r="I52" s="8" t="inlineStr">
         <is>
-          <t>팀 업무관리</t>
+          <t>신제품 철재페인트 / 네이버</t>
         </is>
       </c>
       <c r="J52" s="8" t="inlineStr">
         <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
-        </is>
-      </c>
-      <c r="K52" s="43" t="inlineStr">
-        <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
-        </is>
-      </c>
-      <c r="L52" s="8" t="inlineStr">
-        <is>
-          <t>용정하</t>
-        </is>
-      </c>
+          <t>네이버 검색, 검색광고 관리자</t>
+        </is>
+      </c>
+      <c r="K52" s="43" t="n"/>
+      <c r="L52" s="8" t="n"/>
       <c r="M52" s="8" t="n"/>
       <c r="N52" s="8" t="inlineStr">
         <is>
-          <t>검토 피드백</t>
+          <t>노출 순위 점검 메모</t>
         </is>
       </c>
       <c r="O52" s="8" t="inlineStr">
         <is>
-          <t>주 1회</t>
+          <t>주 2~3회</t>
         </is>
       </c>
       <c r="P52" s="8" t="inlineStr">
         <is>
-          <t>비정형(판단 필요)</t>
+          <t>정형(매뉴얼화 가능)</t>
         </is>
       </c>
       <c r="Q52" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
+          <t>예 - 확실히 중복</t>
         </is>
       </c>
       <c r="R52" s="9" t="inlineStr">
         <is>
-          <t>업무보드 데이터 자동 집계로 보고서 수기작성 제거</t>
+          <t>키워드 순위 자동 추적 리포트로 대체</t>
         </is>
       </c>
     </row>
@@ -5042,10 +5142,10 @@
         </is>
       </c>
       <c r="C53" s="54" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="D53" s="54" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="E53" s="5">
         <f>IF(OR(C53="",D53=""),"",(D53-C53)*1440)</f>
@@ -5053,65 +5153,41 @@
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>기획·보고·회의</t>
+          <t>기타·행정</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>MGT-06 팀원 업무·산출물 검토·피드백</t>
+          <t>ETC-05 휴게·점심</t>
         </is>
       </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
-          <t>AX+업무리스트 보고서 검토 및 피드백(채림님)</t>
-        </is>
-      </c>
-      <c r="I53" s="8" t="inlineStr">
-        <is>
-          <t>팀 업무관리</t>
-        </is>
-      </c>
-      <c r="J53" s="8" t="inlineStr">
-        <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
-        </is>
-      </c>
-      <c r="K53" s="43" t="inlineStr">
-        <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
-        </is>
-      </c>
-      <c r="L53" s="8" t="inlineStr">
-        <is>
-          <t>양채림</t>
-        </is>
-      </c>
+          <t>점심 및 휴게</t>
+        </is>
+      </c>
+      <c r="I53" s="8" t="n"/>
+      <c r="J53" s="8" t="n"/>
+      <c r="K53" s="43" t="n"/>
+      <c r="L53" s="8" t="n"/>
       <c r="M53" s="8" t="n"/>
-      <c r="N53" s="8" t="inlineStr">
-        <is>
-          <t>검토 피드백</t>
-        </is>
-      </c>
+      <c r="N53" s="8" t="n"/>
       <c r="O53" s="8" t="inlineStr">
         <is>
-          <t>주 1회</t>
+          <t>매일</t>
         </is>
       </c>
       <c r="P53" s="8" t="inlineStr">
         <is>
-          <t>비정형(판단 필요)</t>
+          <t>정형(매뉴얼화 가능)</t>
         </is>
       </c>
       <c r="Q53" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
-        </is>
-      </c>
-      <c r="R53" s="9" t="inlineStr">
-        <is>
-          <t>업무보드 데이터 자동 집계로 보고서 수기작성 제거</t>
-        </is>
-      </c>
+          <t>예 - 확실히 중복</t>
+        </is>
+      </c>
+      <c r="R53" s="9" t="n"/>
     </row>
     <row r="54" ht="19.5" customHeight="1" s="26">
       <c r="A54" s="53">
@@ -5124,10 +5200,10 @@
         </is>
       </c>
       <c r="C54" s="54" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="D54" s="54" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.5625</v>
       </c>
       <c r="E54" s="5">
         <f>IF(OR(C54="",D54=""),"",(D54-C54)*1440)</f>
@@ -5140,17 +5216,17 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>MGT-07 업무 인수인계·이관</t>
+          <t>MGT-06 팀원 업무·산출물 검토·피드백</t>
         </is>
       </c>
       <c r="H54" s="9" t="inlineStr">
         <is>
-          <t>그로홈 업무 인수인계 받음 — 담당 범위·진행건 확인</t>
+          <t>AX+업무리스트 보고서 검토 및 피드백(정하님)</t>
         </is>
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
-          <t>그로홈</t>
+          <t>팀 업무관리</t>
         </is>
       </c>
       <c r="J54" s="8" t="inlineStr">
@@ -5163,16 +5239,20 @@
           <t>https://pourstorecrm.web.app/pour-os</t>
         </is>
       </c>
-      <c r="L54" s="8" t="n"/>
+      <c r="L54" s="8" t="inlineStr">
+        <is>
+          <t>용정하</t>
+        </is>
+      </c>
       <c r="M54" s="8" t="n"/>
       <c r="N54" s="8" t="inlineStr">
         <is>
-          <t>인수인계 항목 정리</t>
+          <t>검토 피드백</t>
         </is>
       </c>
       <c r="O54" s="8" t="inlineStr">
         <is>
-          <t>1회성</t>
+          <t>주 1회</t>
         </is>
       </c>
       <c r="P54" s="8" t="inlineStr">
@@ -5182,12 +5262,12 @@
       </c>
       <c r="Q54" s="8" t="inlineStr">
         <is>
-          <t>모름</t>
+          <t>아마도 중복</t>
         </is>
       </c>
       <c r="R54" s="9" t="inlineStr">
         <is>
-          <t>인수인계 체크리스트·담당 매핑표 상시 관리</t>
+          <t>업무보드 데이터 자동 집계로 보고서 수기작성 제거</t>
         </is>
       </c>
     </row>
@@ -5202,10 +5282,10 @@
         </is>
       </c>
       <c r="C55" s="54" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.5625</v>
       </c>
       <c r="D55" s="54" t="n">
-        <v>0.6875</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="E55" s="5">
         <f>IF(OR(C55="",D55=""),"",(D55-C55)*1440)</f>
@@ -5213,40 +5293,53 @@
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>콘텐츠제작</t>
+          <t>기획·보고·회의</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>CNT-07 카탈로그·영업자료 제작</t>
+          <t>MGT-06 팀원 업무·산출물 검토·피드백</t>
         </is>
       </c>
       <c r="H55" s="9" t="inlineStr">
         <is>
-          <t>부자재 소개 카달로그 제작</t>
+          <t>AX+업무리스트 보고서 검토 및 피드백(채림님)</t>
         </is>
       </c>
       <c r="I55" s="8" t="inlineStr">
         <is>
-          <t>부자재</t>
-        </is>
-      </c>
-      <c r="J55" s="8" t="n"/>
-      <c r="L55" s="8" t="n"/>
+          <t>팀 업무관리</t>
+        </is>
+      </c>
+      <c r="J55" s="8" t="inlineStr">
+        <is>
+          <t>CRM센터-POUR OS(업무보드)</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>https://pourstorecrm.web.app/pour-os</t>
+        </is>
+      </c>
+      <c r="L55" s="8" t="inlineStr">
+        <is>
+          <t>양채림</t>
+        </is>
+      </c>
       <c r="M55" s="8" t="n"/>
       <c r="N55" s="8" t="inlineStr">
         <is>
-          <t>부자재 소개 카달로그</t>
+          <t>검토 피드백</t>
         </is>
       </c>
       <c r="O55" s="8" t="inlineStr">
         <is>
-          <t>1회성</t>
+          <t>주 1회</t>
         </is>
       </c>
       <c r="P55" s="8" t="inlineStr">
         <is>
-          <t>반정형</t>
+          <t>비정형(판단 필요)</t>
         </is>
       </c>
       <c r="Q55" s="8" t="inlineStr">
@@ -5256,7 +5349,7 @@
       </c>
       <c r="R55" s="9" t="inlineStr">
         <is>
-          <t>상품 마스터 데이터로 카달로그 자동 생성</t>
+          <t>업무보드 데이터 자동 집계로 보고서 수기작성 제거</t>
         </is>
       </c>
     </row>
@@ -5271,10 +5364,10 @@
         </is>
       </c>
       <c r="C56" s="54" t="n">
-        <v>0.6875</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D56" s="54" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.625</v>
       </c>
       <c r="E56" s="5">
         <f>IF(OR(C56="",D56=""),"",(D56-C56)*1440)</f>
@@ -5282,44 +5375,44 @@
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>데이터·정산</t>
+          <t>기획·보고·회의</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>DAT-04 리포트·대시보드 작성</t>
+          <t>MGT-07 업무 인수인계·이관</t>
         </is>
       </c>
       <c r="H56" s="9" t="inlineStr">
         <is>
-          <t>POUR스토어 단가·공헌이익·손익계산 대시보드 제작 — 진행중</t>
+          <t>그로홈 업무 인수인계 받음 — 담당 범위·진행건 확인</t>
         </is>
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>POUR스토어</t>
+          <t>그로홈</t>
         </is>
       </c>
       <c r="J56" s="8" t="inlineStr">
         <is>
-          <t>단가 대시보드, 엑셀</t>
+          <t>CRM센터-POUR OS(업무보드)</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>POUR스토어 가격·마진 통합 대시보드 (pour-construction-form.pages.dev)</t>
+          <t>https://pourstorecrm.web.app/pour-os</t>
         </is>
       </c>
       <c r="L56" s="8" t="n"/>
       <c r="M56" s="8" t="n"/>
       <c r="N56" s="8" t="inlineStr">
         <is>
-          <t>단가·공헌이익·손익 대시보드</t>
+          <t>인수인계 항목 정리</t>
         </is>
       </c>
       <c r="O56" s="8" t="inlineStr">
         <is>
-          <t>주 2~3회</t>
+          <t>1회성</t>
         </is>
       </c>
       <c r="P56" s="8" t="inlineStr">
@@ -5329,12 +5422,12 @@
       </c>
       <c r="Q56" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
+          <t>모름</t>
         </is>
       </c>
       <c r="R56" s="9" t="inlineStr">
         <is>
-          <t>채널 수수료·원가 데이터 자동 연동으로 수기 입력 제거</t>
+          <t>인수인계 체크리스트·담당 매핑표 상시 관리</t>
         </is>
       </c>
     </row>
@@ -5349,10 +5442,10 @@
         </is>
       </c>
       <c r="C57" s="54" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.625</v>
       </c>
       <c r="D57" s="54" t="n">
-        <v>0.75</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E57" s="5">
         <f>IF(OR(C57="",D57=""),"",(D57-C57)*1440)</f>
@@ -5360,38 +5453,34 @@
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>제조·생산관리</t>
+          <t>콘텐츠제작</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>MFG-08 MSDS·라벨 등 제품 표시사항 제작</t>
+          <t>CNT-05 SNS 채널 운영·업로드</t>
         </is>
       </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
-          <t>신제품 코트재 MSDS 컬러별 31개 제작 — 진행중</t>
+          <t>공식계정 블로그 메인페이지 스킨 변경 (다음주에) 요청</t>
         </is>
       </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>코트재 신제품 31색</t>
-        </is>
-      </c>
-      <c r="J57" s="8" t="inlineStr">
-        <is>
-          <t>챗지피티</t>
-        </is>
-      </c>
-      <c r="L57" s="8" t="n"/>
-      <c r="M57" s="8" t="inlineStr">
-        <is>
-          <t>세이고, 쿠팡물류센터</t>
-        </is>
-      </c>
+          <t>공식 블로그</t>
+        </is>
+      </c>
+      <c r="J57" s="8" t="n"/>
+      <c r="L57" s="8" t="inlineStr">
+        <is>
+          <t>양채림</t>
+        </is>
+      </c>
+      <c r="M57" s="8" t="n"/>
       <c r="N57" s="8" t="inlineStr">
         <is>
-          <t>MSDS 31종</t>
+          <t>블로그 메인 스킨 변경 요청</t>
         </is>
       </c>
       <c r="O57" s="8" t="inlineStr">
@@ -5406,12 +5495,12 @@
       </c>
       <c r="Q57" s="8" t="inlineStr">
         <is>
-          <t>아니오 - 우리팀 고유</t>
+          <t>아마도 중복</t>
         </is>
       </c>
       <c r="R57" s="9" t="inlineStr">
         <is>
-          <t>품목·색상 데이터 연동으로 MSDS 서식 자동 생성</t>
+          <t>채널별 디자인 자산 공용 관리</t>
         </is>
       </c>
     </row>
@@ -5425,24 +5514,64 @@
           <t>수</t>
         </is>
       </c>
-      <c r="C58" s="54" t="n"/>
-      <c r="D58" s="54" t="n"/>
+      <c r="C58" s="54" t="n">
+        <v>0.6458333333333334</v>
+      </c>
+      <c r="D58" s="54" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="E58" s="5">
         <f>IF(OR(C58="",D58=""),"",(D58-C58)*1440)</f>
         <v/>
       </c>
-      <c r="F58" s="8" t="n"/>
-      <c r="G58" s="8" t="n"/>
-      <c r="H58" s="9" t="n"/>
-      <c r="I58" s="8" t="n"/>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>콘텐츠제작</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>CNT-06 디자인 시안 피드백</t>
+        </is>
+      </c>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>셀러 제안 시 첨부배너 검토 및 승인</t>
+        </is>
+      </c>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>셀러 제안용 배너</t>
+        </is>
+      </c>
       <c r="J58" s="8" t="n"/>
       <c r="L58" s="8" t="n"/>
       <c r="M58" s="8" t="n"/>
-      <c r="N58" s="8" t="n"/>
-      <c r="O58" s="8" t="n"/>
-      <c r="P58" s="8" t="n"/>
-      <c r="Q58" s="8" t="n"/>
-      <c r="R58" s="9" t="n"/>
+      <c r="N58" s="8" t="inlineStr">
+        <is>
+          <t>첨부배너 검토·승인</t>
+        </is>
+      </c>
+      <c r="O58" s="8" t="inlineStr">
+        <is>
+          <t>분기/비정기</t>
+        </is>
+      </c>
+      <c r="P58" s="8" t="inlineStr">
+        <is>
+          <t>반정형</t>
+        </is>
+      </c>
+      <c r="Q58" s="8" t="inlineStr">
+        <is>
+          <t>아마도 중복</t>
+        </is>
+      </c>
+      <c r="R58" s="9" t="inlineStr">
+        <is>
+          <t>제안용 배너 템플릿 라이브러리화</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="19.5" customHeight="1" s="26">
       <c r="A59" s="53">
@@ -5454,24 +5583,64 @@
           <t>수</t>
         </is>
       </c>
-      <c r="C59" s="54" t="n"/>
-      <c r="D59" s="54" t="n"/>
+      <c r="C59" s="54" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="D59" s="54" t="n">
+        <v>0.7083333333333334</v>
+      </c>
       <c r="E59" s="5">
         <f>IF(OR(C59="",D59=""),"",(D59-C59)*1440)</f>
         <v/>
       </c>
-      <c r="F59" s="8" t="n"/>
-      <c r="G59" s="8" t="n"/>
-      <c r="H59" s="9" t="n"/>
-      <c r="I59" s="8" t="n"/>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>콘텐츠제작</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>CNT-07 카탈로그·영업자료 제작</t>
+        </is>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>부자재 소개 카달로그 제작</t>
+        </is>
+      </c>
+      <c r="I59" s="8" t="inlineStr">
+        <is>
+          <t>부자재</t>
+        </is>
+      </c>
       <c r="J59" s="8" t="n"/>
       <c r="L59" s="8" t="n"/>
       <c r="M59" s="8" t="n"/>
-      <c r="N59" s="8" t="n"/>
-      <c r="O59" s="8" t="n"/>
-      <c r="P59" s="8" t="n"/>
-      <c r="Q59" s="8" t="n"/>
-      <c r="R59" s="9" t="n"/>
+      <c r="N59" s="8" t="inlineStr">
+        <is>
+          <t>부자재 소개 카달로그</t>
+        </is>
+      </c>
+      <c r="O59" s="8" t="inlineStr">
+        <is>
+          <t>1회성</t>
+        </is>
+      </c>
+      <c r="P59" s="8" t="inlineStr">
+        <is>
+          <t>반정형</t>
+        </is>
+      </c>
+      <c r="Q59" s="8" t="inlineStr">
+        <is>
+          <t>아마도 중복</t>
+        </is>
+      </c>
+      <c r="R59" s="9" t="inlineStr">
+        <is>
+          <t>상품 마스터 데이터로 카달로그 자동 생성</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="19.5" customHeight="1" s="26">
       <c r="A60" s="53">
@@ -5483,24 +5652,73 @@
           <t>수</t>
         </is>
       </c>
-      <c r="C60" s="54" t="n"/>
-      <c r="D60" s="54" t="n"/>
+      <c r="C60" s="54" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="D60" s="54" t="n">
+        <v>0.7291666666666666</v>
+      </c>
       <c r="E60" s="5">
         <f>IF(OR(C60="",D60=""),"",(D60-C60)*1440)</f>
         <v/>
       </c>
-      <c r="F60" s="8" t="n"/>
-      <c r="G60" s="8" t="n"/>
-      <c r="H60" s="9" t="n"/>
-      <c r="I60" s="8" t="n"/>
-      <c r="J60" s="8" t="n"/>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>데이터·정산</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>DAT-04 리포트·대시보드 작성</t>
+        </is>
+      </c>
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>POUR스토어 단가·공헌이익·손익계산 대시보드 제작 — 진행중</t>
+        </is>
+      </c>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>POUR스토어</t>
+        </is>
+      </c>
+      <c r="J60" s="8" t="inlineStr">
+        <is>
+          <t>단가 대시보드, 엑셀</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>POUR스토어 가격·마진 통합 대시보드 (pour-construction-form.pages.dev)</t>
+        </is>
+      </c>
       <c r="L60" s="8" t="n"/>
       <c r="M60" s="8" t="n"/>
-      <c r="N60" s="8" t="n"/>
-      <c r="O60" s="8" t="n"/>
-      <c r="P60" s="8" t="n"/>
-      <c r="Q60" s="8" t="n"/>
-      <c r="R60" s="9" t="n"/>
+      <c r="N60" s="8" t="inlineStr">
+        <is>
+          <t>단가·공헌이익·손익 대시보드</t>
+        </is>
+      </c>
+      <c r="O60" s="8" t="inlineStr">
+        <is>
+          <t>주 2~3회</t>
+        </is>
+      </c>
+      <c r="P60" s="8" t="inlineStr">
+        <is>
+          <t>비정형(판단 필요)</t>
+        </is>
+      </c>
+      <c r="Q60" s="8" t="inlineStr">
+        <is>
+          <t>아마도 중복</t>
+        </is>
+      </c>
+      <c r="R60" s="9" t="inlineStr">
+        <is>
+          <t>채널 수수료·원가 데이터 자동 연동으로 수기 입력 제거</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="19.5" customHeight="1" s="26">
       <c r="A61" s="53">
@@ -5512,24 +5730,72 @@
           <t>수</t>
         </is>
       </c>
-      <c r="C61" s="54" t="n"/>
-      <c r="D61" s="54" t="n"/>
+      <c r="C61" s="54" t="n">
+        <v>0.7291666666666666</v>
+      </c>
+      <c r="D61" s="54" t="n">
+        <v>0.75</v>
+      </c>
       <c r="E61" s="5">
         <f>IF(OR(C61="",D61=""),"",(D61-C61)*1440)</f>
         <v/>
       </c>
-      <c r="F61" s="8" t="n"/>
-      <c r="G61" s="8" t="n"/>
-      <c r="H61" s="9" t="n"/>
-      <c r="I61" s="8" t="n"/>
-      <c r="J61" s="8" t="n"/>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>제조·생산관리</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t>MFG-08 MSDS·라벨 등 제품 표시사항 제작</t>
+        </is>
+      </c>
+      <c r="H61" s="9" t="inlineStr">
+        <is>
+          <t>신제품 코트재 MSDS 컬러별 31개 제작 — 진행중</t>
+        </is>
+      </c>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>코트재 신제품 31색</t>
+        </is>
+      </c>
+      <c r="J61" s="8" t="inlineStr">
+        <is>
+          <t>챗지피티</t>
+        </is>
+      </c>
       <c r="L61" s="8" t="n"/>
-      <c r="M61" s="8" t="n"/>
-      <c r="N61" s="8" t="n"/>
-      <c r="O61" s="8" t="n"/>
-      <c r="P61" s="8" t="n"/>
-      <c r="Q61" s="8" t="n"/>
-      <c r="R61" s="9" t="n"/>
+      <c r="M61" s="8" t="inlineStr">
+        <is>
+          <t>세이고, 쿠팡물류센터</t>
+        </is>
+      </c>
+      <c r="N61" s="8" t="inlineStr">
+        <is>
+          <t>MSDS 31종</t>
+        </is>
+      </c>
+      <c r="O61" s="8" t="inlineStr">
+        <is>
+          <t>1회성</t>
+        </is>
+      </c>
+      <c r="P61" s="8" t="inlineStr">
+        <is>
+          <t>반정형</t>
+        </is>
+      </c>
+      <c r="Q61" s="8" t="inlineStr">
+        <is>
+          <t>아니오 - 우리팀 고유</t>
+        </is>
+      </c>
+      <c r="R61" s="9" t="inlineStr">
+        <is>
+          <t>품목·색상 데이터 연동으로 MSDS 서식 자동 생성</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="19.5" customHeight="1" s="26">
       <c r="A62" s="53">
@@ -8007,11 +8273,7 @@
           <t>예 - 확실히 중복</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>채널별 주문을 통합 주문판으로 자동 취합</t>
-        </is>
-      </c>
+      <c r="U4" s="8" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -8158,16 +8420,7 @@
           <t>POUR스토어</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
-        </is>
-      </c>
+      <c r="M6" s="8" t="n"/>
       <c r="O6" s="8" t="inlineStr">
         <is>
           <t>김민지</t>
@@ -8254,16 +8507,7 @@
           <t>대리점(가나랜드·경남지사)</t>
         </is>
       </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
-        </is>
-      </c>
+      <c r="M7" s="8" t="n"/>
       <c r="O7" s="8" t="inlineStr">
         <is>
           <t>이란</t>
@@ -8290,11 +8534,7 @@
           <t>모름</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>대리점 인터뷰 질문지 표준 템플릿화</t>
-        </is>
-      </c>
+      <c r="U7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -8649,11 +8889,7 @@
           <t>모름</t>
         </is>
       </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>개선 요청·피드백 이력을 앱 내 이슈보드로 관리해 재설명 시간 제거</t>
-        </is>
-      </c>
+      <c r="U11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -8744,11 +8980,7 @@
           <t>예 - 확실히 중복</t>
         </is>
       </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>상품 마스터 DB 기준 채널 자동 등록</t>
-        </is>
-      </c>
+      <c r="U12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -8804,16 +9036,7 @@
           <t>신제품 4종</t>
         </is>
       </c>
-      <c r="M13" s="8" t="inlineStr">
-        <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
-        </is>
-      </c>
+      <c r="M13" s="8" t="n"/>
       <c r="O13" s="8" t="inlineStr">
         <is>
           <t>양채림</t>
@@ -8878,7 +9101,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="G14" s="58" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6875</v>
       </c>
       <c r="H14" s="7">
         <f>IF(OR(F14="",G14=""),"",(G14-F14)*1440)</f>
@@ -8966,10 +9189,10 @@
         </is>
       </c>
       <c r="F15" s="58" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="G15" s="58" t="n">
         <v>0.7083333333333334</v>
-      </c>
-      <c r="G15" s="58" t="n">
-        <v>0.75</v>
       </c>
       <c r="H15" s="7">
         <f>IF(OR(F15="",G15=""),"",(G15-F15)*1440)</f>
@@ -8977,67 +9200,58 @@
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>마케팅·광고운영</t>
+          <t>콘텐츠제작</t>
         </is>
       </c>
       <c r="J15" s="8" t="inlineStr">
         <is>
-          <t>MKT-04 인플루언서·체험단 섭외/관리</t>
+          <t>CNT-06 디자인 시안 피드백</t>
         </is>
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>퍼포먼스마케팅 인플루언서/셀러 협업 현황 확인 및 컨택 방안 피드백(채림님께)</t>
+          <t>대리점 경남지사 명함디자인 컨펌 승인</t>
         </is>
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>POUR스토어</t>
-        </is>
-      </c>
-      <c r="M15" s="8" t="inlineStr">
-        <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
-        </is>
-      </c>
+          <t>대리점(경남지사)</t>
+        </is>
+      </c>
+      <c r="M15" s="8" t="n"/>
       <c r="O15" s="8" t="inlineStr">
         <is>
-          <t>양채림</t>
+          <t>이란</t>
         </is>
       </c>
       <c r="P15" s="8" t="inlineStr">
         <is>
-          <t>인플루언서·셀러</t>
+          <t>경남지사</t>
         </is>
       </c>
       <c r="Q15" s="8" t="inlineStr">
         <is>
-          <t>협업 컨택 방안 피드백</t>
+          <t>명함 디자인 컨펌</t>
         </is>
       </c>
       <c r="R15" s="8" t="inlineStr">
         <is>
-          <t>주 1회</t>
+          <t>1회성</t>
         </is>
       </c>
       <c r="S15" s="8" t="inlineStr">
         <is>
-          <t>비정형(판단 필요)</t>
+          <t>반정형</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
+          <t>모름</t>
         </is>
       </c>
       <c r="U15" s="8" t="inlineStr">
         <is>
-          <t>인플루언서/셀러 컨택 이력 DB 공용화(중복 컨택 방지)</t>
+          <t>대리점 인쇄물 디자인 템플릿 표준화</t>
         </is>
       </c>
     </row>
@@ -9058,18 +9272,18 @@
         </is>
       </c>
       <c r="D16" s="57" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>월</t>
         </is>
       </c>
       <c r="F16" s="58" t="n">
-        <v>0.375</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G16" s="58" t="n">
-        <v>0.3958333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="H16" s="7">
         <f>IF(OR(F16="",G16=""),"",(G16-F16)*1440)</f>
@@ -9077,59 +9291,58 @@
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>기타·행정</t>
+          <t>마케팅·광고운영</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>ETC-01 메일·메신저 확인 및 회신</t>
+          <t>MKT-04 인플루언서·체험단 섭외/관리</t>
         </is>
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>출근 후 메일·메신저·업무보드 확인 및 회신</t>
+          <t>퍼포먼스마케팅 인플루언서/셀러 협업 현황 확인 및 컨택 방안 피드백(채림님께)</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>전사</t>
-        </is>
-      </c>
-      <c r="M16" s="8" t="inlineStr">
-        <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
-        </is>
-      </c>
-      <c r="O16" s="8" t="n"/>
-      <c r="P16" s="8" t="n"/>
+          <t>POUR스토어</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="n"/>
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>양채림</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="inlineStr">
+        <is>
+          <t>인플루언서·셀러</t>
+        </is>
+      </c>
       <c r="Q16" s="8" t="inlineStr">
         <is>
-          <t>회신 처리</t>
+          <t>협업 컨택 방안 피드백</t>
         </is>
       </c>
       <c r="R16" s="8" t="inlineStr">
         <is>
-          <t>매일</t>
+          <t>주 1회</t>
         </is>
       </c>
       <c r="S16" s="8" t="inlineStr">
         <is>
-          <t>정형(매뉴얼화 가능)</t>
+          <t>비정형(판단 필요)</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>예 - 확실히 중복</t>
+          <t>아마도 중복</t>
         </is>
       </c>
       <c r="U16" s="8" t="inlineStr">
         <is>
-          <t>팀별 요청·공지를 업무보드 알림 하나로 일원화</t>
+          <t>인플루언서/셀러 컨택 이력 DB 공용화(중복 컨택 방지)</t>
         </is>
       </c>
     </row>
@@ -9158,10 +9371,10 @@
         </is>
       </c>
       <c r="F17" s="58" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="G17" s="58" t="n">
         <v>0.3958333333333333</v>
-      </c>
-      <c r="G17" s="58" t="n">
-        <v>0.4583333333333333</v>
       </c>
       <c r="H17" s="7">
         <f>IF(OR(F17="",G17=""),"",(G17-F17)*1440)</f>
@@ -9169,59 +9382,59 @@
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>기획·보고·회의</t>
+          <t>기타·행정</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>MGT-01 팀 내부 회의</t>
+          <t>ETC-01 메일·메신저 확인 및 회신</t>
         </is>
       </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>모여라딜 피봇팅 방향 논의 및 정하님 업무 진행방향 미팅</t>
+          <t>출근 후 메일·메신저·업무보드 확인 및 회신</t>
         </is>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>모여라딜</t>
-        </is>
-      </c>
-      <c r="M17" s="8" t="n"/>
+          <t>전사</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t>CRM센터-POUR OS(업무보드)</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>https://pourstorecrm.web.app/pour-os</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
-        <is>
-          <t>용정하</t>
-        </is>
-      </c>
+      <c r="O17" s="8" t="n"/>
       <c r="P17" s="8" t="n"/>
       <c r="Q17" s="8" t="inlineStr">
         <is>
-          <t>미팅 결과·업무 방향 메모</t>
+          <t>회신 처리</t>
         </is>
       </c>
       <c r="R17" s="8" t="inlineStr">
         <is>
-          <t>주 1회</t>
+          <t>매일</t>
         </is>
       </c>
       <c r="S17" s="8" t="inlineStr">
         <is>
-          <t>비정형(판단 필요)</t>
+          <t>정형(매뉴얼화 가능)</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>모름</t>
+          <t>예 - 확실히 중복</t>
         </is>
       </c>
       <c r="U17" s="8" t="inlineStr">
         <is>
-          <t>논의 결과를 업무보드 프로젝트 카드로 즉시 반영</t>
+          <t>팀별 요청·공지를 업무보드 알림 하나로 일원화</t>
         </is>
       </c>
     </row>
@@ -9250,10 +9463,10 @@
         </is>
       </c>
       <c r="F18" s="58" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="G18" s="58" t="n">
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="H18" s="7">
         <f>IF(OR(F18="",G18=""),"",(G18-F18)*1440)</f>
@@ -9261,29 +9474,25 @@
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>콘텐츠제작</t>
+          <t>기획·보고·회의</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>CNT-02 촬영 기획·진행</t>
+          <t>MGT-01 팀 내부 회의</t>
         </is>
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>제품시공 촬영 — 테스트촬영 및 대여 탐색, 채림님께 인수인계하여 진행 요청 (아파트·공장·일반주택 대상)</t>
+          <t>모여라딜 피봇팅 방향 논의 및 정하님 업무 진행방향 미팅</t>
         </is>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>시공 제품 / 아파트·공장·일반주택</t>
-        </is>
-      </c>
-      <c r="M18" s="8" t="inlineStr">
-        <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
-        </is>
-      </c>
+          <t>모여라딜</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="n"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>https://pourstorecrm.web.app/pour-os</t>
@@ -9291,18 +9500,18 @@
       </c>
       <c r="O18" s="8" t="inlineStr">
         <is>
-          <t>양채림</t>
+          <t>용정하</t>
         </is>
       </c>
       <c r="P18" s="8" t="n"/>
       <c r="Q18" s="8" t="inlineStr">
         <is>
-          <t>테스트 촬영본, 촬영 진행 요청서</t>
+          <t>미팅 결과·업무 방향 메모</t>
         </is>
       </c>
       <c r="R18" s="8" t="inlineStr">
         <is>
-          <t>1회성</t>
+          <t>주 1회</t>
         </is>
       </c>
       <c r="S18" s="8" t="inlineStr">
@@ -9312,12 +9521,12 @@
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
+          <t>모름</t>
         </is>
       </c>
       <c r="U18" s="8" t="inlineStr">
         <is>
-          <t>건물유형별 시공 촬영 가이드·촬영 자산 라이브러리 공용화</t>
+          <t>논의 결과를 업무보드 프로젝트 카드로 즉시 반영</t>
         </is>
       </c>
     </row>
@@ -9346,10 +9555,10 @@
         </is>
       </c>
       <c r="F19" s="58" t="n">
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="G19" s="58" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="H19" s="7">
         <f>IF(OR(F19="",G19=""),"",(G19-F19)*1440)</f>
@@ -9357,40 +9566,65 @@
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>기타·행정</t>
+          <t>콘텐츠제작</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>ETC-05 휴게·점심</t>
+          <t>CNT-02 촬영 기획·진행</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>점심 및 휴게</t>
-        </is>
-      </c>
-      <c r="L19" s="8" t="n"/>
-      <c r="M19" s="8" t="n"/>
-      <c r="O19" s="8" t="n"/>
+          <t>제품시공 촬영 — 테스트촬영 및 대여 탐색, 채림님께 인수인계하여 진행 요청 (아파트·공장·일반주택 대상)</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>시공 제품 / 아파트·공장·일반주택</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t>CRM센터-POUR OS(업무보드)</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>https://pourstorecrm.web.app/pour-os</t>
+        </is>
+      </c>
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>양채림</t>
+        </is>
+      </c>
       <c r="P19" s="8" t="n"/>
-      <c r="Q19" s="8" t="n"/>
+      <c r="Q19" s="8" t="inlineStr">
+        <is>
+          <t>테스트 촬영본, 촬영 진행 요청서</t>
+        </is>
+      </c>
       <c r="R19" s="8" t="inlineStr">
         <is>
-          <t>매일</t>
+          <t>1회성</t>
         </is>
       </c>
       <c r="S19" s="8" t="inlineStr">
         <is>
-          <t>정형(매뉴얼화 가능)</t>
+          <t>비정형(판단 필요)</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>예 - 확실히 중복</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="n"/>
+          <t>아마도 중복</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>건물유형별 시공 촬영 가이드·촬영 자산 라이브러리 공용화</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -9417,10 +9651,10 @@
         </is>
       </c>
       <c r="F20" s="58" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G20" s="58" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="H20" s="7">
         <f>IF(OR(F20="",G20=""),"",(G20-F20)*1440)</f>
@@ -9428,17 +9662,17 @@
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>마케팅·광고운영</t>
+          <t>콘텐츠제작</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>MKT-04 인플루언서·체험단 섭외/관리</t>
+          <t>CNT-04 카피·문구 작성</t>
         </is>
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>채림님 인플루언서 협업마케팅 진행방향 안내 및 멘트 컨펌</t>
+          <t>관리주체 안내 멘트 컨펌 승인</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
@@ -9446,49 +9680,36 @@
           <t>POUR스토어</t>
         </is>
       </c>
-      <c r="M20" s="8" t="inlineStr">
-        <is>
-          <t>레뷰, 리뷰플레이스</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
-        </is>
-      </c>
+      <c r="M20" s="8" t="n"/>
       <c r="O20" s="8" t="inlineStr">
         <is>
-          <t>양채림</t>
-        </is>
-      </c>
-      <c r="P20" s="8" t="inlineStr">
-        <is>
-          <t>인플루언서</t>
-        </is>
-      </c>
+          <t>이란</t>
+        </is>
+      </c>
+      <c r="P20" s="8" t="n"/>
       <c r="Q20" s="8" t="inlineStr">
         <is>
-          <t>협업 진행안 컨펌</t>
+          <t>안내 멘트 컨펌</t>
         </is>
       </c>
       <c r="R20" s="8" t="inlineStr">
         <is>
-          <t>주 1회</t>
+          <t>1회성</t>
         </is>
       </c>
       <c r="S20" s="8" t="inlineStr">
         <is>
-          <t>비정형(판단 필요)</t>
+          <t>반정형</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
+          <t>모름</t>
         </is>
       </c>
       <c r="U20" s="8" t="inlineStr">
         <is>
-          <t>인플루언서 협업 진행 기준(가이드) 문서화 후 위임</t>
+          <t>고객 안내 멘트 표준 문구집 관리</t>
         </is>
       </c>
     </row>
@@ -9517,10 +9738,10 @@
         </is>
       </c>
       <c r="F21" s="58" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="G21" s="58" t="n">
-        <v>0.625</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="H21" s="7">
         <f>IF(OR(F21="",G21=""),"",(G21-F21)*1440)</f>
@@ -9528,65 +9749,40 @@
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>사내시스템·자동화</t>
+          <t>기타·행정</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>SYS-01 사내 시스템·앱 기획/개선 요청</t>
+          <t>ETC-05 휴게·점심</t>
         </is>
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>소싱앱 UX/UI 개선 — 정하님 추가 고도화 건 2차 피드백</t>
-        </is>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t>소싱앱</t>
-        </is>
-      </c>
-      <c r="M21" s="8" t="inlineStr">
-        <is>
-          <t>소싱앱</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>소싱 관리 · 모여라딜 (moyeoradeal-sourcing.pages.dev)</t>
-        </is>
-      </c>
-      <c r="O21" s="8" t="inlineStr">
-        <is>
-          <t>용정하</t>
-        </is>
-      </c>
+          <t>점심 및 휴게</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="n"/>
+      <c r="M21" s="8" t="n"/>
+      <c r="O21" s="8" t="n"/>
       <c r="P21" s="8" t="n"/>
-      <c r="Q21" s="8" t="inlineStr">
-        <is>
-          <t>UX/UI 2차 피드백</t>
-        </is>
-      </c>
+      <c r="Q21" s="8" t="n"/>
       <c r="R21" s="8" t="inlineStr">
         <is>
-          <t>주 2~3회</t>
+          <t>매일</t>
         </is>
       </c>
       <c r="S21" s="8" t="inlineStr">
         <is>
-          <t>비정형(판단 필요)</t>
+          <t>정형(매뉴얼화 가능)</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>모름</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>개선 요청·피드백 이력을 앱 내 이슈보드로 관리</t>
-        </is>
-      </c>
+          <t>예 - 확실히 중복</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -9613,10 +9809,10 @@
         </is>
       </c>
       <c r="F22" s="58" t="n">
-        <v>0.625</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="G22" s="58" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="H22" s="7">
         <f>IF(OR(F22="",G22=""),"",(G22-F22)*1440)</f>
@@ -9624,40 +9820,52 @@
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>상품기획·소싱</t>
+          <t>마케팅·광고운영</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>PLN-01 신상품 아이템 발굴/시장조사</t>
+          <t>MKT-04 인플루언서·체험단 섭외/관리</t>
         </is>
       </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
-          <t>부자재(롤링독) 판매 세팅 검토 — 우선순위 재조정으로 보류</t>
+          <t>채림님 인플루언서 협업마케팅 진행방향 안내 및 멘트 컨펌</t>
         </is>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>부자재·안전용품</t>
-        </is>
-      </c>
-      <c r="M22" s="8" t="n"/>
+          <t>POUR스토어</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="inlineStr">
+        <is>
+          <t>레뷰, 리뷰플레이스</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://pour-construction-form.pages.dev/pourstore-pricing-dashboard</t>
-        </is>
-      </c>
-      <c r="O22" s="8" t="n"/>
-      <c r="P22" s="8" t="n"/>
+          <t>https://pourstorecrm.web.app/pour-os</t>
+        </is>
+      </c>
+      <c r="O22" s="8" t="inlineStr">
+        <is>
+          <t>양채림</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="inlineStr">
+        <is>
+          <t>인플루언서</t>
+        </is>
+      </c>
       <c r="Q22" s="8" t="inlineStr">
         <is>
-          <t>판매 세팅 검토안(보류)</t>
+          <t>협업 진행안 컨펌</t>
         </is>
       </c>
       <c r="R22" s="8" t="inlineStr">
         <is>
-          <t>분기/비정기</t>
+          <t>주 1회</t>
         </is>
       </c>
       <c r="S22" s="8" t="inlineStr">
@@ -9672,7 +9880,7 @@
       </c>
       <c r="U22" s="8" t="inlineStr">
         <is>
-          <t>부자재 카테고리 소싱 기준 정립 후 일괄 세팅</t>
+          <t>인플루언서 협업 진행 기준(가이드) 문서화 후 위임</t>
         </is>
       </c>
     </row>
@@ -9701,10 +9909,10 @@
         </is>
       </c>
       <c r="F23" s="58" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="G23" s="58" t="n">
-        <v>0.6875</v>
+        <v>0.625</v>
       </c>
       <c r="H23" s="7">
         <f>IF(OR(F23="",G23=""),"",(G23-F23)*1440)</f>
@@ -9712,39 +9920,43 @@
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>데이터·정산</t>
+          <t>사내시스템·자동화</t>
         </is>
       </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>DAT-04 리포트·대시보드 작성</t>
+          <t>SYS-01 사내 시스템·앱 기획/개선 요청</t>
         </is>
       </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>POUR스토어 단가·공헌이익·손익계산 대시보드 제작 — 진행중(전주 이월)</t>
+          <t>소싱앱 UX/UI 개선 — 정하님 추가 고도화 건 2차 피드백</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>POUR스토어</t>
+          <t>소싱앱</t>
         </is>
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
-          <t>단가 대시보드, 엑셀</t>
+          <t>소싱앱</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>POUR스토어 가격·마진 통합 대시보드 (pour-construction-form.pages.dev)</t>
-        </is>
-      </c>
-      <c r="O23" s="8" t="n"/>
+          <t>소싱 관리 · 모여라딜 (moyeoradeal-sourcing.pages.dev)</t>
+        </is>
+      </c>
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>용정하</t>
+        </is>
+      </c>
       <c r="P23" s="8" t="n"/>
       <c r="Q23" s="8" t="inlineStr">
         <is>
-          <t>단가·공헌이익·손익 대시보드</t>
+          <t>UX/UI 2차 피드백</t>
         </is>
       </c>
       <c r="R23" s="8" t="inlineStr">
@@ -9759,12 +9971,12 @@
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
+          <t>모름</t>
         </is>
       </c>
       <c r="U23" s="8" t="inlineStr">
         <is>
-          <t>채널 수수료·원가 데이터 자동 연동으로 수기 입력 제거</t>
+          <t>개선 요청·피드백 이력을 앱 내 이슈보드로 관리</t>
         </is>
       </c>
     </row>
@@ -9793,10 +10005,10 @@
         </is>
       </c>
       <c r="F24" s="58" t="n">
-        <v>0.6875</v>
+        <v>0.625</v>
       </c>
       <c r="G24" s="58" t="n">
-        <v>0.75</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="H24" s="7">
         <f>IF(OR(F24="",G24=""),"",(G24-F24)*1440)</f>
@@ -9804,38 +10016,34 @@
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>제조·생산관리</t>
+          <t>마케팅·광고운영</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>MFG-08 MSDS·라벨 등 제품 표시사항 제작</t>
+          <t>MKT-04 인플루언서·체험단 섭외/관리</t>
         </is>
       </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>신제품 코트재 MSDS 컬러별 31개 제작 — 진행중</t>
+          <t>POUR스토어 자사몰에 체험단모집 진행 컨펌 승인 및 서포터즈 관리진행 요청</t>
         </is>
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>코트재 신제품 31색</t>
-        </is>
-      </c>
-      <c r="M24" s="8" t="inlineStr">
-        <is>
-          <t>챗지피티</t>
-        </is>
-      </c>
-      <c r="O24" s="8" t="n"/>
-      <c r="P24" s="8" t="inlineStr">
-        <is>
-          <t>세이고, 쿠팡물류센터</t>
-        </is>
-      </c>
+          <t>POUR스토어 자사몰</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="n"/>
+      <c r="O24" s="8" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="P24" s="8" t="n"/>
       <c r="Q24" s="8" t="inlineStr">
         <is>
-          <t>MSDS 31종</t>
+          <t>체험단 모집 컨펌·서포터즈 관리 요청</t>
         </is>
       </c>
       <c r="R24" s="8" t="inlineStr">
@@ -9845,17 +10053,17 @@
       </c>
       <c r="S24" s="8" t="inlineStr">
         <is>
-          <t>반정형</t>
+          <t>비정형(판단 필요)</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>아니오 - 우리팀 고유</t>
+          <t>아마도 중복</t>
         </is>
       </c>
       <c r="U24" s="8" t="inlineStr">
         <is>
-          <t>품목·색상 데이터 연동으로 MSDS 서식 자동 생성</t>
+          <t>체험단·서포터즈 운영 프로세스 문서화</t>
         </is>
       </c>
     </row>
@@ -9876,18 +10084,18 @@
         </is>
       </c>
       <c r="D25" s="57" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>화</t>
         </is>
       </c>
       <c r="F25" s="58" t="n">
-        <v>0.375</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="G25" s="58" t="n">
-        <v>0.3958333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H25" s="7">
         <f>IF(OR(F25="",G25=""),"",(G25-F25)*1440)</f>
@@ -9895,59 +10103,55 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>기타·행정</t>
+          <t>상품기획·소싱</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>ETC-01 메일·메신저 확인 및 회신</t>
+          <t>PLN-01 신상품 아이템 발굴/시장조사</t>
         </is>
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
-          <t>출근 후 메일·메신저·업무보드 확인 및 회신</t>
+          <t>부자재(롤링독) 판매 세팅 검토 — 우선순위 재조정으로 보류</t>
         </is>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>전사</t>
-        </is>
-      </c>
-      <c r="M25" s="8" t="inlineStr">
-        <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
-        </is>
-      </c>
+          <t>부자재·안전용품</t>
+        </is>
+      </c>
+      <c r="M25" s="8" t="n"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
+          <t>https://pour-construction-form.pages.dev/pourstore-pricing-dashboard</t>
         </is>
       </c>
       <c r="O25" s="8" t="n"/>
       <c r="P25" s="8" t="n"/>
       <c r="Q25" s="8" t="inlineStr">
         <is>
-          <t>회신 처리</t>
+          <t>판매 세팅 검토안(보류)</t>
         </is>
       </c>
       <c r="R25" s="8" t="inlineStr">
         <is>
-          <t>매일</t>
+          <t>분기/비정기</t>
         </is>
       </c>
       <c r="S25" s="8" t="inlineStr">
         <is>
-          <t>정형(매뉴얼화 가능)</t>
+          <t>비정형(판단 필요)</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>예 - 확실히 중복</t>
+          <t>아마도 중복</t>
         </is>
       </c>
       <c r="U25" s="8" t="inlineStr">
         <is>
-          <t>팀별 요청·공지를 업무보드 알림 하나로 일원화</t>
+          <t>부자재 카테고리 소싱 기준 정립 후 일괄 세팅</t>
         </is>
       </c>
     </row>
@@ -9968,18 +10172,18 @@
         </is>
       </c>
       <c r="D26" s="57" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>화</t>
         </is>
       </c>
       <c r="F26" s="58" t="n">
-        <v>0.3958333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G26" s="58" t="n">
-        <v>0.4375</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="H26" s="7">
         <f>IF(OR(F26="",G26=""),"",(G26-F26)*1440)</f>
@@ -9987,67 +10191,59 @@
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>파트너·대리점관리</t>
+          <t>데이터·정산</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>PTR-01 대리점·파트너사 방문·미팅</t>
+          <t>DAT-04 리포트·대시보드 작성</t>
         </is>
       </c>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>부산 대리점 방문 준비 — 촬영물품 및 미팅·인터뷰 질문지 최종 확인</t>
+          <t>POUR스토어 단가·공헌이익·손익계산 대시보드 제작 — 진행중(전주 이월)</t>
         </is>
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>대리점(가나랜드·경남지사)</t>
+          <t>POUR스토어</t>
         </is>
       </c>
       <c r="M26" s="8" t="inlineStr">
         <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
+          <t>단가 대시보드, 엑셀</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
-        </is>
-      </c>
-      <c r="O26" s="8" t="inlineStr">
-        <is>
-          <t>이란</t>
-        </is>
-      </c>
-      <c r="P26" s="8" t="inlineStr">
-        <is>
-          <t>가나랜드, 경남지사</t>
-        </is>
-      </c>
+          <t>POUR스토어 가격·마진 통합 대시보드 (pour-construction-form.pages.dev)</t>
+        </is>
+      </c>
+      <c r="O26" s="8" t="n"/>
+      <c r="P26" s="8" t="n"/>
       <c r="Q26" s="8" t="inlineStr">
         <is>
-          <t>방문 준비 체크리스트</t>
+          <t>단가·공헌이익·손익 대시보드</t>
         </is>
       </c>
       <c r="R26" s="8" t="inlineStr">
         <is>
-          <t>분기/비정기</t>
+          <t>주 2~3회</t>
         </is>
       </c>
       <c r="S26" s="8" t="inlineStr">
         <is>
-          <t>반정형</t>
+          <t>비정형(판단 필요)</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>모름</t>
+          <t>아마도 중복</t>
         </is>
       </c>
       <c r="U26" s="8" t="inlineStr">
         <is>
-          <t>대리점 방문 준비 체크리스트 표준화</t>
+          <t>채널 수수료·원가 데이터 자동 연동으로 수기 입력 제거</t>
         </is>
       </c>
     </row>
@@ -10068,18 +10264,18 @@
         </is>
       </c>
       <c r="D27" s="57" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>화</t>
         </is>
       </c>
       <c r="F27" s="58" t="n">
-        <v>0.4375</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G27" s="58" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.75</v>
       </c>
       <c r="H27" s="7">
         <f>IF(OR(F27="",G27=""),"",(G27-F27)*1440)</f>
@@ -10087,48 +10283,43 @@
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>마케팅·광고운영</t>
+          <t>제조·생산관리</t>
         </is>
       </c>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>MKT-05 프로모션·기획전 기획</t>
+          <t>MFG-08 MSDS·라벨 등 제품 표시사항 제작</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>스토어 8~10월 프로모션 기획안 검토 및 피드백(민지님)</t>
+          <t>신제품 코트재 MSDS 컬러별 31개 제작 — 진행중</t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t>POUR스토어</t>
+          <t>코트재 신제품 31색</t>
         </is>
       </c>
       <c r="M27" s="8" t="inlineStr">
         <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
-        </is>
-      </c>
-      <c r="O27" s="8" t="inlineStr">
-        <is>
-          <t>김민지</t>
-        </is>
-      </c>
-      <c r="P27" s="8" t="n"/>
+          <t>챗지피티</t>
+        </is>
+      </c>
+      <c r="O27" s="8" t="n"/>
+      <c r="P27" s="8" t="inlineStr">
+        <is>
+          <t>세이고, 쿠팡물류센터</t>
+        </is>
+      </c>
       <c r="Q27" s="8" t="inlineStr">
         <is>
-          <t>프로모션 기획 피드백</t>
+          <t>MSDS 31종</t>
         </is>
       </c>
       <c r="R27" s="8" t="inlineStr">
         <is>
-          <t>월 1회</t>
+          <t>1회성</t>
         </is>
       </c>
       <c r="S27" s="8" t="inlineStr">
@@ -10138,12 +10329,12 @@
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
+          <t>아니오 - 우리팀 고유</t>
         </is>
       </c>
       <c r="U27" s="8" t="inlineStr">
         <is>
-          <t>본부 공용 프로모션 캘린더로 3팀 일정·중복 방지</t>
+          <t>품목·색상 데이터 연동으로 MSDS 서식 자동 생성</t>
         </is>
       </c>
     </row>
@@ -10172,10 +10363,10 @@
         </is>
       </c>
       <c r="F28" s="58" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.375</v>
       </c>
       <c r="G28" s="58" t="n">
-        <v>0.5</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="H28" s="7">
         <f>IF(OR(F28="",G28=""),"",(G28-F28)*1440)</f>
@@ -10183,39 +10374,44 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>마케팅·광고운영</t>
+          <t>기타·행정</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>MKT-02 광고 성과 모니터링·최적화</t>
+          <t>ETC-01 메일·메신저 확인 및 회신</t>
         </is>
       </c>
       <c r="K28" s="8" t="inlineStr">
         <is>
-          <t>신제품(철재페인트) 키워드광고 상위노출 확인</t>
+          <t>출근 후 메일·메신저·업무보드 확인 및 회신</t>
         </is>
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>신제품 철재페인트 / 네이버</t>
+          <t>전사</t>
         </is>
       </c>
       <c r="M28" s="8" t="inlineStr">
         <is>
-          <t>네이버 검색, 검색광고 관리자</t>
+          <t>CRM센터-POUR OS(업무보드)</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>https://pourstorecrm.web.app/pour-os</t>
         </is>
       </c>
       <c r="O28" s="8" t="n"/>
       <c r="P28" s="8" t="n"/>
       <c r="Q28" s="8" t="inlineStr">
         <is>
-          <t>노출 순위 점검 메모</t>
+          <t>회신 처리</t>
         </is>
       </c>
       <c r="R28" s="8" t="inlineStr">
         <is>
-          <t>주 2~3회</t>
+          <t>매일</t>
         </is>
       </c>
       <c r="S28" s="8" t="inlineStr">
@@ -10230,7 +10426,7 @@
       </c>
       <c r="U28" s="8" t="inlineStr">
         <is>
-          <t>키워드 순위 자동 추적 리포트로 대체</t>
+          <t>팀별 요청·공지를 업무보드 알림 하나로 일원화</t>
         </is>
       </c>
     </row>
@@ -10259,10 +10455,10 @@
         </is>
       </c>
       <c r="F29" s="58" t="n">
-        <v>0.5</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="G29" s="58" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="H29" s="7">
         <f>IF(OR(F29="",G29=""),"",(G29-F29)*1440)</f>
@@ -10270,40 +10466,69 @@
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>기타·행정</t>
+          <t>파트너·대리점관리</t>
         </is>
       </c>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>ETC-05 휴게·점심</t>
+          <t>PTR-01 대리점·파트너사 방문·미팅</t>
         </is>
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>점심 및 휴게</t>
-        </is>
-      </c>
-      <c r="L29" s="8" t="n"/>
-      <c r="M29" s="8" t="n"/>
-      <c r="O29" s="8" t="n"/>
-      <c r="P29" s="8" t="n"/>
-      <c r="Q29" s="8" t="n"/>
+          <t>부산 대리점 방문 준비 — 촬영물품 및 미팅·인터뷰 질문지 최종 확인</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>대리점(가나랜드·경남지사)</t>
+        </is>
+      </c>
+      <c r="M29" s="8" t="inlineStr">
+        <is>
+          <t>CRM센터-POUR OS(업무보드)</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>https://pourstorecrm.web.app/pour-os</t>
+        </is>
+      </c>
+      <c r="O29" s="8" t="inlineStr">
+        <is>
+          <t>이란</t>
+        </is>
+      </c>
+      <c r="P29" s="8" t="inlineStr">
+        <is>
+          <t>가나랜드, 경남지사</t>
+        </is>
+      </c>
+      <c r="Q29" s="8" t="inlineStr">
+        <is>
+          <t>방문 준비 체크리스트</t>
+        </is>
+      </c>
       <c r="R29" s="8" t="inlineStr">
         <is>
-          <t>매일</t>
+          <t>분기/비정기</t>
         </is>
       </c>
       <c r="S29" s="8" t="inlineStr">
         <is>
-          <t>정형(매뉴얼화 가능)</t>
+          <t>반정형</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>예 - 확실히 중복</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="n"/>
+          <t>모름</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>대리점 방문 준비 체크리스트 표준화</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -10330,10 +10555,10 @@
         </is>
       </c>
       <c r="F30" s="58" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="G30" s="58" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.4375</v>
       </c>
       <c r="H30" s="7">
         <f>IF(OR(F30="",G30=""),"",(G30-F30)*1440)</f>
@@ -10341,22 +10566,22 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>기획·보고·회의</t>
+          <t>마케팅·광고운영</t>
         </is>
       </c>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>MGT-06 팀원 업무·산출물 검토·피드백</t>
+          <t>MKT-05 프로모션·기획전 기획</t>
         </is>
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>AX+업무리스트 보고서 검토 및 피드백(정하님)</t>
+          <t>스토어 8~10월 프로모션 기획안 검토 및 피드백(민지님)</t>
         </is>
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>팀 업무관리</t>
+          <t>POUR스토어</t>
         </is>
       </c>
       <c r="M30" s="8" t="inlineStr">
@@ -10371,23 +10596,23 @@
       </c>
       <c r="O30" s="8" t="inlineStr">
         <is>
-          <t>용정하</t>
+          <t>김민지</t>
         </is>
       </c>
       <c r="P30" s="8" t="n"/>
       <c r="Q30" s="8" t="inlineStr">
         <is>
-          <t>검토 피드백</t>
+          <t>프로모션 기획 피드백</t>
         </is>
       </c>
       <c r="R30" s="8" t="inlineStr">
         <is>
-          <t>주 1회</t>
+          <t>월 1회</t>
         </is>
       </c>
       <c r="S30" s="8" t="inlineStr">
         <is>
-          <t>비정형(판단 필요)</t>
+          <t>반정형</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
@@ -10397,7 +10622,7 @@
       </c>
       <c r="U30" s="8" t="inlineStr">
         <is>
-          <t>업무보드 데이터 자동 집계로 보고서 수기작성 제거</t>
+          <t>본부 공용 프로모션 캘린더로 3팀 일정·중복 방지</t>
         </is>
       </c>
     </row>
@@ -10426,10 +10651,10 @@
         </is>
       </c>
       <c r="F31" s="58" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.4375</v>
       </c>
       <c r="G31" s="58" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="H31" s="7">
         <f>IF(OR(F31="",G31=""),"",(G31-F31)*1440)</f>
@@ -10437,63 +10662,58 @@
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>기획·보고·회의</t>
+          <t>채널·스토어운영</t>
         </is>
       </c>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>MGT-06 팀원 업무·산출물 검토·피드백</t>
+          <t>CHN-01 상품 등록·수정(옵션/가격)</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>AX+업무리스트 보고서 검토 및 피드백(채림님)</t>
+          <t>자사몰 판매가 변경 건 8/19까지 수정 요청</t>
         </is>
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>팀 업무관리</t>
+          <t>POUR스토어 자사몰</t>
         </is>
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
+          <t>자사몰 관리자</t>
         </is>
       </c>
       <c r="O31" s="8" t="inlineStr">
         <is>
-          <t>양채림</t>
+          <t>이란, 김민지</t>
         </is>
       </c>
       <c r="P31" s="8" t="n"/>
       <c r="Q31" s="8" t="inlineStr">
         <is>
-          <t>검토 피드백</t>
+          <t>판매가 변경 요청(8/19까지)</t>
         </is>
       </c>
       <c r="R31" s="8" t="inlineStr">
         <is>
-          <t>주 1회</t>
+          <t>분기/비정기</t>
         </is>
       </c>
       <c r="S31" s="8" t="inlineStr">
         <is>
-          <t>비정형(판단 필요)</t>
+          <t>정형(매뉴얼화 가능)</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
+          <t>예 - 확실히 중복</t>
         </is>
       </c>
       <c r="U31" s="8" t="inlineStr">
         <is>
-          <t>업무보드 데이터 자동 집계로 보고서 수기작성 제거</t>
+          <t>단가 대시보드와 채널 판매가 연동으로 수기 변경 제거</t>
         </is>
       </c>
     </row>
@@ -10522,10 +10742,10 @@
         </is>
       </c>
       <c r="F32" s="58" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="G32" s="58" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="H32" s="7">
         <f>IF(OR(F32="",G32=""),"",(G32-F32)*1440)</f>
@@ -10533,39 +10753,38 @@
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>기획·보고·회의</t>
+          <t>마케팅·광고운영</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>MGT-07 업무 인수인계·이관</t>
+          <t>MKT-01 광고 계정 세팅·집행(메타/구글 등)</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>그로홈 업무 인수인계 받음 — 담당 범위·진행건 확인</t>
+          <t>네이버쇼핑 광고를 위해 카페24 네이버 쇼핑 서비스 신청 요청</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>그로홈</t>
+          <t>POUR스토어 자사몰 / 네이버쇼핑</t>
         </is>
       </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
-        </is>
-      </c>
-      <c r="O32" s="8" t="n"/>
+          <t>카페24 관리자</t>
+        </is>
+      </c>
+      <c r="O32" s="8" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
       <c r="P32" s="8" t="n"/>
       <c r="Q32" s="8" t="inlineStr">
         <is>
-          <t>인수인계 항목 정리</t>
+          <t>네이버쇼핑 서비스 신청</t>
         </is>
       </c>
       <c r="R32" s="8" t="inlineStr">
@@ -10575,17 +10794,17 @@
       </c>
       <c r="S32" s="8" t="inlineStr">
         <is>
-          <t>비정형(판단 필요)</t>
+          <t>정형(매뉴얼화 가능)</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>모름</t>
+          <t>아마도 중복</t>
         </is>
       </c>
       <c r="U32" s="8" t="inlineStr">
         <is>
-          <t>인수인계 체크리스트·담당 매핑표 상시 관리</t>
+          <t>채널 광고 계정·서비스 신청 체크리스트화</t>
         </is>
       </c>
     </row>
@@ -10614,10 +10833,10 @@
         </is>
       </c>
       <c r="F33" s="58" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G33" s="58" t="n">
-        <v>0.6875</v>
+        <v>0.5</v>
       </c>
       <c r="H33" s="7">
         <f>IF(OR(F33="",G33=""),"",(G33-F33)*1440)</f>
@@ -10625,50 +10844,54 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>콘텐츠제작</t>
+          <t>마케팅·광고운영</t>
         </is>
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>CNT-07 카탈로그·영업자료 제작</t>
+          <t>MKT-02 광고 성과 모니터링·최적화</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>부자재 소개 카달로그 제작</t>
+          <t>신제품(철재페인트) 키워드광고 상위노출 확인</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>부자재</t>
-        </is>
-      </c>
-      <c r="M33" s="8" t="n"/>
+          <t>신제품 철재페인트 / 네이버</t>
+        </is>
+      </c>
+      <c r="M33" s="8" t="inlineStr">
+        <is>
+          <t>네이버 검색, 검색광고 관리자</t>
+        </is>
+      </c>
       <c r="O33" s="8" t="n"/>
       <c r="P33" s="8" t="n"/>
       <c r="Q33" s="8" t="inlineStr">
         <is>
-          <t>부자재 소개 카달로그</t>
+          <t>노출 순위 점검 메모</t>
         </is>
       </c>
       <c r="R33" s="8" t="inlineStr">
         <is>
-          <t>1회성</t>
+          <t>주 2~3회</t>
         </is>
       </c>
       <c r="S33" s="8" t="inlineStr">
         <is>
-          <t>반정형</t>
+          <t>정형(매뉴얼화 가능)</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
+          <t>예 - 확실히 중복</t>
         </is>
       </c>
       <c r="U33" s="8" t="inlineStr">
         <is>
-          <t>상품 마스터 데이터로 카달로그 자동 생성</t>
+          <t>키워드 순위 자동 추적 리포트로 대체</t>
         </is>
       </c>
     </row>
@@ -10697,10 +10920,10 @@
         </is>
       </c>
       <c r="F34" s="58" t="n">
-        <v>0.6875</v>
+        <v>0.5</v>
       </c>
       <c r="G34" s="58" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="H34" s="7">
         <f>IF(OR(F34="",G34=""),"",(G34-F34)*1440)</f>
@@ -10708,61 +10931,40 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>데이터·정산</t>
+          <t>기타·행정</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t>DAT-04 리포트·대시보드 작성</t>
+          <t>ETC-05 휴게·점심</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>POUR스토어 단가·공헌이익·손익계산 대시보드 제작 — 진행중</t>
-        </is>
-      </c>
-      <c r="L34" s="8" t="inlineStr">
-        <is>
-          <t>POUR스토어</t>
-        </is>
-      </c>
-      <c r="M34" s="8" t="inlineStr">
-        <is>
-          <t>단가 대시보드, 엑셀</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>POUR스토어 가격·마진 통합 대시보드 (pour-construction-form.pages.dev)</t>
-        </is>
-      </c>
+          <t>점심 및 휴게</t>
+        </is>
+      </c>
+      <c r="L34" s="8" t="n"/>
+      <c r="M34" s="8" t="n"/>
       <c r="O34" s="8" t="n"/>
       <c r="P34" s="8" t="n"/>
-      <c r="Q34" s="8" t="inlineStr">
-        <is>
-          <t>단가·공헌이익·손익 대시보드</t>
-        </is>
-      </c>
+      <c r="Q34" s="8" t="n"/>
       <c r="R34" s="8" t="inlineStr">
         <is>
-          <t>주 2~3회</t>
+          <t>매일</t>
         </is>
       </c>
       <c r="S34" s="8" t="inlineStr">
         <is>
-          <t>비정형(판단 필요)</t>
+          <t>정형(매뉴얼화 가능)</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>채널 수수료·원가 데이터 자동 연동으로 수기 입력 제거</t>
-        </is>
-      </c>
+          <t>예 - 확실히 중복</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -10789,10 +10991,10 @@
         </is>
       </c>
       <c r="F35" s="58" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="G35" s="58" t="n">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="H35" s="7">
         <f>IF(OR(F35="",G35=""),"",(G35-F35)*1440)</f>
@@ -10800,58 +11002,63 @@
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>제조·생산관리</t>
+          <t>기획·보고·회의</t>
         </is>
       </c>
       <c r="J35" s="8" t="inlineStr">
         <is>
-          <t>MFG-08 MSDS·라벨 등 제품 표시사항 제작</t>
+          <t>MGT-06 팀원 업무·산출물 검토·피드백</t>
         </is>
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>신제품 코트재 MSDS 컬러별 31개 제작 — 진행중</t>
+          <t>AX+업무리스트 보고서 검토 및 피드백(정하님)</t>
         </is>
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>코트재 신제품 31색</t>
+          <t>팀 업무관리</t>
         </is>
       </c>
       <c r="M35" s="8" t="inlineStr">
         <is>
-          <t>챗지피티</t>
-        </is>
-      </c>
-      <c r="O35" s="8" t="n"/>
-      <c r="P35" s="8" t="inlineStr">
-        <is>
-          <t>세이고, 쿠팡물류센터</t>
-        </is>
-      </c>
+          <t>CRM센터-POUR OS(업무보드)</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>https://pourstorecrm.web.app/pour-os</t>
+        </is>
+      </c>
+      <c r="O35" s="8" t="inlineStr">
+        <is>
+          <t>용정하</t>
+        </is>
+      </c>
+      <c r="P35" s="8" t="n"/>
       <c r="Q35" s="8" t="inlineStr">
         <is>
-          <t>MSDS 31종</t>
+          <t>검토 피드백</t>
         </is>
       </c>
       <c r="R35" s="8" t="inlineStr">
         <is>
-          <t>1회성</t>
+          <t>주 1회</t>
         </is>
       </c>
       <c r="S35" s="8" t="inlineStr">
         <is>
-          <t>반정형</t>
+          <t>비정형(판단 필요)</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>아니오 - 우리팀 고유</t>
+          <t>아마도 중복</t>
         </is>
       </c>
       <c r="U35" s="8" t="inlineStr">
         <is>
-          <t>품목·색상 데이터 연동으로 MSDS 서식 자동 생성</t>
+          <t>업무보드 데이터 자동 집계로 보고서 수기작성 제거</t>
         </is>
       </c>
     </row>
@@ -10872,18 +11079,18 @@
         </is>
       </c>
       <c r="D36" s="57" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>수</t>
         </is>
       </c>
       <c r="F36" s="58" t="n">
-        <v>0.375</v>
+        <v>0.5625</v>
       </c>
       <c r="G36" s="58" t="n">
-        <v>0.3958333333333333</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="H36" s="7">
         <f>IF(OR(F36="",G36=""),"",(G36-F36)*1440)</f>
@@ -10891,22 +11098,22 @@
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>기타·행정</t>
+          <t>기획·보고·회의</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>ETC-01 메일·메신저 확인 및 회신</t>
+          <t>MGT-06 팀원 업무·산출물 검토·피드백</t>
         </is>
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>출근 후 메일·메신저·업무보드 확인 및 회신</t>
+          <t>AX+업무리스트 보고서 검토 및 피드백(채림님)</t>
         </is>
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
-          <t>전사</t>
+          <t>팀 업무관리</t>
         </is>
       </c>
       <c r="M36" s="8" t="inlineStr">
@@ -10919,31 +11126,35 @@
           <t>https://pourstorecrm.web.app/pour-os</t>
         </is>
       </c>
-      <c r="O36" s="8" t="n"/>
+      <c r="O36" s="8" t="inlineStr">
+        <is>
+          <t>양채림</t>
+        </is>
+      </c>
       <c r="P36" s="8" t="n"/>
       <c r="Q36" s="8" t="inlineStr">
         <is>
-          <t>회신 처리</t>
+          <t>검토 피드백</t>
         </is>
       </c>
       <c r="R36" s="8" t="inlineStr">
         <is>
-          <t>매일</t>
+          <t>주 1회</t>
         </is>
       </c>
       <c r="S36" s="8" t="inlineStr">
         <is>
-          <t>정형(매뉴얼화 가능)</t>
+          <t>비정형(판단 필요)</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>예 - 확실히 중복</t>
+          <t>아마도 중복</t>
         </is>
       </c>
       <c r="U36" s="8" t="inlineStr">
         <is>
-          <t>팀별 요청·공지를 업무보드 알림 하나로 일원화</t>
+          <t>업무보드 데이터 자동 집계로 보고서 수기작성 제거</t>
         </is>
       </c>
     </row>
@@ -10964,18 +11175,18 @@
         </is>
       </c>
       <c r="D37" s="57" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>수</t>
         </is>
       </c>
       <c r="F37" s="58" t="n">
-        <v>0.3958333333333333</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="G37" s="58" t="n">
-        <v>0.4375</v>
+        <v>0.625</v>
       </c>
       <c r="H37" s="7">
         <f>IF(OR(F37="",G37=""),"",(G37-F37)*1440)</f>
@@ -10983,62 +11194,59 @@
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>마케팅·광고운영</t>
+          <t>기획·보고·회의</t>
         </is>
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>MKT-08 제휴마케팅(링크프라이스 등) 운영·성과확인</t>
+          <t>MGT-07 업무 인수인계·이관</t>
         </is>
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>링크프라이스 네이버쇼핑·파워링크 주간보고 수령 → 본부장님 보고 → 보성님 인계</t>
+          <t>그로홈 업무 인수인계 받음 — 담당 범위·진행건 확인</t>
         </is>
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
-          <t>POUR스토어 / 네이버쇼핑·파워링크</t>
+          <t>그로홈</t>
         </is>
       </c>
       <c r="M37" s="8" t="inlineStr">
         <is>
-          <t>링크프라이스 관리자</t>
-        </is>
-      </c>
-      <c r="O37" s="8" t="inlineStr">
-        <is>
-          <t>본부장, 보성님</t>
-        </is>
-      </c>
-      <c r="P37" s="8" t="inlineStr">
-        <is>
-          <t>링크프라이스</t>
-        </is>
-      </c>
+          <t>CRM센터-POUR OS(업무보드)</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>https://pourstorecrm.web.app/pour-os</t>
+        </is>
+      </c>
+      <c r="O37" s="8" t="n"/>
+      <c r="P37" s="8" t="n"/>
       <c r="Q37" s="8" t="inlineStr">
         <is>
-          <t>제휴·검색광고 주간보고</t>
+          <t>인수인계 항목 정리</t>
         </is>
       </c>
       <c r="R37" s="8" t="inlineStr">
         <is>
-          <t>주 1회</t>
+          <t>1회성</t>
         </is>
       </c>
       <c r="S37" s="8" t="inlineStr">
         <is>
-          <t>정형(매뉴얼화 가능)</t>
+          <t>비정형(판단 필요)</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>예 - 확실히 중복</t>
+          <t>모름</t>
         </is>
       </c>
       <c r="U37" s="8" t="inlineStr">
         <is>
-          <t>주간보고 자동 생성 후 공유(수령→전달 단계 제거)</t>
+          <t>인수인계 체크리스트·담당 매핑표 상시 관리</t>
         </is>
       </c>
     </row>
@@ -11059,18 +11267,18 @@
         </is>
       </c>
       <c r="D38" s="57" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>수</t>
         </is>
       </c>
       <c r="F38" s="58" t="n">
-        <v>0.4375</v>
+        <v>0.625</v>
       </c>
       <c r="G38" s="58" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="H38" s="7">
         <f>IF(OR(F38="",G38=""),"",(G38-F38)*1440)</f>
@@ -11078,48 +11286,44 @@
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>기타·행정</t>
+          <t>콘텐츠제작</t>
         </is>
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>ETC-02 행정·경비·구매 처리</t>
+          <t>CNT-05 SNS 채널 운영·업로드</t>
         </is>
       </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
-          <t>씰맥스프로 결제 처리 및 세이고 입고내역 자료 송부(김성준 공장장님께)</t>
+          <t>공식계정 블로그 메인페이지 스킨 변경 (다음주에) 요청</t>
         </is>
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
-          <t>씰맥스프로 / 세이고</t>
+          <t>공식 블로그</t>
         </is>
       </c>
       <c r="M38" s="8" t="n"/>
       <c r="O38" s="8" t="inlineStr">
         <is>
-          <t>김성준 공장장</t>
-        </is>
-      </c>
-      <c r="P38" s="8" t="inlineStr">
-        <is>
-          <t>세이고</t>
-        </is>
-      </c>
+          <t>양채림</t>
+        </is>
+      </c>
+      <c r="P38" s="8" t="n"/>
       <c r="Q38" s="8" t="inlineStr">
         <is>
-          <t>결제 완료·입고내역 자료</t>
+          <t>블로그 메인 스킨 변경 요청</t>
         </is>
       </c>
       <c r="R38" s="8" t="inlineStr">
         <is>
-          <t>주 1회</t>
+          <t>1회성</t>
         </is>
       </c>
       <c r="S38" s="8" t="inlineStr">
         <is>
-          <t>정형(매뉴얼화 가능)</t>
+          <t>반정형</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
@@ -11129,7 +11333,7 @@
       </c>
       <c r="U38" s="8" t="inlineStr">
         <is>
-          <t>결제·입고내역 자동 정산 시트 연동</t>
+          <t>채널별 디자인 자산 공용 관리</t>
         </is>
       </c>
     </row>
@@ -11150,18 +11354,18 @@
         </is>
       </c>
       <c r="D39" s="57" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>수</t>
         </is>
       </c>
       <c r="F39" s="58" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="G39" s="58" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H39" s="7">
         <f>IF(OR(F39="",G39=""),"",(G39-F39)*1440)</f>
@@ -11169,53 +11373,40 @@
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>기획·보고·회의</t>
+          <t>콘텐츠제작</t>
         </is>
       </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>MGT-06 팀원 업무·산출물 검토·피드백</t>
+          <t>CNT-06 디자인 시안 피드백</t>
         </is>
       </c>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>정하님 업무정리 리스트 검토</t>
+          <t>셀러 제안 시 첨부배너 검토 및 승인</t>
         </is>
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
-          <t>팀 업무관리</t>
-        </is>
-      </c>
-      <c r="M39" s="8" t="inlineStr">
-        <is>
-          <t>CRM센터-POUR OS(업무보드)</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
-        </is>
-      </c>
-      <c r="O39" s="8" t="inlineStr">
-        <is>
-          <t>용정하</t>
-        </is>
-      </c>
+          <t>셀러 제안용 배너</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="n"/>
+      <c r="O39" s="8" t="n"/>
       <c r="P39" s="8" t="n"/>
       <c r="Q39" s="8" t="inlineStr">
         <is>
-          <t>검토 의견</t>
+          <t>첨부배너 검토·승인</t>
         </is>
       </c>
       <c r="R39" s="8" t="inlineStr">
         <is>
-          <t>주 1회</t>
+          <t>분기/비정기</t>
         </is>
       </c>
       <c r="S39" s="8" t="inlineStr">
         <is>
-          <t>비정형(판단 필요)</t>
+          <t>반정형</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
@@ -11225,7 +11416,7 @@
       </c>
       <c r="U39" s="8" t="inlineStr">
         <is>
-          <t>업무보드 데이터 자동 집계로 대체</t>
+          <t>제안용 배너 템플릿 라이브러리화</t>
         </is>
       </c>
     </row>
@@ -11246,18 +11437,18 @@
         </is>
       </c>
       <c r="D40" s="57" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>수</t>
         </is>
       </c>
       <c r="F40" s="58" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G40" s="58" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="H40" s="7">
         <f>IF(OR(F40="",G40=""),"",(G40-F40)*1440)</f>
@@ -11265,40 +11456,52 @@
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>기타·행정</t>
+          <t>콘텐츠제작</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>ETC-05 휴게·점심</t>
+          <t>CNT-07 카탈로그·영업자료 제작</t>
         </is>
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>점심 및 휴게</t>
-        </is>
-      </c>
-      <c r="L40" s="8" t="n"/>
+          <t>부자재 소개 카달로그 제작</t>
+        </is>
+      </c>
+      <c r="L40" s="8" t="inlineStr">
+        <is>
+          <t>부자재</t>
+        </is>
+      </c>
       <c r="M40" s="8" t="n"/>
       <c r="O40" s="8" t="n"/>
       <c r="P40" s="8" t="n"/>
-      <c r="Q40" s="8" t="n"/>
+      <c r="Q40" s="8" t="inlineStr">
+        <is>
+          <t>부자재 소개 카달로그</t>
+        </is>
+      </c>
       <c r="R40" s="8" t="inlineStr">
         <is>
-          <t>매일</t>
+          <t>1회성</t>
         </is>
       </c>
       <c r="S40" s="8" t="inlineStr">
         <is>
-          <t>정형(매뉴얼화 가능)</t>
+          <t>반정형</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>예 - 확실히 중복</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="n"/>
+          <t>아마도 중복</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>상품 마스터 데이터로 카달로그 자동 생성</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -11317,18 +11520,18 @@
         </is>
       </c>
       <c r="D41" s="57" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>수</t>
         </is>
       </c>
       <c r="F41" s="58" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G41" s="58" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="H41" s="7">
         <f>IF(OR(F41="",G41=""),"",(G41-F41)*1440)</f>
@@ -11336,52 +11539,44 @@
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>마케팅·광고운영</t>
+          <t>데이터·정산</t>
         </is>
       </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
-          <t>MKT-04 인플루언서·체험단 섭외/관리</t>
+          <t>DAT-04 리포트·대시보드 작성</t>
         </is>
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>채림님 퍼포먼스마케팅 진행 방안(①직판 ②대리점·파트너사 2트랙 바이럴) 안내 및 매체·대행사 시장조사 요청</t>
+          <t>POUR스토어 단가·공헌이익·손익계산 대시보드 제작 — 진행중</t>
         </is>
       </c>
       <c r="L41" s="8" t="inlineStr">
         <is>
-          <t>POUR스토어 / 블로그·유튜브·카페·인스타</t>
+          <t>POUR스토어</t>
         </is>
       </c>
       <c r="M41" s="8" t="inlineStr">
         <is>
-          <t>레뷰, 리뷰플레이스</t>
+          <t>단가 대시보드, 엑셀</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>https://pourstorecrm.web.app/pour-os</t>
-        </is>
-      </c>
-      <c r="O41" s="8" t="inlineStr">
-        <is>
-          <t>양채림</t>
-        </is>
-      </c>
-      <c r="P41" s="8" t="inlineStr">
-        <is>
-          <t>인플루언서, 바이럴 대행사(레뷰 등)</t>
-        </is>
-      </c>
+          <t>POUR스토어 가격·마진 통합 대시보드 (pour-construction-form.pages.dev)</t>
+        </is>
+      </c>
+      <c r="O41" s="8" t="n"/>
+      <c r="P41" s="8" t="n"/>
       <c r="Q41" s="8" t="inlineStr">
         <is>
-          <t>진행 방안 안내·시장조사 요청서</t>
+          <t>단가·공헌이익·손익 대시보드</t>
         </is>
       </c>
       <c r="R41" s="8" t="inlineStr">
         <is>
-          <t>주 1회</t>
+          <t>주 2~3회</t>
         </is>
       </c>
       <c r="S41" s="8" t="inlineStr">
@@ -11396,7 +11591,7 @@
       </c>
       <c r="U41" s="8" t="inlineStr">
         <is>
-          <t>바이럴 매체·대행사 후보 DB 공용화</t>
+          <t>채널 수수료·원가 데이터 자동 연동으로 수기 입력 제거</t>
         </is>
       </c>
     </row>
@@ -11417,18 +11612,18 @@
         </is>
       </c>
       <c r="D42" s="57" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>수</t>
         </is>
       </c>
       <c r="F42" s="58" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="G42" s="58" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="H42" s="7">
         <f>IF(OR(F42="",G42=""),"",(G42-F42)*1440)</f>
@@ -11436,34 +11631,38 @@
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>채널·스토어운영</t>
+          <t>제조·생산관리</t>
         </is>
       </c>
       <c r="J42" s="8" t="inlineStr">
         <is>
-          <t>CHN-03 자사몰 운영·관리</t>
+          <t>MFG-08 MSDS·라벨 등 제품 표시사항 제작</t>
         </is>
       </c>
       <c r="K42" s="8" t="inlineStr">
         <is>
-          <t>자사몰 회원 등급별 구매가능 상품 확인 페이지 제작 및 랜딩 링크 삽입 요청</t>
+          <t>신제품 코트재 MSDS 컬러별 31개 제작 — 진행중</t>
         </is>
       </c>
       <c r="L42" s="8" t="inlineStr">
         <is>
-          <t>POUR스토어 자사몰</t>
+          <t>코트재 신제품 31색</t>
         </is>
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>자사몰 관리자</t>
+          <t>챗지피티</t>
         </is>
       </c>
       <c r="O42" s="8" t="n"/>
-      <c r="P42" s="8" t="n"/>
+      <c r="P42" s="8" t="inlineStr">
+        <is>
+          <t>세이고, 쿠팡물류센터</t>
+        </is>
+      </c>
       <c r="Q42" s="8" t="inlineStr">
         <is>
-          <t>등급별 구매가능 페이지 요청서</t>
+          <t>MSDS 31종</t>
         </is>
       </c>
       <c r="R42" s="8" t="inlineStr">
@@ -11478,12 +11677,12 @@
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>모름</t>
+          <t>아니오 - 우리팀 고유</t>
         </is>
       </c>
       <c r="U42" s="8" t="inlineStr">
         <is>
-          <t>회원등급·판매권한 데이터 연동으로 페이지 자동 생성</t>
+          <t>품목·색상 데이터 연동으로 MSDS 서식 자동 생성</t>
         </is>
       </c>
     </row>
@@ -11512,10 +11711,10 @@
         </is>
       </c>
       <c r="F43" s="58" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.375</v>
       </c>
       <c r="G43" s="58" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="H43" s="7">
         <f>IF(OR(F43="",G43=""),"",(G43-F43)*1440)</f>
@@ -11523,59 +11722,59 @@
       </c>
       <c r="I43" s="8" t="inlineStr">
         <is>
-          <t>데이터·정산</t>
+          <t>기타·행정</t>
         </is>
       </c>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t>DAT-04 리포트·대시보드 작성</t>
+          <t>ETC-01 메일·메신저 확인 및 회신</t>
         </is>
       </c>
       <c r="K43" s="8" t="inlineStr">
         <is>
-          <t>POUR스토어 단가·공헌이익·손익계산 대시보드 제작 — 진행중</t>
+          <t>출근 후 메일·메신저·업무보드 확인 및 회신</t>
         </is>
       </c>
       <c r="L43" s="8" t="inlineStr">
         <is>
-          <t>POUR스토어</t>
+          <t>전사</t>
         </is>
       </c>
       <c r="M43" s="8" t="inlineStr">
         <is>
-          <t>단가 대시보드, 엑셀</t>
+          <t>CRM센터-POUR OS(업무보드)</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>POUR스토어 가격·마진 통합 대시보드 (pour-construction-form.pages.dev)</t>
+          <t>https://pourstorecrm.web.app/pour-os</t>
         </is>
       </c>
       <c r="O43" s="8" t="n"/>
       <c r="P43" s="8" t="n"/>
       <c r="Q43" s="8" t="inlineStr">
         <is>
-          <t>단가·공헌이익·손익 대시보드</t>
+          <t>회신 처리</t>
         </is>
       </c>
       <c r="R43" s="8" t="inlineStr">
         <is>
-          <t>주 2~3회</t>
+          <t>매일</t>
         </is>
       </c>
       <c r="S43" s="8" t="inlineStr">
         <is>
-          <t>비정형(판단 필요)</t>
+          <t>정형(매뉴얼화 가능)</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
+          <t>예 - 확실히 중복</t>
         </is>
       </c>
       <c r="U43" s="8" t="inlineStr">
         <is>
-          <t>채널 수수료·원가 데이터 자동 연동으로 수기 입력 제거</t>
+          <t>팀별 요청·공지를 업무보드 알림 하나로 일원화</t>
         </is>
       </c>
     </row>
@@ -11604,10 +11803,10 @@
         </is>
       </c>
       <c r="F44" s="58" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="G44" s="58" t="n">
-        <v>0.75</v>
+        <v>0.4375</v>
       </c>
       <c r="H44" s="7">
         <f>IF(OR(F44="",G44=""),"",(G44-F44)*1440)</f>
@@ -11615,58 +11814,62 @@
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>제조·생산관리</t>
+          <t>마케팅·광고운영</t>
         </is>
       </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>MFG-08 MSDS·라벨 등 제품 표시사항 제작</t>
+          <t>MKT-08 제휴마케팅(링크프라이스 등) 운영·성과확인</t>
         </is>
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>신제품 코트재 MSDS 컬러별 31개 제작 — 진행중</t>
+          <t>링크프라이스 네이버쇼핑·파워링크 주간보고 수령 → 본부장님 보고 → 보성님 인계</t>
         </is>
       </c>
       <c r="L44" s="8" t="inlineStr">
         <is>
-          <t>코트재 신제품 31색</t>
+          <t>POUR스토어 / 네이버쇼핑·파워링크</t>
         </is>
       </c>
       <c r="M44" s="8" t="inlineStr">
         <is>
-          <t>챗지피티</t>
-        </is>
-      </c>
-      <c r="O44" s="8" t="n"/>
+          <t>링크프라이스 관리자</t>
+        </is>
+      </c>
+      <c r="O44" s="8" t="inlineStr">
+        <is>
+          <t>본부장, 보성님</t>
+        </is>
+      </c>
       <c r="P44" s="8" t="inlineStr">
         <is>
-          <t>세이고, 쿠팡물류센터</t>
+          <t>링크프라이스</t>
         </is>
       </c>
       <c r="Q44" s="8" t="inlineStr">
         <is>
-          <t>MSDS 31종</t>
+          <t>제휴·검색광고 주간보고</t>
         </is>
       </c>
       <c r="R44" s="8" t="inlineStr">
         <is>
-          <t>1회성</t>
+          <t>주 1회</t>
         </is>
       </c>
       <c r="S44" s="8" t="inlineStr">
         <is>
-          <t>반정형</t>
+          <t>정형(매뉴얼화 가능)</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>아니오 - 우리팀 고유</t>
+          <t>예 - 확실히 중복</t>
         </is>
       </c>
       <c r="U44" s="8" t="inlineStr">
         <is>
-          <t>품목·색상 데이터 연동으로 MSDS 서식 자동 생성</t>
+          <t>주간보고 자동 생성 후 공유(수령→전달 단계 제거)</t>
         </is>
       </c>
     </row>
@@ -11687,18 +11890,18 @@
         </is>
       </c>
       <c r="D45" s="57" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>목</t>
         </is>
       </c>
       <c r="F45" s="58" t="n">
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="G45" s="58" t="n">
-        <v>0.4375</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="H45" s="7">
         <f>IF(OR(F45="",G45=""),"",(G45-F45)*1440)</f>
@@ -11711,26 +11914,38 @@
       </c>
       <c r="J45" s="8" t="inlineStr">
         <is>
-          <t>ETC-04 이동·외근</t>
+          <t>ETC-02 행정·경비·구매 처리</t>
         </is>
       </c>
       <c r="K45" s="8" t="inlineStr">
         <is>
-          <t>부산 대리점 방문 이동(사무실 → 경남지사)</t>
+          <t>씰맥스프로 결제 처리 및 세이고 입고내역 자료 송부(김성준 공장장님께)</t>
         </is>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
-          <t>대리점(경남지사)</t>
+          <t>씰맥스프로 / 세이고</t>
         </is>
       </c>
       <c r="M45" s="8" t="n"/>
-      <c r="O45" s="8" t="n"/>
-      <c r="P45" s="8" t="n"/>
-      <c r="Q45" s="8" t="n"/>
+      <c r="O45" s="8" t="inlineStr">
+        <is>
+          <t>김성준 공장장</t>
+        </is>
+      </c>
+      <c r="P45" s="8" t="inlineStr">
+        <is>
+          <t>세이고</t>
+        </is>
+      </c>
+      <c r="Q45" s="8" t="inlineStr">
+        <is>
+          <t>결제 완료·입고내역 자료</t>
+        </is>
+      </c>
       <c r="R45" s="8" t="inlineStr">
         <is>
-          <t>분기/비정기</t>
+          <t>주 1회</t>
         </is>
       </c>
       <c r="S45" s="8" t="inlineStr">
@@ -11745,7 +11960,7 @@
       </c>
       <c r="U45" s="8" t="inlineStr">
         <is>
-          <t>인근 대리점 방문 일정 묶어 이동시간 절감</t>
+          <t>결제·입고내역 자동 정산 시트 연동</t>
         </is>
       </c>
     </row>
@@ -11766,18 +11981,18 @@
         </is>
       </c>
       <c r="D46" s="57" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>목</t>
         </is>
       </c>
       <c r="F46" s="58" t="n">
-        <v>0.4375</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G46" s="58" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="H46" s="7">
         <f>IF(OR(F46="",G46=""),"",(G46-F46)*1440)</f>
@@ -11785,54 +12000,63 @@
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>파트너·대리점관리</t>
+          <t>기획·보고·회의</t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>PTR-01 대리점·파트너사 방문·미팅</t>
+          <t>MGT-06 팀원 업무·산출물 검토·피드백</t>
         </is>
       </c>
       <c r="K46" s="8" t="inlineStr">
         <is>
-          <t>경남지사 방문 미팅 — 판매 현황·요청사항 청취</t>
+          <t>정하님 업무정리 리스트 검토</t>
         </is>
       </c>
       <c r="L46" s="8" t="inlineStr">
         <is>
-          <t>경남지사</t>
-        </is>
-      </c>
-      <c r="M46" s="8" t="n"/>
-      <c r="O46" s="8" t="n"/>
-      <c r="P46" s="8" t="inlineStr">
-        <is>
-          <t>경남지사</t>
-        </is>
-      </c>
+          <t>팀 업무관리</t>
+        </is>
+      </c>
+      <c r="M46" s="8" t="inlineStr">
+        <is>
+          <t>CRM센터-POUR OS(업무보드)</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>https://pourstorecrm.web.app/pour-os</t>
+        </is>
+      </c>
+      <c r="O46" s="8" t="inlineStr">
+        <is>
+          <t>용정하</t>
+        </is>
+      </c>
+      <c r="P46" s="8" t="n"/>
       <c r="Q46" s="8" t="inlineStr">
         <is>
-          <t>방문 미팅 기록</t>
+          <t>검토 의견</t>
         </is>
       </c>
       <c r="R46" s="8" t="inlineStr">
         <is>
-          <t>분기/비정기</t>
+          <t>주 1회</t>
         </is>
       </c>
       <c r="S46" s="8" t="inlineStr">
         <is>
-          <t>반정형</t>
+          <t>비정형(판단 필요)</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>모름</t>
+          <t>아마도 중복</t>
         </is>
       </c>
       <c r="U46" s="8" t="inlineStr">
         <is>
-          <t>대리점 방문 결과를 공용 대리점 카드에 기록·공유</t>
+          <t>업무보드 데이터 자동 집계로 대체</t>
         </is>
       </c>
     </row>
@@ -11853,18 +12077,18 @@
         </is>
       </c>
       <c r="D47" s="57" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>목</t>
         </is>
       </c>
       <c r="F47" s="58" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="G47" s="58" t="n">
-        <v>0.5</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="H47" s="7">
         <f>IF(OR(F47="",G47=""),"",(G47-F47)*1440)</f>
@@ -11872,56 +12096,40 @@
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>파트너·대리점관리</t>
+          <t>기타·행정</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>PTR-02 대리점·파트너 인터뷰·VOC 수집</t>
+          <t>ETC-05 휴게·점심</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>경남지사 인터뷰 진행(질문지 기반 VOC 수집)</t>
-        </is>
-      </c>
-      <c r="L47" s="8" t="inlineStr">
-        <is>
-          <t>경남지사</t>
-        </is>
-      </c>
+          <t>점심 및 휴게</t>
+        </is>
+      </c>
+      <c r="L47" s="8" t="n"/>
       <c r="M47" s="8" t="n"/>
       <c r="O47" s="8" t="n"/>
-      <c r="P47" s="8" t="inlineStr">
-        <is>
-          <t>경남지사</t>
-        </is>
-      </c>
-      <c r="Q47" s="8" t="inlineStr">
-        <is>
-          <t>인터뷰 기록</t>
-        </is>
-      </c>
+      <c r="P47" s="8" t="n"/>
+      <c r="Q47" s="8" t="n"/>
       <c r="R47" s="8" t="inlineStr">
         <is>
-          <t>분기/비정기</t>
+          <t>매일</t>
         </is>
       </c>
       <c r="S47" s="8" t="inlineStr">
         <is>
-          <t>반정형</t>
+          <t>정형(매뉴얼화 가능)</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>모름</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>인터뷰 VOC를 상품·마케팅 기획 입력값으로 자동 연결</t>
-        </is>
-      </c>
+          <t>예 - 확실히 중복</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
@@ -11940,18 +12148,18 @@
         </is>
       </c>
       <c r="D48" s="57" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>목</t>
         </is>
       </c>
       <c r="F48" s="58" t="n">
-        <v>0.5</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="G48" s="58" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="H48" s="7">
         <f>IF(OR(F48="",G48=""),"",(G48-F48)*1440)</f>
@@ -11959,40 +12167,69 @@
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>기타·행정</t>
+          <t>마케팅·광고운영</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
-          <t>ETC-05 휴게·점심</t>
+          <t>MKT-04 인플루언서·체험단 섭외/관리</t>
         </is>
       </c>
       <c r="K48" s="8" t="inlineStr">
         <is>
-          <t>점심 및 휴게</t>
-        </is>
-      </c>
-      <c r="L48" s="8" t="n"/>
-      <c r="M48" s="8" t="n"/>
-      <c r="O48" s="8" t="n"/>
-      <c r="P48" s="8" t="n"/>
-      <c r="Q48" s="8" t="n"/>
+          <t>채림님 퍼포먼스마케팅 진행 방안(①직판 ②대리점·파트너사 2트랙 바이럴) 안내 및 매체·대행사 시장조사 요청</t>
+        </is>
+      </c>
+      <c r="L48" s="8" t="inlineStr">
+        <is>
+          <t>POUR스토어 / 블로그·유튜브·카페·인스타</t>
+        </is>
+      </c>
+      <c r="M48" s="8" t="inlineStr">
+        <is>
+          <t>레뷰, 리뷰플레이스</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>https://pourstorecrm.web.app/pour-os</t>
+        </is>
+      </c>
+      <c r="O48" s="8" t="inlineStr">
+        <is>
+          <t>양채림</t>
+        </is>
+      </c>
+      <c r="P48" s="8" t="inlineStr">
+        <is>
+          <t>인플루언서, 바이럴 대행사(레뷰 등)</t>
+        </is>
+      </c>
+      <c r="Q48" s="8" t="inlineStr">
+        <is>
+          <t>진행 방안 안내·시장조사 요청서</t>
+        </is>
+      </c>
       <c r="R48" s="8" t="inlineStr">
         <is>
-          <t>매일</t>
+          <t>주 1회</t>
         </is>
       </c>
       <c r="S48" s="8" t="inlineStr">
         <is>
-          <t>정형(매뉴얼화 가능)</t>
+          <t>비정형(판단 필요)</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>예 - 확실히 중복</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="n"/>
+          <t>아마도 중복</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>바이럴 매체·대행사 후보 DB 공용화</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -12011,18 +12248,18 @@
         </is>
       </c>
       <c r="D49" s="57" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>목</t>
         </is>
       </c>
       <c r="F49" s="58" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="G49" s="58" t="n">
-        <v>0.5625</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="H49" s="7">
         <f>IF(OR(F49="",G49=""),"",(G49-F49)*1440)</f>
@@ -12030,46 +12267,54 @@
       </c>
       <c r="I49" s="8" t="inlineStr">
         <is>
-          <t>기타·행정</t>
+          <t>채널·스토어운영</t>
         </is>
       </c>
       <c r="J49" s="8" t="inlineStr">
         <is>
-          <t>ETC-04 이동·외근</t>
+          <t>CHN-03 자사몰 운영·관리</t>
         </is>
       </c>
       <c r="K49" s="8" t="inlineStr">
         <is>
-          <t>경남지사 → 가나랜드 이동</t>
+          <t>자사몰 회원 등급별 구매가능 상품 확인 페이지 제작 및 랜딩 링크 삽입 요청</t>
         </is>
       </c>
       <c r="L49" s="8" t="inlineStr">
         <is>
-          <t>대리점(가나랜드)</t>
-        </is>
-      </c>
-      <c r="M49" s="8" t="n"/>
+          <t>POUR스토어 자사몰</t>
+        </is>
+      </c>
+      <c r="M49" s="8" t="inlineStr">
+        <is>
+          <t>자사몰 관리자</t>
+        </is>
+      </c>
       <c r="O49" s="8" t="n"/>
       <c r="P49" s="8" t="n"/>
-      <c r="Q49" s="8" t="n"/>
+      <c r="Q49" s="8" t="inlineStr">
+        <is>
+          <t>등급별 구매가능 페이지 요청서</t>
+        </is>
+      </c>
       <c r="R49" s="8" t="inlineStr">
         <is>
-          <t>분기/비정기</t>
+          <t>1회성</t>
         </is>
       </c>
       <c r="S49" s="8" t="inlineStr">
         <is>
-          <t>정형(매뉴얼화 가능)</t>
+          <t>반정형</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>아마도 중복</t>
+          <t>모름</t>
         </is>
       </c>
       <c r="U49" s="8" t="inlineStr">
         <is>
-          <t>인근 대리점 방문 일정 묶어 이동시간 절감</t>
+          <t>회원등급·판매권한 데이터 연동으로 페이지 자동 생성</t>
         </is>
       </c>
     </row>
@@ -12090,18 +12335,18 @@
         </is>
       </c>
       <c r="D50" s="57" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>목</t>
         </is>
       </c>
       <c r="F50" s="58" t="n">
-        <v>0.5625</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="G50" s="58" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="H50" s="7">
         <f>IF(OR(F50="",G50=""),"",(G50-F50)*1440)</f>
@@ -12109,54 +12354,59 @@
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>파트너·대리점관리</t>
+          <t>데이터·정산</t>
         </is>
       </c>
       <c r="J50" s="8" t="inlineStr">
         <is>
-          <t>PTR-01 대리점·파트너사 방문·미팅</t>
+          <t>DAT-04 리포트·대시보드 작성</t>
         </is>
       </c>
       <c r="K50" s="8" t="inlineStr">
         <is>
-          <t>가나랜드 방문 미팅 — 판매 현황·요청사항 청취</t>
+          <t>POUR스토어 단가·공헌이익·손익계산 대시보드 제작 — 진행중</t>
         </is>
       </c>
       <c r="L50" s="8" t="inlineStr">
         <is>
-          <t>가나랜드</t>
-        </is>
-      </c>
-      <c r="M50" s="8" t="n"/>
+          <t>POUR스토어</t>
+        </is>
+      </c>
+      <c r="M50" s="8" t="inlineStr">
+        <is>
+          <t>단가 대시보드, 엑셀</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>POUR스토어 가격·마진 통합 대시보드 (pour-construction-form.pages.dev)</t>
+        </is>
+      </c>
       <c r="O50" s="8" t="n"/>
-      <c r="P50" s="8" t="inlineStr">
-        <is>
-          <t>가나랜드</t>
-        </is>
-      </c>
+      <c r="P50" s="8" t="n"/>
       <c r="Q50" s="8" t="inlineStr">
         <is>
-          <t>방문 미팅 기록</t>
+          <t>단가·공헌이익·손익 대시보드</t>
         </is>
       </c>
       <c r="R50" s="8" t="inlineStr">
         <is>
-          <t>분기/비정기</t>
+          <t>주 2~3회</t>
         </is>
       </c>
       <c r="S50" s="8" t="inlineStr">
         <is>
-          <t>반정형</t>
+          <t>비정형(판단 필요)</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>모름</t>
+          <t>아마도 중복</t>
         </is>
       </c>
       <c r="U50" s="8" t="inlineStr">
         <is>
-          <t>대리점 방문 결과를 공용 대리점 카드에 기록·공유</t>
+          <t>채널 수수료·원가 데이터 자동 연동으로 수기 입력 제거</t>
         </is>
       </c>
     </row>
@@ -12177,18 +12427,18 @@
         </is>
       </c>
       <c r="D51" s="57" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>목</t>
         </is>
       </c>
       <c r="F51" s="58" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G51" s="58" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="H51" s="7">
         <f>IF(OR(F51="",G51=""),"",(G51-F51)*1440)</f>
@@ -12196,39 +12446,43 @@
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>파트너·대리점관리</t>
+          <t>제조·생산관리</t>
         </is>
       </c>
       <c r="J51" s="8" t="inlineStr">
         <is>
-          <t>PTR-02 대리점·파트너 인터뷰·VOC 수집</t>
+          <t>MFG-08 MSDS·라벨 등 제품 표시사항 제작</t>
         </is>
       </c>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>가나랜드 인터뷰 진행 및 현장 촬영(질문지 기반 VOC 수집)</t>
+          <t>신제품 코트재 MSDS 컬러별 31개 제작 — 진행중</t>
         </is>
       </c>
       <c r="L51" s="8" t="inlineStr">
         <is>
-          <t>가나랜드</t>
-        </is>
-      </c>
-      <c r="M51" s="8" t="n"/>
+          <t>코트재 신제품 31색</t>
+        </is>
+      </c>
+      <c r="M51" s="8" t="inlineStr">
+        <is>
+          <t>챗지피티</t>
+        </is>
+      </c>
       <c r="O51" s="8" t="n"/>
       <c r="P51" s="8" t="inlineStr">
         <is>
-          <t>가나랜드</t>
+          <t>세이고, 쿠팡물류센터</t>
         </is>
       </c>
       <c r="Q51" s="8" t="inlineStr">
         <is>
-          <t>인터뷰 기록·현장 촬영물</t>
+          <t>MSDS 31종</t>
         </is>
       </c>
       <c r="R51" s="8" t="inlineStr">
         <is>
-          <t>분기/비정기</t>
+          <t>1회성</t>
         </is>
       </c>
       <c r="S51" s="8" t="inlineStr">
@@ -12238,12 +12492,12 @@
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
-          <t>모름</t>
+          <t>아니오 - 우리팀 고유</t>
         </is>
       </c>
       <c r="U51" s="8" t="inlineStr">
         <is>
-          <t>인터뷰 VOC를 상품·마케팅 기획 입력값으로 자동 연결</t>
+          <t>품목·색상 데이터 연동으로 MSDS 서식 자동 생성</t>
         </is>
       </c>
     </row>
@@ -12272,10 +12526,10 @@
         </is>
       </c>
       <c r="F52" s="58" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.375</v>
       </c>
       <c r="G52" s="58" t="n">
-        <v>0.75</v>
+        <v>0.4375</v>
       </c>
       <c r="H52" s="7">
         <f>IF(OR(F52="",G52=""),"",(G52-F52)*1440)</f>
@@ -12293,10 +12547,14 @@
       </c>
       <c r="K52" s="8" t="inlineStr">
         <is>
-          <t>부산 → 사무실 복귀 이동</t>
-        </is>
-      </c>
-      <c r="L52" s="8" t="n"/>
+          <t>부산 대리점 방문 이동(사무실 → 경남지사)</t>
+        </is>
+      </c>
+      <c r="L52" s="8" t="inlineStr">
+        <is>
+          <t>대리점(경남지사)</t>
+        </is>
+      </c>
       <c r="M52" s="8" t="n"/>
       <c r="O52" s="8" t="n"/>
       <c r="P52" s="8" t="n"/>
@@ -12323,179 +12581,577 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="n"/>
-      <c r="B53" s="8" t="n"/>
-      <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="n"/>
-      <c r="E53" s="8" t="n"/>
-      <c r="F53" s="8" t="n"/>
-      <c r="G53" s="8" t="n"/>
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>브랜드커머스</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>김송희</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>브랜드커머스, 모여라딜 리드</t>
+        </is>
+      </c>
+      <c r="D53" s="57" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="F53" s="58" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="G53" s="58" t="n">
+        <v>0.4791666666666667</v>
+      </c>
       <c r="H53" s="7">
         <f>IF(OR(F53="",G53=""),"",(G53-F53)*1440)</f>
         <v/>
       </c>
-      <c r="I53" s="8" t="n"/>
-      <c r="J53" s="8" t="n"/>
-      <c r="K53" s="8" t="n"/>
-      <c r="L53" s="8" t="n"/>
+      <c r="I53" s="8" t="inlineStr">
+        <is>
+          <t>파트너·대리점관리</t>
+        </is>
+      </c>
+      <c r="J53" s="8" t="inlineStr">
+        <is>
+          <t>PTR-01 대리점·파트너사 방문·미팅</t>
+        </is>
+      </c>
+      <c r="K53" s="8" t="inlineStr">
+        <is>
+          <t>경남지사 방문 미팅 — 판매 현황·요청사항 청취</t>
+        </is>
+      </c>
+      <c r="L53" s="8" t="inlineStr">
+        <is>
+          <t>경남지사</t>
+        </is>
+      </c>
       <c r="M53" s="8" t="n"/>
       <c r="O53" s="8" t="n"/>
-      <c r="P53" s="8" t="n"/>
-      <c r="Q53" s="8" t="n"/>
-      <c r="R53" s="8" t="n"/>
-      <c r="S53" s="8" t="n"/>
-      <c r="T53" s="8" t="n"/>
-      <c r="U53" s="8" t="n"/>
+      <c r="P53" s="8" t="inlineStr">
+        <is>
+          <t>경남지사</t>
+        </is>
+      </c>
+      <c r="Q53" s="8" t="inlineStr">
+        <is>
+          <t>방문 미팅 기록</t>
+        </is>
+      </c>
+      <c r="R53" s="8" t="inlineStr">
+        <is>
+          <t>분기/비정기</t>
+        </is>
+      </c>
+      <c r="S53" s="8" t="inlineStr">
+        <is>
+          <t>반정형</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>모름</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>대리점 방문 결과를 공용 대리점 카드에 기록·공유</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="n"/>
-      <c r="B54" s="8" t="n"/>
-      <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
-      <c r="E54" s="8" t="n"/>
-      <c r="F54" s="8" t="n"/>
-      <c r="G54" s="8" t="n"/>
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>브랜드커머스</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>김송희</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>브랜드커머스, 모여라딜 리드</t>
+        </is>
+      </c>
+      <c r="D54" s="57" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="F54" s="58" t="n">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="G54" s="58" t="n">
+        <v>0.5</v>
+      </c>
       <c r="H54" s="7">
         <f>IF(OR(F54="",G54=""),"",(G54-F54)*1440)</f>
         <v/>
       </c>
-      <c r="I54" s="8" t="n"/>
-      <c r="J54" s="8" t="n"/>
-      <c r="K54" s="8" t="n"/>
-      <c r="L54" s="8" t="n"/>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>파트너·대리점관리</t>
+        </is>
+      </c>
+      <c r="J54" s="8" t="inlineStr">
+        <is>
+          <t>PTR-02 대리점·파트너 인터뷰·VOC 수집</t>
+        </is>
+      </c>
+      <c r="K54" s="8" t="inlineStr">
+        <is>
+          <t>경남지사 인터뷰 진행(질문지 기반 VOC 수집)</t>
+        </is>
+      </c>
+      <c r="L54" s="8" t="inlineStr">
+        <is>
+          <t>경남지사</t>
+        </is>
+      </c>
       <c r="M54" s="8" t="n"/>
       <c r="O54" s="8" t="n"/>
-      <c r="P54" s="8" t="n"/>
-      <c r="Q54" s="8" t="n"/>
-      <c r="R54" s="8" t="n"/>
-      <c r="S54" s="8" t="n"/>
-      <c r="T54" s="8" t="n"/>
-      <c r="U54" s="8" t="n"/>
+      <c r="P54" s="8" t="inlineStr">
+        <is>
+          <t>경남지사</t>
+        </is>
+      </c>
+      <c r="Q54" s="8" t="inlineStr">
+        <is>
+          <t>인터뷰 기록</t>
+        </is>
+      </c>
+      <c r="R54" s="8" t="inlineStr">
+        <is>
+          <t>분기/비정기</t>
+        </is>
+      </c>
+      <c r="S54" s="8" t="inlineStr">
+        <is>
+          <t>반정형</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>모름</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>인터뷰 VOC를 상품·마케팅 기획 입력값으로 자동 연결</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="n"/>
-      <c r="B55" s="8" t="n"/>
-      <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="n"/>
-      <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="n"/>
-      <c r="G55" s="8" t="n"/>
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>브랜드커머스</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>김송희</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>브랜드커머스, 모여라딜 리드</t>
+        </is>
+      </c>
+      <c r="D55" s="57" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="F55" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G55" s="58" t="n">
+        <v>0.5416666666666666</v>
+      </c>
       <c r="H55" s="7">
         <f>IF(OR(F55="",G55=""),"",(G55-F55)*1440)</f>
         <v/>
       </c>
-      <c r="I55" s="8" t="n"/>
-      <c r="J55" s="8" t="n"/>
-      <c r="K55" s="8" t="n"/>
+      <c r="I55" s="8" t="inlineStr">
+        <is>
+          <t>기타·행정</t>
+        </is>
+      </c>
+      <c r="J55" s="8" t="inlineStr">
+        <is>
+          <t>ETC-05 휴게·점심</t>
+        </is>
+      </c>
+      <c r="K55" s="8" t="inlineStr">
+        <is>
+          <t>점심 및 휴게</t>
+        </is>
+      </c>
       <c r="L55" s="8" t="n"/>
       <c r="M55" s="8" t="n"/>
       <c r="O55" s="8" t="n"/>
       <c r="P55" s="8" t="n"/>
       <c r="Q55" s="8" t="n"/>
-      <c r="R55" s="8" t="n"/>
-      <c r="S55" s="8" t="n"/>
-      <c r="T55" s="8" t="n"/>
+      <c r="R55" s="8" t="inlineStr">
+        <is>
+          <t>매일</t>
+        </is>
+      </c>
+      <c r="S55" s="8" t="inlineStr">
+        <is>
+          <t>정형(매뉴얼화 가능)</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>예 - 확실히 중복</t>
+        </is>
+      </c>
       <c r="U55" s="8" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="n"/>
-      <c r="B56" s="8" t="n"/>
-      <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="n"/>
-      <c r="E56" s="8" t="n"/>
-      <c r="F56" s="8" t="n"/>
-      <c r="G56" s="8" t="n"/>
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>브랜드커머스</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>김송희</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>브랜드커머스, 모여라딜 리드</t>
+        </is>
+      </c>
+      <c r="D56" s="57" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="F56" s="58" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="G56" s="58" t="n">
+        <v>0.5625</v>
+      </c>
       <c r="H56" s="7">
         <f>IF(OR(F56="",G56=""),"",(G56-F56)*1440)</f>
         <v/>
       </c>
-      <c r="I56" s="8" t="n"/>
-      <c r="J56" s="8" t="n"/>
-      <c r="K56" s="8" t="n"/>
-      <c r="L56" s="8" t="n"/>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>기타·행정</t>
+        </is>
+      </c>
+      <c r="J56" s="8" t="inlineStr">
+        <is>
+          <t>ETC-04 이동·외근</t>
+        </is>
+      </c>
+      <c r="K56" s="8" t="inlineStr">
+        <is>
+          <t>경남지사 → 가나랜드 이동</t>
+        </is>
+      </c>
+      <c r="L56" s="8" t="inlineStr">
+        <is>
+          <t>대리점(가나랜드)</t>
+        </is>
+      </c>
       <c r="M56" s="8" t="n"/>
       <c r="O56" s="8" t="n"/>
       <c r="P56" s="8" t="n"/>
       <c r="Q56" s="8" t="n"/>
-      <c r="R56" s="8" t="n"/>
-      <c r="S56" s="8" t="n"/>
-      <c r="T56" s="8" t="n"/>
-      <c r="U56" s="8" t="n"/>
+      <c r="R56" s="8" t="inlineStr">
+        <is>
+          <t>분기/비정기</t>
+        </is>
+      </c>
+      <c r="S56" s="8" t="inlineStr">
+        <is>
+          <t>정형(매뉴얼화 가능)</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>아마도 중복</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>인근 대리점 방문 일정 묶어 이동시간 절감</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="n"/>
-      <c r="B57" s="8" t="n"/>
-      <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
-      <c r="E57" s="8" t="n"/>
-      <c r="F57" s="8" t="n"/>
-      <c r="G57" s="8" t="n"/>
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>브랜드커머스</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>김송희</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>브랜드커머스, 모여라딜 리드</t>
+        </is>
+      </c>
+      <c r="D57" s="57" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="F57" s="58" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="G57" s="58" t="n">
+        <v>0.6041666666666666</v>
+      </c>
       <c r="H57" s="7">
         <f>IF(OR(F57="",G57=""),"",(G57-F57)*1440)</f>
         <v/>
       </c>
-      <c r="I57" s="8" t="n"/>
-      <c r="J57" s="8" t="n"/>
-      <c r="K57" s="8" t="n"/>
-      <c r="L57" s="8" t="n"/>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>파트너·대리점관리</t>
+        </is>
+      </c>
+      <c r="J57" s="8" t="inlineStr">
+        <is>
+          <t>PTR-01 대리점·파트너사 방문·미팅</t>
+        </is>
+      </c>
+      <c r="K57" s="8" t="inlineStr">
+        <is>
+          <t>가나랜드 방문 미팅 — 판매 현황·요청사항 청취</t>
+        </is>
+      </c>
+      <c r="L57" s="8" t="inlineStr">
+        <is>
+          <t>가나랜드</t>
+        </is>
+      </c>
       <c r="M57" s="8" t="n"/>
       <c r="O57" s="8" t="n"/>
-      <c r="P57" s="8" t="n"/>
-      <c r="Q57" s="8" t="n"/>
-      <c r="R57" s="8" t="n"/>
-      <c r="S57" s="8" t="n"/>
-      <c r="T57" s="8" t="n"/>
-      <c r="U57" s="8" t="n"/>
+      <c r="P57" s="8" t="inlineStr">
+        <is>
+          <t>가나랜드</t>
+        </is>
+      </c>
+      <c r="Q57" s="8" t="inlineStr">
+        <is>
+          <t>방문 미팅 기록</t>
+        </is>
+      </c>
+      <c r="R57" s="8" t="inlineStr">
+        <is>
+          <t>분기/비정기</t>
+        </is>
+      </c>
+      <c r="S57" s="8" t="inlineStr">
+        <is>
+          <t>반정형</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>모름</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>대리점 방문 결과를 공용 대리점 카드에 기록·공유</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="n"/>
-      <c r="B58" s="8" t="n"/>
-      <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="n"/>
-      <c r="E58" s="8" t="n"/>
-      <c r="F58" s="8" t="n"/>
-      <c r="G58" s="8" t="n"/>
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>브랜드커머스</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>김송희</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>브랜드커머스, 모여라딜 리드</t>
+        </is>
+      </c>
+      <c r="D58" s="57" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="F58" s="58" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="G58" s="58" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="H58" s="7">
         <f>IF(OR(F58="",G58=""),"",(G58-F58)*1440)</f>
         <v/>
       </c>
-      <c r="I58" s="8" t="n"/>
-      <c r="J58" s="8" t="n"/>
-      <c r="K58" s="8" t="n"/>
-      <c r="L58" s="8" t="n"/>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>파트너·대리점관리</t>
+        </is>
+      </c>
+      <c r="J58" s="8" t="inlineStr">
+        <is>
+          <t>PTR-02 대리점·파트너 인터뷰·VOC 수집</t>
+        </is>
+      </c>
+      <c r="K58" s="8" t="inlineStr">
+        <is>
+          <t>가나랜드 인터뷰 진행 및 현장 촬영(질문지 기반 VOC 수집)</t>
+        </is>
+      </c>
+      <c r="L58" s="8" t="inlineStr">
+        <is>
+          <t>가나랜드</t>
+        </is>
+      </c>
       <c r="M58" s="8" t="n"/>
       <c r="O58" s="8" t="n"/>
-      <c r="P58" s="8" t="n"/>
-      <c r="Q58" s="8" t="n"/>
-      <c r="R58" s="8" t="n"/>
-      <c r="S58" s="8" t="n"/>
-      <c r="T58" s="8" t="n"/>
-      <c r="U58" s="8" t="n"/>
+      <c r="P58" s="8" t="inlineStr">
+        <is>
+          <t>가나랜드</t>
+        </is>
+      </c>
+      <c r="Q58" s="8" t="inlineStr">
+        <is>
+          <t>인터뷰 기록·현장 촬영물</t>
+        </is>
+      </c>
+      <c r="R58" s="8" t="inlineStr">
+        <is>
+          <t>분기/비정기</t>
+        </is>
+      </c>
+      <c r="S58" s="8" t="inlineStr">
+        <is>
+          <t>반정형</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>모름</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>인터뷰 VOC를 상품·마케팅 기획 입력값으로 자동 연결</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="n"/>
-      <c r="B59" s="8" t="n"/>
-      <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
-      <c r="E59" s="8" t="n"/>
-      <c r="F59" s="8" t="n"/>
-      <c r="G59" s="8" t="n"/>
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>브랜드커머스</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>김송희</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>브랜드커머스, 모여라딜 리드</t>
+        </is>
+      </c>
+      <c r="D59" s="57" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="F59" s="58" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G59" s="58" t="n">
+        <v>0.75</v>
+      </c>
       <c r="H59" s="7">
         <f>IF(OR(F59="",G59=""),"",(G59-F59)*1440)</f>
         <v/>
       </c>
-      <c r="I59" s="8" t="n"/>
-      <c r="J59" s="8" t="n"/>
-      <c r="K59" s="8" t="n"/>
+      <c r="I59" s="8" t="inlineStr">
+        <is>
+          <t>기타·행정</t>
+        </is>
+      </c>
+      <c r="J59" s="8" t="inlineStr">
+        <is>
+          <t>ETC-04 이동·외근</t>
+        </is>
+      </c>
+      <c r="K59" s="8" t="inlineStr">
+        <is>
+          <t>부산 → 사무실 복귀 이동</t>
+        </is>
+      </c>
       <c r="L59" s="8" t="n"/>
       <c r="M59" s="8" t="n"/>
       <c r="O59" s="8" t="n"/>
       <c r="P59" s="8" t="n"/>
       <c r="Q59" s="8" t="n"/>
-      <c r="R59" s="8" t="n"/>
-      <c r="S59" s="8" t="n"/>
-      <c r="T59" s="8" t="n"/>
-      <c r="U59" s="8" t="n"/>
+      <c r="R59" s="8" t="inlineStr">
+        <is>
+          <t>분기/비정기</t>
+        </is>
+      </c>
+      <c r="S59" s="8" t="inlineStr">
+        <is>
+          <t>정형(매뉴얼화 가능)</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>아마도 중복</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
+          <t>인근 대리점 방문 일정 묶어 이동시간 절감</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n"/>
